--- a/data/digest_combined_2026-06-09.xlsx
+++ b/data/digest_combined_2026-06-09.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дайджест 2026-06-09" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Дайджест 2026-06-09'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Дайджест 2026-06-09'!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L223"/>
+  <dimension ref="A1:M223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -491,12 +491,13 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="80" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="25" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -532,30 +533,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Опис RSS</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Домен</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Категорія</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Країна</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Сировина</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Посилання</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Файл</t>
         </is>
@@ -594,30 +600,35 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>Прогноз експорту сої з Бразилії в червні показує зниження в річному обчисленні SunSirs</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Незернові компоненти для комбікорму</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Бразилія</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Зернові, Незернові компоненти, Сільськогосподарська продукція</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBpUUNpU1NNVUZiaWlVMnJtQnI5T1BTUnYzV3VNZTVFa0ZJYVRVYlhsSjJOVThLSUF0UHhOak1wbUprdXZoY3RjVGx5dEl0MW00NGRUZC1CSElQZjR5SHc?oc=5</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -656,30 +667,35 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>Ціни на нафту почали цього тижня зі стрибка після останнього спалаху бойових дій на Близькому Сході, цього разу між Іраном та Ізраїлем. Це гірша новина для світової економіки, ніж була б місяць тому. Світові запаси нафти починають висихати, і ніщо їх не поповнює. Дедалі більше попереджень про те, що світ зіткнувся з безпрецедентним скороченням поставок нафти, і ціни ось-ось зростуть набагато вище. Останнім, хто приєднався до зростаючого хору попереджень, був Chevron</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>світ</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>https://oilprice.com/Energy/Energy-General/Global-Economy-Is-One-Oil-Price-Spike-Away-From-Trouble.html</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -718,30 +734,35 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Міна не обов’язково вражає судно, щоб порушити світову торгівлю. В Ормузькій протоці лише загроза мін викликала невизначеність у всій морській галузі,...</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Іран</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>https://gcaptain.com/clearing-the-strait-how-autonomous-systems-are-redefining-mine-countermeasure-operations/</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -780,30 +801,35 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>Дефіцит сечовини викликає хаос в Akot The Times of India</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTXpHdFNSLUl4NVBTbGxxbktkVXA0X3JZeExsYXBjY21CRjFaYXUtTzBsZThZZ0RJSjhpaU9yRzIxWWRDX29fMS02ZU5SODBJRTFtblB5cHIyUENUNzRUbFFWTmdmU0tHNDlEaGI3blZ1dnJsaWFBRkRkVnZlUXI1MWdTQWJ3Vnp4WHhqSUxtT0R2Mm9IN3JIR3Z0VmhKN3QwZkpBWHNnMmFxelFD0gGyAUFVX3lxTE5NWmJVOGgwNl9wSEljallVRTZyTVdZczVMUGxhQ1l6S0I1WGJiT0h1aHE2S0hDZFdNODctc001Wm1yVUVxT1V0R3NweHZmZHVxLVBaNlBPb0J3VTc1aHQ3T3lTNVRkRlRvdTRNbGI0Z0U4Ml9SM1dGZEVSR21GYWhVa0w3UDhZNW54T2VNbVZyanJ5Sk5ad1J1Skdyam42bEJSbWU5NmJrYzZYc0xIWmwxcVE?oc=5</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -842,30 +868,35 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>Фермери протестують в Амрітсарі через дефіцит сечовини та добрив із заходами безпеки The News Mill</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQVnlWZmI0OGZvVVVZTVd0RzhNczRxWVBqYWhZZWd0eHByRHM2dGNKY3l2a1ZnYlREOXU0bVRxSXlsbGhIbzdLdkdDaGtBYVlhaVlSa3JKUkxCcnZOMFQzbi1xT014VEY0bTU5SmtPSlZTbnZ4RmtTT1JQRGpLemZiTHhmczk4aDBNZlRSYzQ3T2twWG81bmQyVzJ1RlVCUDZ5anVZZk5ib2F2WnNiMWl4a2FrV3RuYVcwb2JYTkpiZWdkUy1y?oc=5</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -904,30 +935,35 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>Ормузька протока зрештою буде знову відкрита, але Іран і Оман встановлять нові умови для проходу, включаючи плату за транзит, сказав Казем Джалалі, посол Ірану в Росії, в інтерв’ю виданню «Известия» в понеділок. «Звичайно, ця протока буде відкритою, але з новими умовами, які будуть визначені владою Ірану та Оману», — цитує Reuters слова Джалалі російському виданню. "Ми розуміємо, що Іран і Оман надають певні послуги, пов'язані з цією протокою. І буде стягуватися плата</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Іран, Оман</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>https://oilprice.com/Latest-Energy-News/World-News/Iranian-Official-Says-Hormuz-to-Reopen-with-New-Toll-Regime.html</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -966,26 +1002,31 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>ЄС запровадив санкції проти Ірану через обмеження морського руху в Ормузі Reuters</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Іран, ЄС</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNR1lTSXVKQ2pJQlEzZTg4Z3FvUjdzMEg5QlhuTFo1R2NWZGgwMWw3REhuODBIUjN4VWFCMV9ZZzhXTlpZaVBXZGJodUFVbkU0ME1Ib2hVblljSUtuNXdKZ0gwOVFZRHRCcHJlckYzM193WUZFUkFHSl9KV3ZCb25DM1RxMGhkSnZqMzJpSndTZFZ4czR4RFFMelpjUGZsS2FlYXlFaEV1WFRLbmx1Z1BwV0FGbw?oc=5</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1024,30 +1065,35 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>Найближчими тижнями читачі дедалі частіше бачитимуть дві рідко вживані фрази в матеріалах про наші світові запаси нафти, що скорочуються: «операційний мінімум» і «дно резервуарів». Фрази більш-менш означають те саме, хоча перша є більш абстрактною та точною, тоді як друга є більш наочною. Вони означають швидке виснаження існуючих запасів нафти та передвіщають стрибки цін, що відбудуться через втрату поставок нафти з Перської затоки через закриття Іраном Ормуської протоки.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Глобально</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>https://oilprice.com/Energy/Energy-General/The-Countdown-to-a-Major-Oil-Price-Surge-Has-Begun.html</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1086,30 +1132,35 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>8 червня – пов’язані з Іраном єменські хуси заявили в понеділок, що вони заборонять кораблям, пов’язаним з Ізраїлем, плавати в Червоному морі після того, як Ізраїль поновив свої військові атаки на Іран, що посилило занепокоєння щодо глобального судноплавства та енергетики...</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Йемен, Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>https://gcaptain.com/why-the-iran-aligned-houthis-threatening-red-sea-shipping-could-mean-more-for-the-oil-market-this-time/</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1148,30 +1199,35 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>Протест фермерів підкреслює кризу сечовини на тлі напруги глобального ланцюга поставок Devdiscourse</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNWE5iZzU5Qzd6bDlpWnNDaVNmNGFsU0RqR0FWdU1xS0FIcG1hcG53M21JWE5zQjQtS1dqdW5XMC0temNEb1J6T3dDLTZydGJSRE9vUG0zN3ZrbmFEZmlqUUkxUHFpcGxZVzFuZVkxX1pPNW01bnRkMzl0djlHZV80QnFkSmo3cFA0T1Zia1RNVWgzMjNlWGhmR3VjSlQ3VXdaMVNOTXhGbWQ5X0J4Z2RPSjBISEJsRG1MSFFtR0szcmU2bk3SAcgBQVVfeXFMUFZaZmlDOXlMRjVYejhFN1NQRDZoOEZ0bG9TYlB3SkNMYXlTa0ZuS21KYkVKVm9ydklBdGRZclNuTGNNcVMzeUwxdC1DaGxNUDI0bVl1SGREeGxHVGMwazZVOHZuUlBQZHBsaHotYTVudnpGak9HS2EyQllKdFZ1d1pXSWNHZXZIOTZ0VWdXeThUYTB2ZEM4QzBWTjlkY0c5QXdiWko1bEI3cFRpeHVuMDk5SmVVTV9IbTNBNV9TeTAwamVDcU91aXo?oc=5</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1210,30 +1266,35 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>Напруженість на Близькому Сході різко загострилася після того, як Ізраїль завдав ударів по Ірану, викликавши нове занепокоєння для світових ринків судноплавства, які вже борються з проблемами в Ормузькій протоці та поновленням загроз у Червоному морі. Ізраїльські військові заявили, що вони завдали удару по нафтохімічному заводу на південному заході Ірану, а також по військових цілях на заході та...</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Ізраїль, Іран, Йемен</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>https://splash247.com/houthis-enter-the-fray-as-israel-and-iran-trade-missiles/</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1272,26 +1333,31 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>Іран запускає ракети по Ізраїлю, а Трамп захищає перемир'я Bloomberg</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQc1o0YklsWHlXbVpHNzktdGUwZDlXSWJ4MHdOd3FGVzh4VGQ5MGJwRHFJclNMbDd6UlpWTlZxeVlILXA3WExlZ3VEUFlkOE1Vb2pEbHc5LU00WlFUVWVXbVRzZGhuRkg4RHV0dTAyTjZDY2Eybm9PY014N3RzNVlvV19qQlNvZ0VmSFlSblo2blltMlhxaUhBVGxmNjZkTWVoZ1dWZGxJNFdoTHlYUkxUYXdrcw?oc=5</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1330,30 +1396,35 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>Трамп каже, що він буде тиснути на Ізраїль, щоб він стримався після того, як Іран відповість на напад на Бейрут Reuters</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Ізраїль, Іран</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQQ09pbXlqUEZwdUE4cVVKVEtySklkRGIwSmx6LXlNZm1qWnN1cE8wT1FkODFaUGtJVWh3UG1CRXRMM3JuUWpKQ3ZwOU82aGZpM0llWkZvNUhyLUx5dFJHeV9Bd1B0Rm9DQVdhWno2aG9IQWhxZFhlc2RSbGRlV3A4UklMVFhFZkxvSlBfS3pWaGljaE83RklTb0pIazNHejYydUFuT2ZoQTN5Y05LNU14bURUaWVOTGc?oc=5</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1392,26 +1463,31 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>З початку війни в Ірані ставки на контейнери з Азії до США зросли на 109% Bloomberg</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Іран, США, Азія</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPWVZSZFJBbXVLNEpKa1BlenJJVVBCNzBJVVBISng5M0lULUxZTGtPMWd1OWoybUlmMG9xdlVYTTFSXzl1MWVlWjNIanNRd3Zib2NVUm85YVpocFAyYkJCTWpFakc2M0tJNEN0ZmZuMjJxMTlCSGkwSUJod1d6d1Y0WENHQ0g3WWhxdGRlSVByY1lfMWdLa21qdjhsQmhzM2RURVFHVmZxeWk5bmx5empF?oc=5</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1450,30 +1526,35 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
+          <t>Прем'єр-міністр Ізраїлю заявив, що його країна стримує вогонь "на даний момент", після того, як збройні сили Ірану заявили про припинення військових дій.</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="L16" s="7" t="inlineStr">
         <is>
           <t>https://www.bbc.com/news/articles/cj6ge150z5go?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1512,26 +1593,31 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
+          <t>П’ятий катарський танкер зі зрідженим природним газом пройшов через Ормузьку протоку з вантажем, свідчать дані відстеження суден, у результаті чого загальна кількість завантажених СПГ-суден, які вийшли з водного шляху з початку війни, досягла дев’яти. Під контролем QatarEnergy…</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Катар</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>https://www.marinelink.com/news/fifth-qataricontrolled-lng-tanker-exits-540065</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1570,30 +1656,35 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
+          <t>Імпорт нафти в Китай впав до восьмирічного мінімуму через військові зриви Bloomberg</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="L18" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNYXM4MWZUVmhPb19HcEF3aUFfVFJja21WVFNrYTBrSGVBUGs3Rm9TdjJNN3JaNTc5dkt1RVY5RjBzWko2WHhPbE8zRkpUazZUb2NxaG5ld0cxS2ZhN3J4eEtqTlhxSWlYdHVsMTNNdnUzTjI1Tmx5dlI4YUJBX2k0a1VwRlVfOWc1X25EcE53TUNQLTlNUTZ0QVhVcU9WX2FOZWxUX2hKU28tdG5rR1pfT1VoTDk?oc=5</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1632,30 +1723,35 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
+          <t>Президент попередив Нетаньяху, що він залишиться сам, якщо атаки продовжаться після того, як Ізраїль та Іран призупинять бойові дії</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>США, Іран</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>https://www.aljazeera.com/news/2026/6/9/trump-warns-netanyahu-youll-be-on-your-own-if-attacks-on-iran-continue?traffic_source=rss</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1694,30 +1790,35 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
+          <t>Посольство Китаю у Вашингтоні, округ Колумбія, засуджує визначення, називаючи його «дискримінаційним».</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Обладнання</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>https://www.aljazeera.com/economy/2026/6/9/us-lists-chinas-byd-alibaba-baidu-as-chinese-military-companies?traffic_source=rss</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1756,30 +1857,35 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>Ескалація цих вихідних між Іраном та Ізраїлем показала, наскільки можуть бути надії на угоду, і наскільки трейдери можуть бути надто самовдоволеними щодо триваючого перебою з поставками нафти. Після того, як Іран перекрив Ормузьку протоку понад три місяці тому, глобальні запаси нафти та понад 1,2 мільярда барелів Китаю, високі обсяги нафти на воді та здатність Саудівської Аравії швидко перенаправляти свій експорт, щоб не залежати від Ормузького вузла, не давали цінам на нафту різко підскочити.</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>https://oilprice.com/Energy/Crude-Oil/Risks-to-Red-Sea-Oil-Exports-Could-Roil-Oil-Market-Further.html</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1818,26 +1924,31 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
+          <t>Нові запропоновані списки націлені на російський «військово-промисловий комплекс, порушників прав людини та пропагандистів».</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Росія, ЄС</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>https://www.aljazeera.com/news/2026/6/8/eu-planning-to-add-to-1-5-trillion-sanctions-hit-on-russia?traffic_source=rss</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1876,30 +1987,35 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
+          <t>Глобальна торгівля сьогодні знаходиться в центрі «структурного стресу», в якому геополітика, енергетична залежність і кліматичні обмеження збиваються разом, змінюючи потоки товарів, капіталу та політичні пріоритети. Це було центральною темою нещодавньої широкомасштабної дискусії між Іларією Мазеллі, керівником відділу аналізу макроекономічної та ринкової інформації компанії Maersk, і Джоном Летцінгом, ...</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>світ</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>https://www.hellenicshippingnews.com/choke-points-energy-shock-and-policy-drift/</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -1938,30 +2054,35 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
+          <t>Ринки в Азії постраждали від розпродажу технологій, а нафта нестабільна, оскільки Іран та Ізраїль атакують один одного.</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
+      <c r="L24" s="7" t="inlineStr">
         <is>
           <t>https://www.bbc.com/news/articles/c78yd5g9qx0o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2000,30 +2121,35 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
+          <t>Фермери протестують у Пенджабі через брак сечовини та підвищення цін на паливо land2capital.com</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Добрива, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="L25" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTXp4RmNwc2ZKUFVsc1Y5aUg4QkN3akdBUVIzWVY3bUphcDZBbDhBMG5PLVJaSDBVY05ITFpLMlpfLUNFaGQyM05LalVJZFozRERnZE5YbEQ1enZPOXNIb2ZnLThvQ3hndDU5WnNVdWtRZDQ3b0wtVGJTWWx6X01OT0dHYUhMVVUxRlB6NnNvWV9zUXNPYnpOa3hDQ1c1di05cmt1N0ZxTVhSZF80?oc=5</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2062,30 +2188,35 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
+          <t>Сенатори США Марк Келлі (штат Аризона) та Елізабет Воррен (штат Массачусетс) тиснуть на адміністрацію Трампа, щоб відновити призупинені портові збори для суден, пов’язаних з Китаєм, стверджуючи, що ці заходи мають вирішальне значення для відновлення американського...</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>США, Китай</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr">
+      <c r="L26" s="7" t="inlineStr">
         <is>
           <t>https://gcaptain.com/senators-urge-trump-administration-to-reinstate-port-fees-on-chinese-ships/</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2124,30 +2255,35 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>Глобальні обсяги контейнерних перевезень зберігали високий темп у квітні, показавши значне зростання в річному обчисленні в перший повний місяць після того, як Іран закрив Ормузьку протоку. Згідно з даними Container Trade Statistics, незважаючи на серйозні збої внаслідок війни в Ірані, де військові дії зараз простягаються від Перської затоки до Середземного моря, світовий контейнерний рух залишався «надзвичайно стабільним» і становив 16,2 мільйона двадцятифутових еквівалентних одиниць. Це на 4% більше, ніж у квітні 2025 року, і незначне покращення на 1,6%.</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Глобально</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/containers-say-hold-my-disruptions-as-ocean-rates-surge</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2186,30 +2322,35 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
+          <t>Керівник British Airways попередив, що ціни на авіаквитки знову зростуть, якщо витрати на пальне залишаться високими. Виконавчий директор авіакомпанії Шон Дойл сказав, що «нікуди не подітися» від того факту, що «якщо пальне подорожчає, тарифи повинні піднятися». З початку війни в Ірані в лютому ціни на авіапаливо різко зросли. Незважаючи на переговори про припинення вогню, Ормузька протока, яка постачає близько 40 відсотків авіаційного палива в Європі, залишається закритою. Після попередження BA про можливе підвищення цін минулого місяця відключити</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Європа, Іран</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>https://oilprice.com/Energy/Energy-General/Airfares-Are-Set-to-Rise-Again-as-the-Fuel-Crisis-Deepens.html</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2248,30 +2389,35 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>Росія готується різко скоротити експорт сирої нафти цього місяця, оскільки зростаючі збої на нафтопереробних заводах, дефіцит палива та бомбардування в Україні змушують Москву перенаправляти більше барелів на внутрішній ринок. Експорт із західних портів Росії Приморськ, Усть-Луга та Новоросійськ, як очікується, впаде приблизно до 1,7 мільйона барелів на день у червні з 2,5 мільйона барелів на день у травні, згідно з підрахунками Reuters на основі попередніх галузевих і торгових даних. Занепад відбувається, коли цього прагне Росія</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Росія</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>https://oilprice.com/Latest-Energy-News/World-News/Russia-Slashes-Oil-Exports-As-Fuel-Shortages-And-Drone-Attacks-Bite.html</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2310,26 +2456,31 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
+          <t>Як битва Ізраїлю з Хезболлою вписується у війну в Ірані Bloomberg</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="7" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQSlN1ODJtWDh0VXZZVlJsbUM1c0l5eVJlUk5aZDJMbE9nbVNWcGZJeVQ3VG56TGtZZWJMcmRQcjdSZlU0MUZKaE9BcEhpVXRfUlBDel9LSHZVQVlJcU9WaGg2cnhwMVdQNlU2WDVVN1QtMkUtUVpZQS1ieUNIZlMwalF5ZVgwbVM0aVhyX3drdTNLaE4ycWZMNHFPbkV4N1BuZVVEUVpvc3VMU2hYVzJVZG5zWDBIemNtcWc?oc=5</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2368,26 +2519,31 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
+          <t>Британський індекс FTSE 100 відновився після низьких значень, оскільки Ізраїль та Іран припинили завдавати ударів один одному Reuters</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Ізраїль, Іран</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQNDdEa2lUd1oybTU4QUd5UFVXeDFyTFR3SS0ySkRMN3RfY21VTW9pY3JRS0hJa3dnTWk1RzNYMGFJSkFlVU9STS1zaGNBOWVtNjVwbVZOLTA3cFZrVWVZaDVuWFRpSzQ2SEJybHprSU9WTS12b2xIdHVzQ0hxSFE0RlY3WExtbGJwRGdTaFF2UmRTOUdJSFN1R05ab2pTX2xKLTJIMFo4bHMzb0E?oc=5</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2426,30 +2582,35 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
+          <t>Десятиліттями нафтотрейдери, керівники та аналітики попереджали, що закриття Ормузької протоки стане глобальною економічною катастрофою.</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Глобально</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>https://gcaptain.com/why-oils-not-at-200-after-the-biggest-supply-shock-in-history/</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2488,30 +2649,35 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
+          <t>Стрімке зростання цін на добрива зменшує перевагу бразильських фермерів перед американськими конкурентами Reuters</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Бразилія, США</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="K33" s="7" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOTTRJN0N3YTkwemFtSTJzRjRZWnJXVHJFRWRGZGNEeF8zQXZJVXVSRXlHRnJUYVRtdXZEZjhUXzljSGZRTEUzWVRnZTZLSFF0Q1AydVY0TDc1WTRLSHB4OTRWVDB6bkcyZkxhNUJ3UmlFMDRReXNfendtMV9UZncxUHhzZXk5Y29OMWJnSTBKM0ZwRjdhSFpnakJSMlJkamlrZEhETE1UVmN0akgweDBZWWFzeDhuWkg4N3c?oc=5</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2550,30 +2716,35 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
+          <t>Після закриття Ормузької протоки для більшості комерційних суден наприкінці лютого 2026 року приблизно 1550 суден, що перевозили приблизно 20 000 моряків, не змогли пройти транзитом або вирішили залишитися на якорі в Перській затоці, Оманській затоці та підходах.</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Іран, ОАЕ, Оман</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K34" s="7" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>https://www.marinelink.com/news/vps-fuel-quality-management-vessels-540049</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2612,30 +2783,35 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
+          <t>Міністри Великої сімки прагнуть до спільних дій щодо добрив, оскільки розгорається війна Постачання Bloomberg</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>G7 країни</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPMFlTcjhvMmNkUzNTY1htcDBEdFhxa3VMU1VLTnM3dmgzSThUMlQtcjNkV0Z0N04wVE1LMDBXYWRWZFpxTHN3NFY5Wnl6Mk5fUXdXTldKak9sTHNoM01mVnNyLVdPZDlPYmxQSWJRdXY4ZzVGcXRGV2g3X0ZIUmM2NVF5VkZHMnpLdkJ5RDhkUEM4TXhSLVRTYUh2M0tYUWxxWENJWUNoSTRBS3prb0NTMjE1NHQ?oc=5</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2674,30 +2850,35 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
+          <t>Європейський імпорт дизельного та авіаційного палива скорочується, оскільки триває війна Bloomberg</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Європа</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K36" s="7" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQQ1BPbUVRWGtQQTk4V0RvYllwUVVIZ2NSOVNRYW5tc1lGOFlxSWJDNG12ZWxqbHhPb1dpc3NnWHVzQlRVeUY1S1hUTW9iYnB5dDVGemEwb2h1aVZLQmhSTE5XMFAxdHJUUGJnWmRJdHNSSmZpVDZ3amI0OTd2dlJ3M1Axc05RVzI5V0RFYVRXel93OVR4cmprSUtOdGlmemNuaVNpTTNlbGxEMS1VOEEzRGhPaEg?oc=5</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2736,26 +2917,31 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
+          <t>Велика ескалація торгівлі Ізраїлю та Ірану, Трамп раптово припинив інтерв’ю NBC, змінивши звички споживачів США AP News</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Близький Схід</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE45T0JsR191dVA4SnVoODY0c2pTOVBBckE3aDMzdER0QTdIOTBkMGlkNEtkR0RudWRYRnBhd3poRUVJcElJYWFlV1N5UTdZV0tVZF9KRDBvazBKWElpdDA5NjFUQkQ?oc=5</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2794,30 +2980,35 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
+          <t>Зростаюча волатильність цін на пальне збільшує тиск на логістичні витрати для індійських експортерів/імпортерів. Останнім ударом стала хвиля надзвичайних надбавок на паливо, оголошених CMA CGM на внутрішньому боці Індії для торгівлі до/з Африки. Вони охоплюють вантажі, що надходять до Південної Африки, Танзанії, Мозамбіку та Кенії та вивозяться з них, згідно з численними комерційними повідомленнями, випущеними французьким лайнером минулого тижня. І масштаб підвищення тарифів приголомшливий: йде ... Після паливної кризи ведеться до значного CMA CGM</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Індія, Африка</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>https://theloadstar.com/fuel-crisis-drives-hefty-inland-surcharges-on-india-africa-cargo/</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2856,30 +3047,35 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>Хуси введуть «повну заборону» на ізраїльські кораблі в Червоному морі Bloomberg</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Йемен, Ізраїль</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNSE5ZTVFuNHNXUkhuTVJXdXR2R2QwVm9BVlZfdHBDSHZody03R2w2RFlET0l1dEUzeDRMWEpoUFNKTTMzUTNyVUZBRUZkNTNZMmV5Q2JWTU1qd2hGOGtMT3ZYbXNoZklqNDJxeFdDSjlkZFA1dEZYN0xiTGl2MFhiX2tHUDVMTmtYaWZqS3VYaWZNT2lDYnhnNFZlSkNBczQtc3BlZ1FYRmxGZnMwcUw4Zy1Obw?oc=5</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2918,26 +3114,31 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
+          <t>Ціни на вугілля в Азії досягли 2-річного максимуму через експортні правила Індонезії Bloomberg</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Індонезія</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPWktvMEZiNS1id3pvclk2aFBwem9DMEdjRE5JbW1GRjRhNEpTd3FoNTE4UzMxckphUDdNWTJTMHB6NUd2a3VxM1V1Qk9GekFEOHZnZy14S0ctNmloM01IMmdFSk1ORFRNYVRqYlQzVUNORW1NNVNkNnotVlZzZHp2YXdHSTFQd1hJUlJZendVcjhMUGdVRnNBdUhJd3BXdDZsZmR5QmdQQzVicndPU1BON2E1VFFDZw?oc=5</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -2976,30 +3177,35 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
+          <t>Ingredion купує британську Tate &amp; Lyle за 3,6 мільярда доларів Reuters</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>Незернові компоненти для комбікорму</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>США, Великобританія</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Незернові компоненти, Сільськогосподарська продукція</t>
         </is>
       </c>
-      <c r="K41" s="7" t="inlineStr">
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPSENOTklNOThXdGRJazBrYkROTnQyMGRPYmZCcmliR0VQOHRJNTBNT0w4ZkRxbkpWYzlOYzRxYzVoaGtfdU1aSUczbEdqeXlxRFZTVHZFcEM2dUFqblR6dEY0a0VmLTRIbnhKZUNwYTRZZXVuOFRydkhINzh1d05fN1dhVmFBdkl6bEZPd1JtQ0pWaTYxeVVranlHRkhZeGx5ekx2Um84OVVlUQ?oc=5</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3038,30 +3244,35 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
+          <t>Імпорт соєвого шроту в ЄС у сезоні 2025/26 впав на 6% порівняно з аналогічним періодом минулого року</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>Незернові компоненти для комбікорму</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>ЄС</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>Зернові, Незернові компоненти, Сільськогосподарська продукція</t>
         </is>
       </c>
-      <c r="K42" s="7" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE02blZGT2xuSllqVXFqQzVybUxLbGh2RU1vMFVhOXdzVlVaZjdDcXZDaXNzZkg2Y2FsdWlHQXllYVhtbnFGUk1LWVRxQkNWcWhnR2NQRDRzb0c0X1VtSGc?oc=5</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3100,30 +3311,35 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>Глобальна електронна комерція Китаю зупиняється, оскільки війна в Ірані підвищує витрати, зменшує попит Reuters</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Китай, Іран, глобально</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPMVVScGhlUWlOQl9KZk9nY2dHdV96RG9VWFVPSW9jaU80R3ZxQnlXTV84OVNldmtSQWpIZEFaNGhvYzljWVB1ajdWV01ueWVEY2JyaURkNnVxc0RBQl9NN2c5X2o1RWlGdzhiS1o2VVNnSzJ3a0lLYjQ3clRySG9pczJLLWg5WnFzOFZNbld1ZGZHYkFmNUFYVE9RazZxVTZXaDJrMU9aeDdxTUJqeXpKb1RVS01pdkI2OXM3NkcyNzNNZlJDU09aVkt2ai1UMTkxa3pWLQ?oc=5</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3162,26 +3378,31 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
+          <t>Індонезія конкретизує план посилення державного контролю над імпортом товарів Reuters</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Індонезія</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="7" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNTVVCMHVOS0NlVktpZkxVcWdZNWFRc2lEU0N4bFppRC12Wmp2TWRwYmx1ajVQRVdBUlZ3M1gtaUdSb1pQWkZmcjZtdFJNa3ZCS3hfQTRBaGZQLWxSMWdfZmNpUGVGSjJVRHdEYUpHNVhUWnJPZEdxaFlMUDdrSzZrX2RDZjVzRkJha0E2aEF5VVZaQnltdzRBQlBFcHRmeGVIRENvLW1taUhoclotRWREV0tGUDhxVnlLVE1Yd2RlWmZlYnhG?oc=5</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3220,30 +3441,35 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
+          <t>Саудівська Аравія знизила липневі ціни на нафту для Азії, хоча все ще на високому рівні за десятиліття Bloomberg</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Саудівська Аравія</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K45" s="7" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQbHA3UWRobWw3bm81a1hXbHhQMzhUQ3J0Tmo2amNPM25wNjZHeHdBTklWOU9EdkM3Sl9DVEFzU1hNT0c3YmhQQWgxRndMTmhlV002Y200V25meVE1SFp2WDBSRm10OW1mcEZTNGZ5cnBCRWZEVWMzUFJ5amdyemZMYl90T2t6RjJzRjJTX1hRM200dVZudHJFRWE0NmFQV1V0U0JSd0xDWjNZMjBucDVseW02TEQ?oc=5</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3282,30 +3508,35 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
+          <t>Готуйтеся до потоку нафти, як тільки Ормуз знову відкриє Bloomberg</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Іран</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K46" s="7" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPb0JKUkR1c1A5UUJJcE43MnViMHhGMVRiZm5Jd2pzRHdaYWZUaEJ1WmVocjNiMTJUaXRYa2RQeHFhQkRndjc5anVkQ1E1Y2N5Y1VrdVZDR251dHVKUUNqVUZBZldWYmJFd1pjMk5uSHpreGVfNHJFRl80X2lSYjJqc0EyZ0ExRkR2UHNpdzdEOHQzSG9DZGJNOTc5NnhiU3dkT0ZLVVRRTzBoWjFMNWZ5R1ZzTEZiN3ozY3c?oc=5</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3344,26 +3575,31 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
+          <t>Ізраїльські військові стверджують, що вони вразили цілі в західному та центральному Ірані Reuters</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQamkxU3JDUHZmTU8tdE05NUJXUFNyNm5WaWZJNFlLLUYxWjhyVXg1XzI2ZnRkZTFKV0IwVXBzR1JKdmVmX3BySVktZnlmVW5SeTE1Y0RaZW1rV2tuX3M4ZkMwVlA2SWcxck9ObkdPLTQweHNvRW53dnZhZlAwMHlvMGIwMHM0UG00UUxXdThMektUUHNBdFFlZXl1bjFNUGYyNmhzeS1mY04tZ25oMFAzM1l0eWE?oc=5</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3402,26 +3638,31 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
+          <t>India Inc підвищує ціни, зменшує упаковки, оскільки війна в Ірані скорочує маржу Reuters</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="7" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOVTFEdmNLQllMX21mYlVVMTNLMG9rbWVPczRLT0REWFB5QUtFMXpRNnJaVXZ4T2JObXBMMXV6OXI4V09hOHdGdVpKT0RIZF8yX1RBN09QanpnNWYzaEZrSjYzWno0MW53aGszamNEM2ctZGdkYVlCekFhLU0zUVQzVXhHZVpRdmFHbTRvbVFTaWNGV2xyN19PdVB0N1hLbEdlQ05xREdDYVNXdHJHejRJ?oc=5</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="M48" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3460,30 +3701,35 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>Ціни на нафту зросли на 1 долар після того, як Іран та Ізраїль заявили, що припинили атаки Reuters</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K49" s="7" t="inlineStr">
+      <c r="L49" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPNTlEbEFKMHpFNlgyeTJmTXIzWlNLWEI2aTV1OTFkTHgzejlqM2ZpQUM1NjZVaGo1WXk2UHV1TW9xMVhvWDVwcXVOdTBuaWp6aVBRMjBFSHRBUVBNREpHblcwNFNILW52TmhRT1gtaFVaZTJJWjdWQmwyV1A1SDBFY05RRzZxQkRQV3YzbVZEX2tWQ1haMW9CLTBRVko5YWx5VHUwSw?oc=5</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3522,30 +3768,35 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
+          <t>Міжнародні авіакомпанії знизили прогноз прибутку на 2026 рік через паливний шок через війну в Ірані Reuters</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>глобально</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
+      <c r="L50" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQenE5amZ2NmVSM2gzMXBWVjczMDdsZnRreUZObWlzUGJ2YVpBeU45cTNOdmt2Z1lOc1MtcmZqV2JSZ1RwaktBUzYyTDcwZVRjYnhiWk9xX2hQc3QxMUJ3NjVacWF2MTdwZ2hfOFozZEh3NzdyQWpza2xGRVNIYzAxV3hKaTJlM2dmTGxUdWRuR1RuaS1od2pWcEFpRXh6Tk5FV2lycE1Na2FaSjFlNlVGRDF6dEVfa09iZHN5dDhGTDFrSWM?oc=5</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="M50" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3584,30 +3835,35 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>Підтверджено другий випадок хробака в Техасі, оскільки побоювання спалаху зростають Reuters</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
           <t>здоров'я_біобезпека</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>Ветпрепарати</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>Ветпрепарати</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOblFxdFc0MEJ5OVd2VXZpQm5MMEhRQzlwS2lWb042ZGx0SFRTb1o3NnZnRjU5STNPR3ZpMk9tQi03MXVjbFBOSWlSeEVLQ0NDWkZLek9ZWGVNVjV5YzVVWmpaNUdWYlZfSlFDYjd3VlRzcVdDZTZ0UVdyWEc0alFVZEtGOVd6Z25fSENsLWdUV3FIR2lsR1Fxd0RFYm5iSEhGbVNyM3NDMl9yWXN2QVhhWWVhZUlmRmpxZmZuRWdLbGF0R1F1UUkzOUdR?oc=5</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3646,30 +3902,35 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
+          <t>Embraer бачить, що авіакомпанії відкладають рішення щодо варіантів купівлі літаків через війну в Ірані Reuters</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Іран</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>Логістика, Обладнання</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr">
+      <c r="L52" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNVFQ3d19Vc0w5bmZneWpXbi1QMldBcm5BQkxrbG5HWGYxVDZ4QkVTZ1pzRVNnUTNGTWVFY09ZRTJpbDh2UjkxVzVxeDRXZ2toMllLeUNKbXk1a2VtWXIwaE5rc1pWREl1QkNwTUgwUS1WUEdneExFYWdxMG9zWkF5NU45b1J6Q05WOWxESzMtY0xoaC1KOE9HNTNsSUpRam9EZHBNcFlIcEQ3LVJBOFZMWnp4OWE1NkdCX1VKVjBMcnU2U3lhVWlEOVRGU3A?oc=5</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3708,30 +3969,35 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
+          <t>Удари США та Ірану, страхи Уолл-стріт, позов Paramount і Кабо-Верде Reuters</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>США, Іран</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="L53" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPcEhkXzdJbXZFNTY5ak41UEx0cjdaanRaZXNJR2lHd1Q5Mld3dEdJQlFtTm43VXhDcFZQWTVZWEdzR2lZMXloVkNkMFIxSWJ4QTRRV3JxYkpGaER1UExpZ0xCSlZNY3NaUHktdS1yQmJrYjZkZWdpU0JPSWVUdThrcHNfNEN1clVLRUFtYVo3Rko2NmNiaktfZGhMb2FMZ0QtMTAxelhqSy1KczQ?oc=5</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="M53" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3770,26 +4036,31 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
+          <t>Закриття кордону з гвинтами сприяє буму виробництва яловичини в Мексиці, похмуро в Техасі Reuters</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>Покупні корми тваринництво</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Мексика, США</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="7" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOdE5LM1VqUi0yQjIyc1ZaajRpcV9vak5BWkh6LUMzVHFmRUFtMHNubEJTRkh1OTlOWk5KS3FqNFZvOW90OERycHE5WVN5cXFIbVo5bVp5QkttYU1jRUJkRm1tYXQ4dXVWQkhwLTlQU1MxRHVrSlY3elAxM0VHb3RXOExtNGxIYW44a0xCcUtNMTdhRW9mdGJnQlpvMXpfQkZFdUZyWUdrTUZZQkRNQnNz?oc=5</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="M54" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3828,30 +4099,35 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
+          <t>Росія Сєчін каже, що американські компанії виграють від закриття Ормузької протоки Reuters</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Іран, США</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K55" s="7" t="inlineStr">
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPSHJyOUJ0WVpCMVZ2MFNmNWEtQ1JuZW1LUW5obFNZZTlEZDBmcWE3S3ZYYXI0Q0Y5MHJLNjdGSjI1RnVRYmdtdmtqWGFIWmRINy1RdWMzdGMxTEROWENRQnJlMUxma2FkTHVNN1BDLW83QjdWWHhhdG9nZ3ktU1dGQk5KMFFyR09wZXM4bHhXSGxnWFZEMUJkb3BoRDNkc3FjUW5NODJyR2tRZlB5Q1ltN3RUcjY?oc=5</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3890,30 +4166,35 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
+          <t>Іран, здається, сміливий результатом, і його лідери можуть відчути, що апетит Трампа до ризику низький.</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="J56" s="5" t="inlineStr">
         <is>
           <t>Іран</t>
         </is>
       </c>
-      <c r="J56" s="5" t="inlineStr">
+      <c r="K56" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="L56" s="7" t="inlineStr">
         <is>
           <t>https://www.bbc.com/news/articles/cp8lm75186lo?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
+      <c r="M56" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -3952,30 +4233,35 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
+          <t>Пентагон назвав технічного гіганта Alibaba та виробника електромобілів BYD підтримкою китайських військових AP News</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="J57" s="5" t="inlineStr">
         <is>
           <t>США, Китай</t>
         </is>
       </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="K57" s="5" t="inlineStr">
         <is>
           <t>Обладнання, Технології</t>
         </is>
       </c>
-      <c r="K57" s="7" t="inlineStr">
+      <c r="L57" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQVXo0VVg0a2pPM2Z2VS15eXZET2tCTVp1Z1F4RHpRTFFiMUx3dWdlNFFJcjg5czJLT0tKMlg5LUFERkc2MUFHd25ISHdCTTZULTIwLWRXTjlFUldoZHNCbVFkcEQxNnhyaHJtbFdTbVlxSWlLXzZHOXVqSE9BenFmTTBrdTZnRGZyZW5TWHZMclpWb0YtRVNteWFiZ0NFM1VPd0FiR0NfNlNyaGtBYlE?oc=5</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="M57" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4014,26 +4300,31 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
+          <t>Біля узбережжя Нікарагуа формується тропічний шторм «Крістіна», повідомляють синоптики AP News</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
           <t>погода_клімат</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>Нікарагуа</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="7" t="inlineStr">
+      <c r="K58" s="5" t="inlineStr"/>
+      <c r="L58" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNTkFVdktmNkVVMUFQZ29EOW83andPbmxzUU4ya1NXUy1HWHlxY3gzakIzQW9wQW12NFNsTjhGNVoyaTBuLTR1U0sxVmhXVDNJa3JkOUNMOGY1SWk3MmJnZHU1QUlpb2RmYld6ajlhUTFnVXJPTFk5SmJXUExsNkNVNVdDNThxcUEzTkZ5bHYtRzNNTGtDaV8yY2ZvNFppemM4T1ZnN0FrR1JVWDFqLU1mOUJmMFpNMWNI?oc=5</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="M58" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4072,30 +4363,35 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
+          <t>Українські страйки викликали пожежі на нафтових об'єктах у Росії та Криму AP News</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>Росія, Крим</t>
         </is>
       </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K59" s="7" t="inlineStr">
+      <c r="L59" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOUnplM0s0OTg5QUQxamR3Nnhia3ZkdUdtc3pWcGxySHFybHJWdTh0MWItdmV3Z1NBSUQ4VkRpaUV1MEFSQzNHMnlWZG9fMVBZaXBOQXRRX3N3YVhTM2VsVmdIQWo0dlI1SWRVQXJHeDRKRkZPZDB1T0xxcms1V0pxMVBxR2xCU2huQlo5UThENmxteklXdWRNXw?oc=5</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="M59" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4134,26 +4430,31 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
+          <t>Популістська політика Prabowo спричиняє «закрутку» на індонезійських ринках Reuters</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
         <is>
           <t>Індонезія</t>
         </is>
       </c>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="7" t="inlineStr">
+      <c r="K60" s="5" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNSW56ZHNjVnktdXYzcUNCalV1MDNVVHY0cDhNRG9ZTGVLRWlYb2lOMm1BWWgtMzdIX1ltTHd6T3ZvaUpXNHo1RTBKYkdLN1BLbU1sT1BaSW9OQU52cjR4S0x5MFFuTXNyU0luQzFpcmtLWVhNNWV0ZGtHNzZzNHlqblBpLV9GZUQwLVJqUjgxSkl4TXd2UDFqdmtUdGRoRTBpeURnWHVIbGJURk9VTTREXy0yTi1ScDIx?oc=5</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr">
+      <c r="M60" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4192,30 +4493,35 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
+          <t>Збройні сили США вивели з ладу порожній нафтовий танкер в Оманській затоці в понеділок після того, як він намагався припливти до іранського порту, порушуючи блокаду Ірану, повідомила армія США. Центральне командування повідомило в дописі на X, що M/T Marivex…</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>Іран, США</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K61" s="7" t="inlineStr">
+      <c r="L61" s="7" t="inlineStr">
         <is>
           <t>https://www.marinelink.com/news/us-disables-tanker-indian-crew-safe-fire-540062</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="M61" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4254,30 +4560,35 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
+          <t>Кинувши виклик Трампу короткою боротьбою з Іраном, Ізраїль прагне вплинути на мирні переговори Reuters</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>Ізраїль, Іран, США</t>
         </is>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K62" s="7" t="inlineStr">
+      <c r="L62" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQTmtRMjRxTjh5TTVpTlNkblM0VlFZemNDUHlvR01vT0lYYVd1M3JWTWVlVy1BZFVhTHNtdjY1cjM3WjBIanNzR1l5eGhEMnhFbTR0WlRDdmxyZzYwTjJxNmVxNkxQYU0zQzdzN0FDRUxiMUZYNFgxM3RxTHpqQkhMS0JrVkJmV2huRTI0LV9TTDZ0VUdUVTZzVVBPem1UR3JmR1U4MXN6aWhHWU9kOWFlVldzaUZPVXRaT2ZMUHY1V1pENm11aWViTFpYQVZRQQ?oc=5</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr">
+      <c r="M62" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4316,30 +4627,35 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>Збої в морському судноплавстві через Ормузьку протоку змінюють глобальні потоки торгівлі нафтою таким чином, що може загрожувати тривалим зниженням потреби в танкерах, навіть якщо альтернативні маршрути постачання частково компенсують менші обсяги морських перевезень, збільшуючи попит на тонно-милі, вважають експерти галузі. Рівень нафти на воді, барометр для вимог танкерів, впав. У квітні вони були...</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="J63" s="5" t="inlineStr">
         <is>
           <t>світ</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="K63" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K63" s="7" t="inlineStr">
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>https://www.hellenicshippingnews.com/strait-of-hormuz-disruption-threatens-extended-decline-in-global-tanker-demand/</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="M63" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4378,26 +4694,31 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
+          <t>Індекс перевезення насипних вантажів Балтійської біржі, який відстежує ставки на судна, що перевозять насипні вантажі, знизився сьому поспіль у понеділок, впавши приблизно на 2,2% до найнижчого рівня з 5 травня на рівні 2916 пунктів під тиском більших сегментів суден. Індекс capesize, який зазвичай транспортує вантажі вагою 150 000 тонн, включаючи залізну руду та вугілля, ...</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr">
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>Метали, Паливо</t>
         </is>
       </c>
-      <c r="K64" s="7" t="inlineStr">
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>https://www.hellenicshippingnews.com/baltic-dry-index-at-over-1-month-low/</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr">
+      <c r="M64" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4436,26 +4757,31 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
+          <t>Зеленський каже, що мав «позитивну» розмову з Віткоффом і Кушнером Reuters</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>НМА</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="J65" s="5" t="inlineStr">
         <is>
           <t>Україна, США</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr"/>
-      <c r="K65" s="7" t="inlineStr">
+      <c r="K65" s="5" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOb1h4RXpXa1N5Y1lwUzlYTWlxMUcxUy1SelEydmRwNmdTZ3BUSkZtYm10ZXlqVncxSlAzVUpURHlNQnhHcFR1SmloakRmMGdoV0JHYWF5b2Z0SjJ6RTdGejEzODA4SzcwbktTbGRLSUZmVGtVekRBcjhVWl8zR0h3RWt0Q25sNVA3cVFMbnIwOHN4NFhUbEptM0tfSkVhSXhfaFZwNkJjZlNBMnRtaWQzUlpCZERwcnpHS3NtaUFHZw?oc=5</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="M65" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4494,26 +4820,31 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
+          <t>Казначейські облігації падають через дані про робочі місця, напруга в Ірані. Підвищення ставок на паливо. Bloomberg</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J66" s="5" t="inlineStr"/>
-      <c r="K66" s="7" t="inlineStr">
+      <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxNb1Z5VXh3OTNRNTBKRXJ5T19nOGFNTDF5ZWc4N3VmYlFieXBiLW45aXozS0pIX3hvak4tNmdieUtZa2M3UmllMm03aXJ6b0JBRXh2MERLNDVCYnQxYzlrYkpjLVluMHExSzNOV2t3SkZTUXNTSjVyUkkzQmt1Q09JMDRMT2RTbDBBVkFQUDRjTm43dGVfSHIzTXN2cXRocGpTNjF5NFcwT1ludGp2anpjU01VVQ?oc=5</t>
         </is>
       </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="M66" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4552,26 +4883,31 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
+          <t>Вперше з моменту початку хиткого перемир'я два місяці тому Ізраїль та Іран обмінялися ракетними ударами.</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>Іран, Ізраїль</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr"/>
-      <c r="K67" s="7" t="inlineStr">
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr">
         <is>
           <t>https://www.bbc.com/news/videos/ckg8nke01g5o?at_medium=RSS&amp;at_campaign=rss</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="M67" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4610,26 +4946,31 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
+          <t>Міністерство юстиції США все частіше звертається до Закону про неправдиві претензії, щоб переслідувати компанії, звинувачених в ухиленні від сплати митних зборів. Ця тенденція, на думку юридичних експертів, швидше за все, прискориться, оскільки тарифи залишаються високими, а викривачі стають активнішими. Олександр М. Оуенс, партнер компанії Pietragallo Gordon Alfano Bosick &amp; Raspanti LLP у Філадельфії, який представляє інтереси інформаторів і компаній у справах щодо неправдивих позовів, сказав, що боротьба з шахрайством на митниці розвинулась із нішевої сфери державного контролю.</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J68" s="5" t="inlineStr"/>
-      <c r="K68" s="7" t="inlineStr">
+      <c r="K68" s="5" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/customs-fraud-cases-surge-as-whistleblowers-target-tariff-evasion</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="M68" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4668,30 +5009,35 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
+          <t>Збройні сили США вивели з ладу танкер, пов’язаний з тіньовим флотом Ірану, в Оманській затоці в понеділок, ставши сьомим комерційним судном, заблокованим після того, як Вашингтон запровадив морську блокаду...</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>США, Іран</t>
         </is>
       </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="K69" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K69" s="7" t="inlineStr">
+      <c r="L69" s="7" t="inlineStr">
         <is>
           <t>https://gcaptain.com/u-s-forces-disable-sanctioned-shadow-fleet-tanker-bound-for-iran/</t>
         </is>
       </c>
-      <c r="L69" s="5" t="inlineStr">
+      <c r="M69" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4730,30 +5076,35 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
+          <t>Ціни на добрива в США впали до рівня, який був останнім часом перед війною в Ірані Bloomberg</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="J70" s="5" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="K70" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="K70" s="7" t="inlineStr">
+      <c r="L70" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNTFp0Wi1meUV2VEVHTUhrZkFNU2VqeWxSU0w3dFp4c2lvUGFEWTVReDhRcVZiNHBJcnV1NGI2YTNoTG9Fa0ZJTmlReUo1QlFFdV9yY0ZXZ3UzNEk4UmRrUUJwYlJKUndvcEVteVZma3ZpN2o3UGxPS0xhNWs2eERfcE5QSE40S3c4Vm95d3RMRnA0NEF4Vy0ybmVUaldJWHc1OGNKZTVZQVNiNTdmNjRuWQ?oc=5</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="M70" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4792,30 +5143,35 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
+          <t>Культові антикварні автомобілі Куби простоюють, оскільки енергетична блокада США поглиблює паливну кризу AP News</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="J71" s="5" t="inlineStr">
         <is>
           <t>Куба</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="K71" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K71" s="7" t="inlineStr">
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPandaN1JueDBlbjdlakxvZjlXRzk4aVdSSG9McUh1T2FqUUNDUFQwM3ltSTczUE9nZmtNcmpnZFFHc2I0UXk3OEZqWHR4U2VxZlFqdnE0UGdsbm1DUGdCc3pkTDNwS19WMlhCXzRmVWtjeUV1VFB1RzVRdnQ2ZWhVM0kwSFI2eVlvdkllcGZSZGxwcWdWWnFrdC1pVQ?oc=5</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="M71" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4854,22 +5210,27 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
+          <t>Долар — найкращий вибір у новому глобальному режимі високих ставок, BMO каже Bloomberg</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="5" t="inlineStr"/>
-      <c r="K72" s="7" t="inlineStr">
+      <c r="K72" s="5" t="inlineStr"/>
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQb0NMVUdidEtsdWFrMFhDeVJPUzVPalNwS3JyOUJMS2VMYm9hcHVwUDlpRU5MZVRuM1JPVy1oQVgyQ2txdDc3RXp4MDN5c2h4T2Q5M3poWUtRX20wbXRzSjJlZTQxTll1UHFPSXFMd0w3WmptUXM3S2tGODAxWGY3bWJwQXMweWhPUjVRN2s3R2xMa2xPZ1huSDhGSEZuS0VWSUdPeXZ3QnhEYlBRanJIWjE2WQ?oc=5</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="M72" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4908,30 +5269,35 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
+          <t>Китайським покупцям пропонують іранську нафту зі знижками порівняно з травневою премією, оскільки попит з боку незалежних виробників Китаю останніми тижнями впав на тлі стрімкого зростання витрат на сировину, що негативно впливає на маржу нафтопереробки. Як повідомили Bloomberg у понеділок анонімні трейдери, які беруть участь у ринку, ціна Iranian Light з поставкою в Китай у липні була знижена до рівня 1 долар за барель до порівняння ICE Brent. Це можна порівняти з премією до 2 доларів за барель у попередні два місяці</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="J73" s="5" t="inlineStr">
         <is>
           <t>Іран, Китай</t>
         </is>
       </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="K73" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K73" s="7" t="inlineStr">
+      <c r="L73" s="7" t="inlineStr">
         <is>
           <t>https://oilprice.com/Latest-Energy-News/World-News/Weak-Chinese-Demand-Forces-Cuts-to-Iranian-Crude-Prices.html</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="M73" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -4970,26 +5336,31 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
+          <t>Очікується, що в червні обсяги контейнерного імпорту США знову зростуть порівняно з аналогічним періодом минулого року, оскільки роздрібні торговці прискорюють поставки перед потенційними змінами тарифів і зростанням транспортних витрат, але прогнозується, що обсяги...</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="J74" s="5" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J74" s="5" t="inlineStr"/>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="K74" s="5" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr">
         <is>
           <t>https://gcaptain.com/u-s-container-imports-get-temporary-boost-before-expected-slowdown/</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5028,30 +5399,35 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
+          <t>ФАО закликає відкрити торгівлю всіма сільськогосподарськими ресурсами та ефективним використанням добрив на тлі глобальних ризиків виробництва продуктів харчування Продовольча та сільськогосподарська організація</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="J75" s="5" t="inlineStr">
         <is>
           <t>Глобально</t>
         </is>
       </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="K75" s="5" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="K75" s="7" t="inlineStr">
+      <c r="L75" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNcEdwN0pOeXdPZnRCV0N0bFdnajJNSEVRQmw0UE9MQ3pyeWw0MTgtSEhnY3VaeWJOWWhCWVByT2duR3NocW5yQ1dyN3E4cUlrelE4ZDUxMDFrNEhzZmZkUEhaSHhPMERsam1HUkJyX0MtdDRHMjZwVHI2aXpnSmI0N0FVcmFMekdWZnJTdDk4eHpNN3BtMG9raHc2bEZNcjhzTUdveFdzVE9VSlhxejhRaXhXcS1ScFFPSmVFZWpSNjh3bzRuT21vT3pJQ1VRY2YxMlJGS1hOaVZkc19zMDBIVUozSQ?oc=5</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="M75" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5090,30 +5466,35 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
+          <t>Євросоюз дозволив військовим у Середземному морі, які беруть участь у операції IRINI (запобігання незаконним поставкам зброї до Лівії) перевіряти також танкери, які підозрюють у перевезенні російської нафти. Про це пише "GuildHall". Як заявила глава дипломатії ЄС Кая Каллас напередодні неформальної зустрічі міністрів оборони країн ЄС, операція IRINI змінила правила застосування сил. Огляди суден вже проводяться "для того, щоб обмежити можливості Росії фінансувати війну проти України за рахунок нафтових перевезень". "Йдеться про розширення практичного інструментарію ЄС проти російського тіньового флоту. Якщо раніше тиск здебільшого будувався навколо санкційних списків, страхування, портових обмежень та контролю окремих держав, то тепер Брюссель посилює військово-морський компонент", – пише видання "Caliber". Операція IRINI була започаткована Євросоюзом у 2020 році в Середземному морі з метою контролю за комерційними суднами та запобігання незаконним поставкам зброї до Лівії. Зараз її мандат фактично використовують і для боротьби з суднами, які підозрюються в обході нафтових санкцій проти Росії. Російський тіньовий флот включає танкери, які використовуються для перевезення нафти в обхід західних обмежень, часто через непрозорі схеми власності, зміну прапорів і маршрути через треті країни. "Рішення ЄС означає перехід від переважно санкційного тиску до більш прямого морського контролю за підозрілими перевезеннями. Ключове питання тепер полягає в тому, наскільки активно країни ЄС застосовуватимуть новий мандат і чи зможе він реально ускладнити роботу російських нафтових маршрутів", – говориться у публікації. Нагадаємо: Раніше повідомлялося, що Європейська комісія завершить роботу над новим, 21-м пакетом санкцій Євросоюзу проти Росії цього тижня та передасть його на затвердження у Раду ЄС. Зупинка російських криголамів біля норвезького порту Хоннінгсвог стали частиною арктичної судноплавної логістики Росії, але на тлі посилення санкцій є шанс, що надалі Норвегія припинить надання послуг цим суднам. Шведський суд визнав законним арешт вантажного судна Caffa в Балтійському морі та дозволив передати його Україні в межах розслідування вивезення зерна з окупованих Росією територій. Моніторингова група "Інституту Чорноморських стратегічних досліджень" повідомила, що у 2025 році з російських портів танкери з сирою нафтою виконали 2346 рейсів, найбільшу кількість, 1111 рейсів, вони здійснили з портів Росії на Балтійському морі. За рік вони перевезли значно більше 230 мільйонів тон.</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>ЄС, Росія, Середземне море</t>
         </is>
       </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K76" s="7" t="inlineStr">
+      <c r="L76" s="7" t="inlineStr">
         <is>
           <t>https://epravda.com.ua/biznes/yes-aktivnishe-zaluchatime-viyskoviy-flot-do-perevirok-tinovogo-flotu-822458/</t>
         </is>
       </c>
-      <c r="L76" s="5" t="inlineStr">
+      <c r="M76" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5152,26 +5533,31 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
+          <t>Індійсько-американська торговельна угода може бути завершена після завершення розслідування тарифів, повідомляє Reuters</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>Індія, США</t>
         </is>
       </c>
-      <c r="J77" s="5" t="inlineStr"/>
-      <c r="K77" s="7" t="inlineStr">
+      <c r="K77" s="5" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxNZFBDQ2VIMzNWQnpCdFo0N0F5NjhHVEJkb2xJMjBHdmo4OE1qZTlELXJFMnl6Mk1tYm9GZVc1T3BNcnpLWG4wUy1NTGd6eFVrS0VKYUpJd1JUSEZRaW1ldDRZSXVYbG5TYlljZFQzZHZwRjhjdERFaXZCS2lBRGxxOS15MDZwSGhiZko5RGZobHVYSTB1Rm5heWZuZTU3czBlTnBSbG1mNVBGaTNiOGNpcnU5U1p5NzJweTZ1aXhB?oc=5</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr">
+      <c r="M77" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5210,26 +5596,31 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
+          <t>Німеччина поглиблює енергетичні зв’язки з Канадою завдяки тимчасовій угоді про СПГ Reuters</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="J78" s="5" t="inlineStr">
         <is>
           <t>Німеччина, Канада</t>
         </is>
       </c>
-      <c r="J78" s="5" t="inlineStr"/>
-      <c r="K78" s="7" t="inlineStr">
+      <c r="K78" s="5" t="inlineStr"/>
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNXzN4Qm1WZ1ZaamxmeDBaMmJYUFc3TW9nbXJFZkJkWGZqaWk2WGdlcWU2aV9xVHRVMElPYXdJemZZdmk1NU5XWXJ0aVY1Vjdnb3A1Uk11U1ZjRURpemROTzVrWjRDUC1GU296M3l2NUw2ZmJBOTllU2JnWVhCazlob1IxTmNRWnY1ekw0MjYxVjlmQ25HSGdKRlNBcUtuTko0dVBzYkZTaGF0NUZlWVV6NTVR?oc=5</t>
         </is>
       </c>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5268,30 +5659,35 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
+          <t>Різке підвищення спотових ставок на контейнери на основних торгах зі сходу на захід підштовхнуло ціни на фрахт цього тижня до зростання, але новий аналіз показує, що останній сплеск є набагато більш незвичним для транстихоокеанського коридору, ніж для коридору Азія-Європа. За даними Sea-Intelligence, спотові ставки, виміряні Світовим індексом контейнерних перевезень (WCI), зафіксували винятково сильні тижневі прирости, що викликало запитання щодо того, чи останній рух ринку є надзвичайною подією чи більш знайомою закономірністю. Кон</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
         <is>
           <t>Міжнародні маршрути</t>
         </is>
       </c>
-      <c r="J79" s="5" t="inlineStr">
+      <c r="K79" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K79" s="7" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>https://theloadstar.com/near-record-transpac-spot-rate-surge-a-harbinger-of-instability-says-sea-intelligence/</t>
         </is>
       </c>
-      <c r="L79" s="5" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5330,30 +5726,35 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
+          <t>Індійська компанія BPCL повідомляє про закриття нафтопереробного заводу в Мумбаї в листопаді Reuters</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="J80" s="5" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="K80" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K80" s="7" t="inlineStr">
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOUDFubEV4dmNlOEwyaWpzU1N3VjdjdEVBWldLejhZRWhVenZDT2h4TlVHSF9FZTRTOGI2ckJFd1VKSms0VnE0WlBNV19sNDBYNXdXUEZiQ3JYSERablAwQkdDUXNicDZjbTgtb1JSYW14aE02c1JpM0xZUFlQMzZFbURsWVNYRDBsbndHSER1MUp1RnFwd2xrZ1FaNExkSjZ1NDFwcHNLYml6RlVlckxSYkJaMTNBVWR2RFE?oc=5</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5392,30 +5793,35 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
+          <t>Виробники чіпів заброньовані до 2028 року, інвестиції в центри обробки даних зростають, а вантажі, пов’язані зі штучним інтелектом, все частіше перевозять ширший ринок авіаперевезень. У той час як обсяги електронної комерції зменшуються, а попит на загальні вантажі залишається нерівномірним, поставки, пов’язані з напівпровідниками, серверами та інфраструктурою центрів обробки даних, генерують одне з найсильніших темпів зростання в галузі. «Залежно від того, з яким клієнтом або компанією ви спілкуєтеся, вони говорять про те, що їх забронюють до кінця наступного року, а деякі навіть...</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="J81" s="5" t="inlineStr">
         <is>
           <t>глобально</t>
         </is>
       </c>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="K81" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K81" s="7" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>https://theloadstar.com/booked-out-until-2028-the-ai-boom-is-now-air-cargos-growth-engine/</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="M81" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5454,26 +5860,31 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
+          <t>Трамп каже, що блокада Ірану залишається, і вимагає припинити стрілянину по Блумбергу</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="J82" s="5" t="inlineStr">
         <is>
           <t>Іран</t>
         </is>
       </c>
-      <c r="J82" s="5" t="inlineStr"/>
-      <c r="K82" s="7" t="inlineStr">
+      <c r="K82" s="5" t="inlineStr"/>
+      <c r="L82" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPTzVwbHpYR192dU90WFZjQVp4ZlpONDlVT0NhSlNCTTd5OUFQTGZMODdVdVVPQ0RkNEpHZTdrODh5cjZDTVVxVUFRbklMOWtxM2RyN0NtZHRsa091RlhIaGpiLWhicE53VGE1SW5LZjI2UUhxNmw5a1Y3R2dITjFwMGwyblpLOUJFbk02RmxoZWw3OUd0ajdzVXowSzFXR0xyajNaMEg3YjI5ZHJfbmZXa3h3?oc=5</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="M82" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5512,30 +5923,35 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
+          <t>Ціни на соєвий шрот у Китаї досягли багаторічного мінімуму УкрАгроКонсалт</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="I83" s="5" t="inlineStr">
         <is>
           <t>Незернові компоненти для комбікорму</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="J83" s="5" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="K83" s="5" t="inlineStr">
         <is>
           <t>Сільськогосподарська продукція</t>
         </is>
       </c>
-      <c r="K83" s="7" t="inlineStr">
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxObkpHaS1YT0cxWk1zbjZ0RHh1V0NBb0VWbDVoYWw1QVVpYkJySURKd05wOVJvR0dqXzNoX3hGenVZaUlpaEFmcmw1WFRqOGRucWI2OVY3WVdMWkpRSnRsYVdUN3A1SGpsTmZhUk5XNTQxUUVSaEFSeXRVWWVsajJZUTJiZw?oc=5</t>
         </is>
       </c>
-      <c r="L83" s="5" t="inlineStr">
+      <c r="M83" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5574,30 +5990,35 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
+          <t>Китай нарощує купівлю СПГ в очікуванні літньої спеки Bloomberg</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="J84" s="5" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="K84" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K84" s="7" t="inlineStr">
+      <c r="L84" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPdXcyV1JUWHdYOGlWRHJ5RmFpNjFfWk1SVWJQa21LNGs0SG1RZXlCTjdHMFBrTS0tbkpfX09KV2VIa1JqNGNaMG1QU2FxVDAtYWRNNHpUR09SSVpmMWhOSTBrb1p2VVhIWTY5Nnhya1FtUExuMjd2dUNmbEY2Y2hHdzF1VEFGWDZWVWVUV29aREFINHRiLXZ1QldCZldlYlVVd0hic29CNjFUamJRQUE?oc=5</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
+      <c r="M84" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5636,30 +6057,35 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
+          <t>Китайські нафтопереробники затримують проекти з поставками нафти на Близький Схід, порушує Reuters</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="I85" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>Китай, Близький Схід</t>
         </is>
       </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="K85" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K85" s="7" t="inlineStr">
+      <c r="L85" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOdkRzYlNYWUZlaG10bzE3OXNaVWtGMHhpaVo2Wnh1MmJEWVhPUGFZc2J6MmtqaDJaNnhpVk1tT0JDYy1hQ1gtX3BNWkp0a0NDYzlQMFpvenVwTk4tczhrQ3Zrc2JGYWJIVkpDbGdzcnA1TV8zZVp3aGJJWjAybThKcG9jWmJEZm0yVGdJY3lkTDhNRmFkU1BsaTl3djQ4bkwyZDUtV0xFNGFmbUJ0Uk5TODd3WDUwWlZkVnpsZzZn?oc=5</t>
         </is>
       </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="M85" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5698,30 +6124,35 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
+          <t>Опитування Reuters Reuters</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="K86" s="5" t="inlineStr">
         <is>
           <t>Технології</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr">
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxORVk2cmhBT0U4eXpwRnREVFNJQTBKLXVkbG9PckRVN3Q1VjlJNDNnZ2ZoM2xLaE5iZmlhZ3MzN1RHVTV5QlBTZTAtY3Z4TVE5NUpmZXBPa0VtTkZEa3pscWFLTlFpVFBHUEtfT2ZTSVVoVDBuQldHaERWVFVKdWVlRkJxdTM1M0ZYeGszQnc1d0hDSmFHMnBDMFM0RUpEaU56TVVQZU5CT1Vvbk15?oc=5</t>
         </is>
       </c>
-      <c r="L86" s="5" t="inlineStr">
+      <c r="M86" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5760,30 +6191,35 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
+          <t>Робітники посилять страйк на заводах Inpex Ichthys LNG після провалу переговорів Reuters</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
           <t>страйки_перебої</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="I87" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>Австралія</t>
         </is>
       </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="K87" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K87" s="7" t="inlineStr">
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQeXIxN1J4RUkzaURfbHRtd1pqWXdqTWU4cENjN2xuV3ZfRFRLTlpSbzBjZlRkTnlYWWlYeldJTGhIQWpiVmN6Q2xDOUViT3BtZG95dl9VRDQ2VFpmVnZRNnl3YXFiX2VSblRjMkV1ZWQ1cUVnRDhBaEw3QlY4dzJyWlVyeVBtLUdSb1ltZXl3T054Rm5IVW1KZTVLQ2NHRWdlZHVybmhvU3BFcFprczAxQjNYOG5OWEpobFpmNDEzcDFpdw?oc=5</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="M87" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5822,26 +6258,31 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
+          <t>Іноземні резерви Індонезії зазнають найдовшого падіння з 2018 року Bloomberg</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="I88" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>Індонезія</t>
         </is>
       </c>
-      <c r="J88" s="5" t="inlineStr"/>
-      <c r="K88" s="7" t="inlineStr">
+      <c r="K88" s="5" t="inlineStr"/>
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPQkZoMVFRSGFkWWc1dXp2eXZnaEpqa2NwZTVodVRJSUtIZXlsU1lpVjVIdlNiZjN6alZNNkxONG9GRlF0MFpVWkhMSE1qbkZxWi1HSjRwNmN3V2h1eUxMTHc5TDBkTGc0VGtkNWpiOVNJcm1ibUkyWlpXdFprNTlrUzhfOHdJLWNzaXJGM3FJZlZYZzk3dTk1d1VEeks4STlySjlac0NjZ282TU0tbzUyQmNqcGFKZ2NyX1Nad2RMYw?oc=5</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="M88" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5880,26 +6321,31 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
+          <t>Акції відновлюються, нафта знижується, оскільки Іран та Ізраїль сигналізують про паузу Reuters</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr"/>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr"/>
+      <c r="K89" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K89" s="7" t="inlineStr">
+      <c r="L89" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQeFRCX29KbXlhVmEwNV9yUFRNQjZUcXFKVFlubUFGNkdrRDd0Z0ZwY3RUTFlXVmg5N1ppXzFHZ2Niai01RmtXOW1lY0pDRFI0VXJTZF9jeWFqSnZVRjREWDVfM21yMHNTR2NGcDcyb2NKczljNGNuRHJua1BlUkp0cUg2UQ?oc=5</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="M89" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -5938,30 +6384,35 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
+          <t>Генеральний директор LATAM бачить додаткові скорочення пропускної здатності авіакомпаній, якщо паливний шок триватиме Reuters</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H90" s="5" t="inlineStr">
+      <c r="I90" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>Латинська Америка</t>
         </is>
       </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="K90" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K90" s="7" t="inlineStr">
+      <c r="L90" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNUXI5eV8xS2g0ZExfSXRiYk9LWGpSM19ocTkxUjhPeDdESTZvQnVXR0FxNEkxQkgzYThFaWlqQzNwWW9oMF9pVThvYm9oaUFxdEJHVmZHVE9kM1NxS3JwYmR0U01yempfblVMQXh6TkZySTl4U281Wmx2Skc3dE9NdGJockR6WnNKUVE3UkZWd0Z4amZDdWFtTkFFT2JDZVl2aW9PN0FTTjZ3RFZYZnc?oc=5</t>
         </is>
       </c>
-      <c r="L90" s="5" t="inlineStr">
+      <c r="M90" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6000,30 +6451,35 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
+          <t>Goldman Sachs більше не очікує зниження процентної ставки ФРС цього року Bloomberg</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="I91" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="J91" s="5" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J91" s="5" t="inlineStr">
+      <c r="K91" s="5" t="inlineStr">
         <is>
           <t>Фінанси</t>
         </is>
       </c>
-      <c r="K91" s="7" t="inlineStr">
+      <c r="L91" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxNdXlxdWZpaFEwSXhDRFh6ZV94ME14X1JHRFI2MGoxODRmT2dob24xQXhheW00SDBITTRKTHU2blZDeU9jQ2hPSVJWb3EwR1VuSGQ1ekpiRzFkbWNZMUFUcm03dXg0Z2lxcEIyWjNZdnZjdEMxODB1NGlKajY4NmJ3MHRSMWRfTXBsd0J6MVN5Njd0eEdQOHZTeExvcUNjbUVlbTNLdVpKQzZObG8zUzhqYkp6VFltMjlqRG9HM19ZTFY?oc=5</t>
         </is>
       </c>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="M91" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6062,30 +6518,35 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
+          <t>ОПЕК+ погоджується ще одне символічне збільшення квоти на липень Bloomberg</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H92" s="5" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="J92" s="5" t="inlineStr">
         <is>
           <t>OPEC+</t>
         </is>
       </c>
-      <c r="J92" s="5" t="inlineStr">
+      <c r="K92" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K92" s="7" t="inlineStr">
+      <c r="L92" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPM0s3c0wwaVk3dDBQaDVsOHdFMW4xNjhjYmkzLUlvcXFLU29pOFdHTWdycHBnRlJVdkZxWVRoazd5WlktQXpUWjc4cXc1RC0zc2lJOThHa3RHY29zUExaWXF2YmVXdWY4V3NtYnJSQVhSOGQyMlR3QWMwRi1XaXhPZlRRdnE2dzQxeXptd01YWEkwOWpkRklhTGNzNW5RU1NNZW1jM3RMUjNXVTNRVVZOSV9CQQ?oc=5</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr">
+      <c r="M92" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6124,30 +6585,35 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
+          <t>Більшість ринків Перської затоки закінчуються зниженням на тлі нової ескалації США та Ірану Reuters</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="J93" s="5" t="inlineStr">
         <is>
           <t>США, Іран, Перська затока</t>
         </is>
       </c>
-      <c r="J93" s="5" t="inlineStr">
+      <c r="K93" s="5" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K93" s="7" t="inlineStr">
+      <c r="L93" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNRDlFSUN2aW9WY0xORWtTOEo2RlhOTkJxaVVNZUV2YmNDRDR2LWhvSU9JbEx1LW1hQWlpaG5KVEFmMktnVFBOOTVfX0pjc1dweS00NG94UG0xVEVBcTFiSGh1N3JTeWt2SE1yOWkzdS1FZE9GNW1mN00zYVNOS0tSYzF4YWZ1T1dmWnZNUE9lMS12aGYtaXJQM2lBaHZGaXpxR1V3UTVDdmFmMnR3Q0QtcQ?oc=5</t>
         </is>
       </c>
-      <c r="L93" s="5" t="inlineStr">
+      <c r="M93" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6186,26 +6652,31 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
+          <t>Україна заявила, що безпілотник вдарив по заводу з виробництва ядерного палива поблизу Чорнобиля Bloomberg</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H94" s="5" t="inlineStr">
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I94" s="5" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
-      <c r="J94" s="5" t="inlineStr"/>
-      <c r="K94" s="7" t="inlineStr">
+      <c r="K94" s="5" t="inlineStr"/>
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQTEo0TzFKMXBHem4ydXc5UjZEbVZBNmRWMFdfX0ZZWVhMeXhhbm56emJxYkhiTWRqc1ZsTWUwS2w3amhJMU5ZeXFpd1pKN2ZMdDF3MWl0Z1lSVTJ0MDRwNzVManA0UXRRX01vd1dBTW5GTDJ4cXJ0NUlRN21FMWdJTkhzdzQwblZnNEdyNVpZRGF6a0ZITFVoeVhTOGdsY2E2eVZHcFd0STcxRUdHa2Jz?oc=5</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="M94" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6244,22 +6715,27 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
+          <t>Пентагідрат сульфату міді в світі - аналіз ринку, прогноз, розмір, тенденції та інформація IndexBox</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>Добавки та спеції</t>
         </is>
       </c>
-      <c r="I95" s="5" t="inlineStr"/>
       <c r="J95" s="5" t="inlineStr"/>
-      <c r="K95" s="7" t="inlineStr">
+      <c r="K95" s="5" t="inlineStr"/>
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOZmE5S21kSlp2TXd5Yl85Ni14aXZMcVNHOVgzXy1sS3hHcXhrTG5wTlJRQlYzcVhsdDA4VWt5alNFUkVNOWhNbnM1MGJGRG04VVRGeFVEcURDWTNuN1lISlRrNWFPa0l6dktvaFVpZU5WWUxzLUdXMXRQTl9obzItVEdRc0NNSjFXT3pMbzhJSUU4aUNZeXVKTVRYakdqTnpqOGh2MlU4bWtnVGVwOE1YQXNzY24wQ3Vfam9JZXZkLUpCc2pROENOWlpKN18tZi12RE9GU2FERG5pWGhiR2V5R3VmV0NKeGxpN2tjVExR?oc=5</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="M95" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6298,30 +6774,35 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
+          <t>Відстрочка замовлення на реактивні літаки через війну в Ірані обійдеться близькосхідним перевізникам дорого, вважає віце-президент IATA Reuters</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H96" s="5" t="inlineStr">
+      <c r="I96" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>Близький Схід</t>
         </is>
       </c>
-      <c r="J96" s="5" t="inlineStr">
+      <c r="K96" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K96" s="7" t="inlineStr">
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPR2hDc1JBd0IwRnMwSXAzMzBIdmxac0FnZ1Vhby1ucmxXcml1QTJ5ODM4V3A3MEEyS2RubXdlNXQ3UmVWNEQ2aGJVcWxpZHdReGZDRmFfRVhVX0FXQnBaUENJbnVXbThiR2c1UnJEZ1FFVHQ1bHFxbHJLS0F4ck01MnV0bkk5ZkZnSzZGc2lvS0NPcGdiUm9haEJHZUtMdlJfR3JDQUxKZDRnX3FSeWNKR1RRSHlNc1o2R1I2NWt5TTVKTFRuMVdlRXVzdklfRFYwT0NnYWtYVG1OQQ?oc=5</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="M96" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6360,30 +6841,35 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
+          <t>Нерозумно для близькосхідних перевізників відкладати поставки через війну, каже Reuters віце-президент авіакомпаній</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H97" s="5" t="inlineStr">
+      <c r="I97" s="5" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I97" s="5" t="inlineStr">
+      <c r="J97" s="5" t="inlineStr">
         <is>
           <t>Близький Схід</t>
         </is>
       </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="K97" s="5" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K97" s="7" t="inlineStr">
+      <c r="L97" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPWGlkemRMYlJXMEdKaGxQWGcwWmFNMENxcUxHSUpsS2V4dFBVelRBeUlqa0pPRzR6NTdFNkY1ZURoMGVIclF4Y1UwTHF6SVd4a3RWWnczWnhEQWZaY0ZkM1ZIM0dnRTBuWF9mQU5WbXBxMHJNajRBeUZfZUhzUUs1TE5oLVBEUG9wOXd0N19UTkI3R2RjSmxFSGlOMmozc3pJanJOUkZTUVlrMFVEbkpGQlVvbExpa0NVSlZFY2RIMmlwelQ0TmNj?oc=5</t>
         </is>
       </c>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="M97" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6422,30 +6908,35 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
+          <t>Air New Zealand планує збільшити витрати на пальне до 2027 року Reuters</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="I98" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I98" s="5" t="inlineStr">
+      <c r="J98" s="5" t="inlineStr">
         <is>
           <t>Нова Зеландія</t>
         </is>
       </c>
-      <c r="J98" s="5" t="inlineStr">
+      <c r="K98" s="5" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K98" s="7" t="inlineStr">
+      <c r="L98" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxiR2M3aXdFeldjZnBPeFBiLUhHYTU4dVR1ZlU3MUZ4RnpqTVdyTTZ1OG1kdTNQbDdtZm0zbHgxMWdlVVdBQlB4R0pCa3BEWjMxSXF4X1RtRE5xSzM5TzJob3MtSVlpcVJVeTU3WkRad3RkTmhramZ0M2J1MlZsU3dNSjNaUU52c0kyVDZ2S0podUlsdlNvZ3Z0NGFIaWRQUk9hZ2E3a25ybGJjV0dnSkh6MEE?oc=5</t>
         </is>
       </c>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="M98" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6484,26 +6975,31 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
+          <t>На гравців LNG чекає ще один шок Bloomberg</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I99" s="5" t="inlineStr">
+      <c r="J99" s="5" t="inlineStr">
         <is>
           <t>глобально</t>
         </is>
       </c>
-      <c r="J99" s="5" t="inlineStr"/>
-      <c r="K99" s="7" t="inlineStr">
+      <c r="K99" s="5" t="inlineStr"/>
+      <c r="L99" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNajRSM0J1dVlDbWlIczR3RWZhWUUzQ2ljNTNmc3Jab29ldWFKclBXTE9MNU5iZERCdWJiZWZoOWdLSjFTa0I4enB2TzRNREg0aEtoNGphU3gtb2ZWLVRRTnpjUi1zWDBVcVp2SWtSNjEyeDBqbkxjWEctSmZfdV9oeEVzeEF0NnFpVU5vZ3ZNWjdXYnd5Z1lQaXpzYUtvNDJnSVpSRGVsU3d6ZkNuYmo0dm5XVkJxeHc?oc=5</t>
         </is>
       </c>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="M99" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6542,30 +7038,35 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
+          <t>Фокус: Китайські інвестори, які стоять за нікелевим бумом в Індонезії, шукають альтернативи, оскільки зміни політики кусають Reuters</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>Вит.матеріали/МШП</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="J100" s="5" t="inlineStr">
         <is>
           <t>Індонезія, Китай</t>
         </is>
       </c>
-      <c r="J100" s="5" t="inlineStr">
+      <c r="K100" s="5" t="inlineStr">
         <is>
           <t>Метали</t>
         </is>
       </c>
-      <c r="K100" s="7" t="inlineStr">
+      <c r="L100" s="7" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOZnlveHhGQnUxcW9xX2ZYZktkdWpZVW1PclpFRVVnTjFMU3ZOWm1kaGJNMFc1a1lkWDQxYXhndU1hdGJuUDBPT1lEX1VEUF8zdDh0SktYZ0s1UzVhYU1zTkVMYnJzcUtHZTIwV3NrcVN1QmtZRU5fb0VjY0dxbzBSRXNrVnI4dkNoVmk2blNiWnRfZUJUb1Nhc3Fja1JWSWEwbUZGRVpFX3MtR3N2clRMSndSb2NzZGdQVFRNU2hMY0hYQ1FfMTAw?oc=5</t>
         </is>
       </c>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="M100" s="5" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6604,26 +7105,31 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
+          <t>Високі витрати на пальне призводять до банкрутства та консолідації авіакомпаній, каже Reuters керівник галузі</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr"/>
-      <c r="J101" s="8" t="inlineStr">
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K101" s="10" t="inlineStr">
+      <c r="L101" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNM3h5cWZHY2VFM09zSHhJdTVKRWdqRmMxemVQNUtsYzVJXzVHM1dkT1lyR0ZaX2VBbzd2MGlIelhCYVFNUVJQRVI2a2FfOThRaGZZX19rTFY4ZVdBcHVlQWtid192VUVvM3kxenJfOWNvOW1YSVI4TFp3b3A3M01HTm5kZ0IyNS0tMnlyZHpldmNxTUxnRXdrNGdycHMxY0tZVGFwZGxFcmxzR1UtX2lEVUR3a1haVXJYWlNiTWZXRGFScTd3VlFvZHVsYkM1YnRDWjZV?oc=5</t>
         </is>
       </c>
-      <c r="L101" s="8" t="inlineStr">
+      <c r="M101" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6662,30 +7168,35 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
+          <t>Вбивства сталися після того, як Іран попередив про «нищівні удари», якщо ізраїльські атаки продовжаться в Лівані, зокрема на півдні.</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr">
+      <c r="I102" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="J102" s="8" t="inlineStr">
         <is>
           <t>Ліван, Ізраїль</t>
         </is>
       </c>
-      <c r="J102" s="8" t="inlineStr">
+      <c r="K102" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K102" s="10" t="inlineStr">
+      <c r="L102" s="10" t="inlineStr">
         <is>
           <t>https://www.aljazeera.com/news/2026/6/9/israel-kills-14-in-southern-lebanon-after-trading-fire-with-iran?traffic_source=rss</t>
         </is>
       </c>
-      <c r="L102" s="8" t="inlineStr">
+      <c r="M102" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6724,30 +7235,35 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
+          <t>Soybean Prices in Ukraine are Rising: Exporters Compete with Processors Новини аграрного бізнесу</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H103" s="8" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>Незернові компоненти для комбікорму</t>
         </is>
       </c>
-      <c r="I103" s="8" t="inlineStr">
+      <c r="J103" s="8" t="inlineStr">
         <is>
           <t>Україна</t>
         </is>
       </c>
-      <c r="J103" s="8" t="inlineStr">
+      <c r="K103" s="8" t="inlineStr">
         <is>
           <t>Незернові компоненти</t>
         </is>
       </c>
-      <c r="K103" s="10" t="inlineStr">
+      <c r="L103" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPNDNFSldzXzl1eWpEN2ZkVW04WGZrUzlYTHYwd1UxaE44ZUtFbVFJZ0x5NVVqb2k5NVFrZDVUZ3dNX2RfM2JHZkdESHBGbFlsZnotN0JMaHNEeHpxVy1ueTREckhRcGxtMUx2b2pIR29WRlluODdBanNMWmptaTdibXdoR1k4cXJSRWlWajlsbWZwZ1J6aHFOU3VWdGN5RTI2?oc=5</t>
         </is>
       </c>
-      <c r="L103" s="8" t="inlineStr">
+      <c r="M103" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6786,26 +7302,31 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
+          <t>Долар відступає від двомісячного максимуму, оскільки напруга в Перській затоці зменшується; зростання ставок Reuters</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr">
+      <c r="I104" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I104" s="8" t="inlineStr"/>
-      <c r="J104" s="8" t="inlineStr">
+      <c r="J104" s="8" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr">
         <is>
           <t>Фінанси</t>
         </is>
       </c>
-      <c r="K104" s="10" t="inlineStr">
+      <c r="L104" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeWs5WHdObzRZRHJxcnRhbVBqbS1DV09RV0RUUFdsQnVMZ0czT2x0NFNnSDh3ODl3QXdTd1VTV0hiQkd0ektSRFhhQWEtdW1uMjU2bTl2TW1tcV9qVkJMbHNQeWZUYjlEcHN4RURDNDNicUsxLUVic0RqcHJHVU9YR3ZEYzVxeUxnNk1BQTlLRUZTb3ZtbzBtUm1sZENrenozQVJENkc4SUpYVHZvTlBDTXd6RUlIM2lhQmZKY1E4TQ?oc=5</t>
         </is>
       </c>
-      <c r="L104" s="8" t="inlineStr">
+      <c r="M104" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6844,26 +7365,31 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
+          <t>Судновласники світу розмістили замовлення на рекордну кількість нових нафтових супертанкерів, перевершивши бум у 2008 році, який зрештою призвів до надлишку та падіння ставок.</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr">
+      <c r="I105" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr"/>
-      <c r="J105" s="8" t="inlineStr">
+      <c r="J105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K105" s="10" t="inlineStr">
+      <c r="L105" s="10" t="inlineStr">
         <is>
           <t>https://gcaptain.com/newbuild-supertanker-orders-hit-record-high-surpassing-2008-peak/</t>
         </is>
       </c>
-      <c r="L105" s="8" t="inlineStr">
+      <c r="M105" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6902,30 +7428,35 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
+          <t>Землетрус магнітудою 7,8 на Філіппінах забрав життя щонайменше 35 осіб, обвалив будівлі та спровокував цунамі AP News</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
           <t>погода_клімат</t>
         </is>
       </c>
-      <c r="H106" s="8" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="J106" s="8" t="inlineStr">
         <is>
           <t>Філіппіни</t>
         </is>
       </c>
-      <c r="J106" s="8" t="inlineStr">
+      <c r="K106" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K106" s="10" t="inlineStr">
+      <c r="L106" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOdVh5VVRZSGpzVXdrUm9YQzByekhmZVRZZzcwZ3dhLU56RjBPTldPSW5ETEd5QTF6RFR5N2NpZThnX21GV1ZGbV95TVBxSmtRbmVkSV9EUWN5TE1ZRWtSZUgyb0ZSSWhPQ3RYaW5ScHVnWkVxWjAxeVY2LWpqU09Qd1RjcEFHLVVzSzROZTFJSTl3QkhnTnc?oc=5</t>
         </is>
       </c>
-      <c r="L106" s="8" t="inlineStr">
+      <c r="M106" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -6964,30 +7495,35 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
+          <t>Схвалення Трампа залишається на рекордно низькому рівні, оскільки більшість американців очікують підвищення цін на газ Reuters</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H107" s="8" t="inlineStr">
+      <c r="I107" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I107" s="8" t="inlineStr">
+      <c r="J107" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J107" s="8" t="inlineStr">
+      <c r="K107" s="8" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K107" s="10" t="inlineStr">
+      <c r="L107" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxOZWhGcWotbmVCTUpWTDA3eDFKdFI5WnB5M0JoeGJ6bU9pUjZDWE5ScW55Vkt4OFpiZGZ3bW8xS1cyUHZqb2pHQ2hPRndISXl0dXZQcWJmMG1TY2gwWndfaVJMUXZ6N1dYeU4zb0h6VC1USFZxVnAwa2FvMjJCT3g3aTl5cnAtUDNnTVVBSS11b1JsRXhJay1NQkg1UlFYRWRRanF0Vmw3TVhTZWtUQzZVNWRPdlRBbEtSWE80aG0ySGUwdDRDVHUw?oc=5</t>
         </is>
       </c>
-      <c r="L107" s="8" t="inlineStr">
+      <c r="M107" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7026,26 +7562,31 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
+          <t>Десятки викрадених на північному заході Нігерії після того, як бандити запросили їх на переговори Reuters</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H108" s="8" t="inlineStr">
+      <c r="I108" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I108" s="8" t="inlineStr">
+      <c r="J108" s="8" t="inlineStr">
         <is>
           <t>Нігерія</t>
         </is>
       </c>
-      <c r="J108" s="8" t="inlineStr"/>
-      <c r="K108" s="10" t="inlineStr">
+      <c r="K108" s="8" t="inlineStr"/>
+      <c r="L108" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQLUs1bHdndlA2T1RNZ0VjYzdieWNYUE9EWXZtSURQUnJ5OVlRZkVOMDVUQURIVl9qUWZHQ0pQemFGX3dwTFFSeVYwYnduMTI3ZEtOdjZkT253aE5OQUdLSHNJTWU5cGI4M2tGNnE2OGZaZ1JxeXUybERObHZUVG9uMU9OZ2s4QmFqb19kUVdISG1DMGFIUkRLOGF0c2haakNqaXBTYUg3TDNRNmU1Z2hwWW55Z2o2QQ?oc=5</t>
         </is>
       </c>
-      <c r="L108" s="8" t="inlineStr">
+      <c r="M108" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7084,26 +7625,31 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
+          <t>Президент Лівану закликає уряд Ізраїлю продовжувати переговори, а не війну Reuters</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr">
+      <c r="I109" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I109" s="8" t="inlineStr">
+      <c r="J109" s="8" t="inlineStr">
         <is>
           <t>Ліван, Ізраїль</t>
         </is>
       </c>
-      <c r="J109" s="8" t="inlineStr"/>
-      <c r="K109" s="10" t="inlineStr">
+      <c r="K109" s="8" t="inlineStr"/>
+      <c r="L109" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNZDkxMXVfRlVIdVNKZzg1OUROSjB0dTFqR04yTUFNVlBuWlZPNF9jQjlCZDB3a3Y0VkhTQWF4YzBITEM1Y3ZldnRBRzhJckpmSVRHRjkwaDhQcnpOTjRVd0IzQW5YbWhCV29memItSnFPcXpKTndscVZVN3dEcHVYN3NzcmUyUnVhR0VubGZlLUdxYnRDM2FOazFuend1WmZSTGZ6eVk0Q3puS0ljMmFIR05WdzdkRGhNLUtmNA?oc=5</t>
         </is>
       </c>
-      <c r="L109" s="8" t="inlineStr">
+      <c r="M109" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7142,26 +7688,31 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
+          <t>Керівник Ірану на переговорах погрожує подолати американську блокаду Ірану Reuters</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H110" s="8" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I110" s="8" t="inlineStr">
+      <c r="J110" s="8" t="inlineStr">
         <is>
           <t>Іран, США</t>
         </is>
       </c>
-      <c r="J110" s="8" t="inlineStr"/>
-      <c r="K110" s="10" t="inlineStr">
+      <c r="K110" s="8" t="inlineStr"/>
+      <c r="L110" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPakVzRnZYalIxVmRrUjV3VXJiMlVVUVo4Y2gzU2c0R21CdmRueEVyUTZ0bkkyMndJR1YwTTRyUXZBcFJkSGRQMTR6c1R3RE1UejRXYXNfZmdwSnpIbk01T21TMTdNY1FuYlF0YnJQdk9oZG1DQVBwUnpzbkYwWDlWaXFyM0hQSnNiNDQ0OFNCWm9vT0tVRVA2ZmluZzBLX25WS3kwNERfSGN0WUk?oc=5</t>
         </is>
       </c>
-      <c r="L110" s="8" t="inlineStr">
+      <c r="M110" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7200,30 +7751,35 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
+          <t>Керівники авіакомпаній критикують виробників двигунів за затримки на галузевому саміті Reuters</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H111" s="8" t="inlineStr">
+      <c r="I111" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I111" s="8" t="inlineStr">
+      <c r="J111" s="8" t="inlineStr">
         <is>
           <t>Глобально</t>
         </is>
       </c>
-      <c r="J111" s="8" t="inlineStr">
+      <c r="K111" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K111" s="10" t="inlineStr">
+      <c r="L111" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPc2thQnBNV3V3LVpReTFNWC1ZMnJ2dUh6Sjh2WlY1aU5BODdpREExZno0VW9oV1h4SkViclJRblhKY0FpeklTbU1jaHBFX05LUDBWUGE5amMwSTJndkJuVjJUVjU0d1kyckswcGVlUDUyZUF3UmxHdjhCUXMwNDZWVlBPUnRqOXRvZTd5SFV0QURKRmlWVU13VnNRaVcxQlRwR2dpaGI1WG0wcXFmU3gtZE1XelAtX2lyRExZ?oc=5</t>
         </is>
       </c>
-      <c r="L111" s="8" t="inlineStr">
+      <c r="M111" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7262,30 +7818,35 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
+          <t>Падіння продажів автомобілів у Китаї поширюється на травень, оскільки VW тестує модернізацію електромобілів Reuters</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H112" s="8" t="inlineStr">
+      <c r="I112" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I112" s="8" t="inlineStr">
+      <c r="J112" s="8" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J112" s="8" t="inlineStr">
+      <c r="K112" s="8" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="K112" s="10" t="inlineStr">
+      <c r="L112" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQNVJVQWJVbW5PRlNYYlluR3BKUWN3dmpfZGFQa2ZfZTlFMEhPeXg2NlNJOEEtZU1qMm0xWkYzZG93TjBsMWxkbXJIcEFHYXdrbm14UUx1WHNHSmVuT2JCSWpSRzBqdU9ONEhmclI2ckJpQWF4WXg3TG9CRWlzU2lkNnBadXl5dl92d0h6NzlVU09obHQxNU1ic2FnWTY?oc=5</t>
         </is>
       </c>
-      <c r="L112" s="8" t="inlineStr">
+      <c r="M112" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7324,26 +7885,31 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
+          <t>Прибуток Mercuria за перше півріччя підскочив на 88% через товарні шоки Bloomberg</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr">
+      <c r="I113" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I113" s="8" t="inlineStr"/>
-      <c r="J113" s="8" t="inlineStr">
+      <c r="J113" s="8" t="inlineStr"/>
+      <c r="K113" s="8" t="inlineStr">
         <is>
           <t>Метали, Хімічна продукція</t>
         </is>
       </c>
-      <c r="K113" s="10" t="inlineStr">
+      <c r="L113" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUEZmWmxhT3FFMWUzYUptRlFDeW1sbUZwR3hJcE4wd2ZoRk9VeTJiRFVHZVNzUlRzVzUtb1BGeVlVOXRpVEJIY1k5MWtXb0FvQjAxRHVRZVVWT0JuOGM1dGdGVFVaNHZOdEhRTWU0VEhpNXVEa2wtTFlhNmlTb19VRkh3cUVRREVJUVpNenh6dWtFR195RzBhYzF0RG9saFUyTFhQQlZpQTdmLW4zaGc?oc=5</t>
         </is>
       </c>
-      <c r="L113" s="8" t="inlineStr">
+      <c r="M113" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7382,30 +7948,35 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
+          <t>Брокерська галузь вантажних перевезень діяла десятиліттями на законних підставах, яких зараз немає. 14 травня Верховний суд США у справі «Монтгомері проти Caribe Transport II, LLC» одноголосно постановив, що Закон штату про дозволи Федеральної авіаційної адміністрації (FAAAA) не має переваги перед позовами про недбале наймання до фрахтових брокерів. Рішення 9-0, автором якого є суддя Емі Коні Барретт, вирішило давній розкол між федеральними окружними судами та скасувало захист із переваги, який б</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H114" s="8" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I114" s="8" t="inlineStr">
+      <c r="J114" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J114" s="8" t="inlineStr">
+      <c r="K114" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K114" s="10" t="inlineStr">
+      <c r="L114" s="10" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/the-supreme-court-just-stripped-brokers-of-their-biggest-legal-shield</t>
         </is>
       </c>
-      <c r="L114" s="8" t="inlineStr">
+      <c r="M114" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7444,30 +8015,35 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
+          <t>Витрати на пальне американських авіакомпаній зросли в квітні до 6,5 мільярдів доларів Reuters</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H115" s="8" t="inlineStr">
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I115" s="8" t="inlineStr">
+      <c r="J115" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J115" s="8" t="inlineStr">
+      <c r="K115" s="8" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K115" s="10" t="inlineStr">
+      <c r="L115" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQT0ViM0pmR0thY1BkcEUxOW55Z2FSNmFfTWNBZ1UtblZ4aFRLUV92bGNlZ3l5Qk1aMGpEWWdDbmZiNEZ6LVR2VXg3czdVejlXbGVPRUVvUzRERjlqY2xCWDA5clVDV25LWThPVHQtM2J2aGRTcUMzaWNWMVRPbW9VWlkxSElDY1dTb0hSR0NqN1BTRmRpeW4wdzZISWdzX2c?oc=5</t>
         </is>
       </c>
-      <c r="L115" s="8" t="inlineStr">
+      <c r="M115" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7506,30 +8082,35 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
+          <t>The post DHL інвестує у французькі операції спершу з'явиться на Logistics Manager.</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H116" s="8" t="inlineStr">
+      <c r="I116" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I116" s="8" t="inlineStr">
+      <c r="J116" s="8" t="inlineStr">
         <is>
           <t>Франція</t>
         </is>
       </c>
-      <c r="J116" s="8" t="inlineStr">
+      <c r="K116" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K116" s="10" t="inlineStr">
+      <c r="L116" s="10" t="inlineStr">
         <is>
           <t>https://www.logisticsmanager.com/dhl-invests-in-french-operations/</t>
         </is>
       </c>
-      <c r="L116" s="8" t="inlineStr">
+      <c r="M116" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7568,30 +8149,35 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
+          <t>FedEx і China Southern Air Logistics підписали Меморандум про взаєморозуміння (MoU) для вивчення можливостей співпраці в галузі підключення до міжнародних рейсів і вузлів, планування мережі, ресурсів флоту, наземних операцій і цифровізації. Обидві сторони намагатимуться використовувати свої ресурси та можливості для поглиблення стратегічної співпраці, підвищення операційної ефективності та глобальних можливостей обслуговування та створення найкращих…</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H117" s="8" t="inlineStr">
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I117" s="8" t="inlineStr">
+      <c r="J117" s="8" t="inlineStr">
         <is>
           <t>Китай, США</t>
         </is>
       </c>
-      <c r="J117" s="8" t="inlineStr">
+      <c r="K117" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K117" s="10" t="inlineStr">
+      <c r="L117" s="10" t="inlineStr">
         <is>
           <t>https://www.aircargonews.net/editorial/2026/06/fedex-and-china-southern-air-logistics-signs-strategic-cooperation-mou/</t>
         </is>
       </c>
-      <c r="L117" s="8" t="inlineStr">
+      <c r="M117" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7630,30 +8216,35 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
+          <t>Схоже, що Gemini Cooperation готується до тривалого захоплення частки ринку в азіатсько-середземноморській торгівлі. Згідно з новим аналізом Sea-Intelligence, партнери Hapag-Lloyd і Maersk поступово вилучають потужності із західного узбережжя Азії та Північної Америки, східного узбережжя Азії та Північної Америки та торгівлі між Азією та Північною Європою та перенаправляють їх на маршрути Азії та Середземномор’я. «Хоча дані про ринкову частку потужності торгової смуги свідчать про те, що Gemini втрачає позиції у великій торгівлі зі сходу на захід</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H118" s="8" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I118" s="8" t="inlineStr">
+      <c r="J118" s="8" t="inlineStr">
         <is>
           <t>Міжнародні маршрути</t>
         </is>
       </c>
-      <c r="J118" s="8" t="inlineStr">
+      <c r="K118" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K118" s="10" t="inlineStr">
+      <c r="L118" s="10" t="inlineStr">
         <is>
           <t>https://theloadstar.com/gemini-carriers-set-for-market-share-grab-on-asia-mediterranean/</t>
         </is>
       </c>
-      <c r="L118" s="8" t="inlineStr">
+      <c r="M118" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7692,30 +8283,35 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
+          <t>Чому слабка потужність гідроенергетики в Італії може перешкодити зусиллям Європи по відновленню газопостачання Reuters</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
           <t>погода_клімат</t>
         </is>
       </c>
-      <c r="H119" s="8" t="inlineStr">
+      <c r="I119" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="J119" s="8" t="inlineStr">
         <is>
           <t>Італія</t>
         </is>
       </c>
-      <c r="J119" s="8" t="inlineStr">
+      <c r="K119" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K119" s="10" t="inlineStr">
+      <c r="L119" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxOcGdOcVFlZUp5eGh3MUZtTlJIQXhkWUhtY2I1VnMyT0cxMFlLcUg3dmJLZFl6d1kzUllCdVRYU25IWVE3VTlaYXZrTWpvaWxDcHJ5dUpfel8yRXAtb3hWbmY4dEtjRWc5emwxemZzWXZOazhPeFVwREJQTmNLUlNHVlBNVFdNLWVFVWJrRmw5OGdZM3BpRkRIaXdGaG9EMkVoQlhTTXVfRjVlMVVEYzhXTEFlR1ZfVkNsQnNvam1JeWJ5dHcySS1TV1R0U1FVWGM?oc=5</t>
         </is>
       </c>
-      <c r="L119" s="8" t="inlineStr">
+      <c r="M119" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7754,30 +8350,35 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
+          <t>Technip Energies виграє контракт на LNG у Мозамбіку для Eni, партнер Reuters</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H120" s="8" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I120" s="8" t="inlineStr">
+      <c r="J120" s="8" t="inlineStr">
         <is>
           <t>Мозамбік</t>
         </is>
       </c>
-      <c r="J120" s="8" t="inlineStr">
+      <c r="K120" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K120" s="10" t="inlineStr">
+      <c r="L120" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPcjNQaFlhWkYycDgtX1JOS2N6dVpQNE9TNHJleUU5MU9BYTdPeW9PZGFmMlFMYkRPdHVjaFQ4VldSNlVOemhsWk9uWjJyTWlMNFl2WVpzcVU0Mlo2cmVIdGFyOFAzM2lVZXVKOXFQaEZUb01uOUpXYUFjY0hJMlhNYThqZVA2bmtpbklnNWhpZ0FXTnNpLVA1Sk1UUHpQWkxNS2t1eXZUVDlVU1B4cTVV?oc=5</t>
         </is>
       </c>
-      <c r="L120" s="8" t="inlineStr">
+      <c r="M120" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7816,26 +8417,31 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
+          <t>Економічні опитування Трампа падають, оскільки війна в Ірані підриває його супердержаву Bloomberg</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H121" s="8" t="inlineStr">
+      <c r="I121" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I121" s="8" t="inlineStr">
+      <c r="J121" s="8" t="inlineStr">
         <is>
           <t>США, Близький Схід</t>
         </is>
       </c>
-      <c r="J121" s="8" t="inlineStr"/>
-      <c r="K121" s="10" t="inlineStr">
+      <c r="K121" s="8" t="inlineStr"/>
+      <c r="L121" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOc3JMdnR4UWFNcFEwa2p0QV9ZZnpKZWV6MklzNGpOcGZhTU5TNFc5OUUwc1lKZXh3MlpKdzYyQ011LUZza0FyeE4zZlExR08tRGJjVVdaUEpSamZCQV84N1hmUV82SkdCOE5EX0FfaDNHb085bEtkTUs5M2wySDlmZ2k4ZXo2bEtCSW9VQkh5eVZSUGRvXzZQMVNJV2FCZ0JTaGRhQzFjTzNYUFQxWFJmOEM5Zw?oc=5</t>
         </is>
       </c>
-      <c r="L121" s="8" t="inlineStr">
+      <c r="M121" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7874,30 +8480,35 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
+          <t>У Нью-Йорку вісьмом особам висунули звинувачення у зв'язку з тим, що, як стверджує прокуратура, було розкраданням вантажу в кількох штатах. Прокурори стверджують, що ця схема передбачала несанкціоноване використання інформації про відправлення та видавання себе за законних транспортних перевізників для перенаправлення вантажів вартістю приблизно 4,49 мільйона доларів США, згідно з обвинуваченням і публічним оголошенням окружної прокуратури Манхеттена. Основні звинувачення не були доведені в суді. Акк</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H122" s="8" t="inlineStr">
+      <c r="I122" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="J122" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J122" s="8" t="inlineStr">
+      <c r="K122" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K122" s="10" t="inlineStr">
+      <c r="L122" s="10" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/eight-indicted-in-alleged-carrier-impersonation-scheme-prosecutors-allege-4-49-million-in-cargo-losses</t>
         </is>
       </c>
-      <c r="L122" s="8" t="inlineStr">
+      <c r="M122" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7936,26 +8547,31 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
+          <t>Індонезія розглядає винятки з експортних правил для трейдерів товарів Bloomberg</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H123" s="8" t="inlineStr">
+      <c r="I123" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="J123" s="8" t="inlineStr">
         <is>
           <t>Індонезія</t>
         </is>
       </c>
-      <c r="J123" s="8" t="inlineStr"/>
-      <c r="K123" s="10" t="inlineStr">
+      <c r="K123" s="8" t="inlineStr"/>
+      <c r="L123" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPSDZVNEE5TWstNk1VUFBjTTBNaExTLXB3RXdPMlgzSXZYNXVCbVM5TEd1ckVLaGhGV2JUSjR2LUNFR195dXZ0RDY3QU9mN3pXemVZZGxwQ1ptTlZMbDgzRC1jMy1jVHh3TTNKX1QtSUVZUUNmaW02S1dlWmdrdzVOaFVCTVdVbDA4aGNJLVlNN3U4T0JVdmVqWmkzMzFYZFRLbVNsdTYzREQ1VTY3eGFXTlJ3?oc=5</t>
         </is>
       </c>
-      <c r="L123" s="8" t="inlineStr">
+      <c r="M123" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -7994,30 +8610,35 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
+          <t>Розгром ринку чинить тиск на Індонезію, щоб вона зробила конкретні кроки Bloomberg</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H124" s="8" t="inlineStr">
+      <c r="I124" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="J124" s="8" t="inlineStr">
         <is>
           <t>Індонезія</t>
         </is>
       </c>
-      <c r="J124" s="8" t="inlineStr">
+      <c r="K124" s="8" t="inlineStr">
         <is>
           <t>Зернові, Логістика</t>
         </is>
       </c>
-      <c r="K124" s="10" t="inlineStr">
+      <c r="L124" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQOEs4RUs1QnlaUENZVmlNQk5qREJMMHlsakdTZG4tclBoSFBrd1ZDMWhNQV90R2ZtbDU3aU5IQWRDZk53dTNfYWpEUEV1dl93MTJuNkpua0t1cFZwQ29yR0pNY1otb1ZQbmNyQ0xWS2w1WktjNUFnRHpLb2FvZms0SXJNMFE4aHNBOTZOaW5waUFNRHkzbEdiQ1lXNVNuX0ZTUW01bjcyMmRQR3d3ZlVBdV94MXAyQQ?oc=5</t>
         </is>
       </c>
-      <c r="L124" s="8" t="inlineStr">
+      <c r="M124" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8056,30 +8677,35 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
+          <t>Минулого тижня було реалізовано три проекти з покращення залізничного сполучення в деяких країнах Ради співробітництва Перської затоки (GCC). Саудівська Аравія подала тендер на проект лінії між Кувейтом та ОАЕ та працює над відновленням залізниці до Туреччини, тоді як на лінії Оман-ОАЕ почалися роботи з укладання колії. Тендер, оголошений компанією Saudi Arabia Railways, стосується 672-кілометрової ділянки між Аль-Хафджі поблизу Кувейту та Аль-Батхою поблизу кордону з ОАЕ. Лінія є частиною ширшого GCC</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H125" s="8" t="inlineStr">
+      <c r="I125" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I125" s="8" t="inlineStr">
+      <c r="J125" s="8" t="inlineStr">
         <is>
           <t>Саудівська Аравія, ОАЕ, Оман</t>
         </is>
       </c>
-      <c r="J125" s="8" t="inlineStr">
+      <c r="K125" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K125" s="10" t="inlineStr">
+      <c r="L125" s="10" t="inlineStr">
         <is>
           <t>https://www.railfreight.com/beltandroad/2026/06/08/multiple-gulf-railway-projects-enter-their-next-phase/</t>
         </is>
       </c>
-      <c r="L125" s="8" t="inlineStr">
+      <c r="M125" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8118,30 +8744,35 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
+          <t>Delta може відмовитися від Safran для місць преміум-класу через затримки поставок Bloomberg</t>
+        </is>
+      </c>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H126" s="8" t="inlineStr">
+      <c r="I126" s="8" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="J126" s="8" t="inlineStr">
         <is>
           <t>США, Франція</t>
         </is>
       </c>
-      <c r="J126" s="8" t="inlineStr">
+      <c r="K126" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K126" s="10" t="inlineStr">
+      <c r="L126" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPZHh5aGl2MXhieGkwbzVCMnh3bkkwNXdrNDNKSzhqQ3BxV0liaU1GTG9DR3VFYzZZNTZVdUVITzV0X3VMaEoxTDRrZ2FfcUhoUnctaXp2bURFUnhuemRqdldaQ0U1aDlFbF9rZWN2YmR1T2FDd2M2OS13NGd0Q21qdUVwTnBqcEJlY1pQX2VWN0JWZEM3Q1FWc1hUQjFSN01yaW9iY1FKMkRudkRNTFE?oc=5</t>
         </is>
       </c>
-      <c r="L126" s="8" t="inlineStr">
+      <c r="M126" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8180,22 +8811,27 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
+          <t>Голова МВФ попереджає, що світ не готовий до потрясінь, які накопичуються Bloomberg</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H127" s="8" t="inlineStr">
+      <c r="I127" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I127" s="8" t="inlineStr"/>
       <c r="J127" s="8" t="inlineStr"/>
-      <c r="K127" s="10" t="inlineStr">
+      <c r="K127" s="8" t="inlineStr"/>
+      <c r="L127" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOSG43TVdTS1VFU0lJX0dKVy10VmUwVWZzbVlQa3pKTE5FQktpd2RyLVhzS3FDVkR2V2NwaE5rRTVGNWkxeFBQN1Fuc1o3OHNtbEg4ZzhZUGJGQy1wUm14OXE4QWNzajNtSnh2TDVCY1lIdXBsOGVxVkF6V01HZzNDekJtME9jWHh0QU9LSDQ1M0RTLUJfa1BRYUlUSk01bTVub1VOMFlxQmxBRDBmQnFuZ2Qxc3M?oc=5</t>
         </is>
       </c>
-      <c r="L127" s="8" t="inlineStr">
+      <c r="M127" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8234,30 +8870,35 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
+          <t>Рупія падає через підвищення ціни на нафту, дохідність казначейських облігацій підтримує долар Reuters</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H128" s="8" t="inlineStr">
+      <c r="I128" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="J128" s="8" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J128" s="8" t="inlineStr">
+      <c r="K128" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K128" s="10" t="inlineStr">
+      <c r="L128" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNRVc2R0NiNjh6dTIxSmR0OFdMaE1MRXAteVZWRVRRWXo2M1RnVHZRSFRPTEh5aXhreHlHZmdGeWRCRThLTUs1MWhGcUhJSmQxYjU2dWlGcmtzNEVxU1lDRVZlNUNHdG9VTDBFTEJkYkdpU2ZiZGdmUnhRYy1RNnN6U2lYMkFyOVYxdVpqWkFOQjFydFgzRi1ZTmNoLXFzUWpVTUJjNU1wU01VUVpPc0JaTw?oc=5</t>
         </is>
       </c>
-      <c r="L128" s="8" t="inlineStr">
+      <c r="M128" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8296,26 +8937,31 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
+          <t>Британські фірми призупиняють прийом на роботу через війну в Ірані, показує опитування REC Reuters</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
           <t>страйки_перебої</t>
         </is>
       </c>
-      <c r="H129" s="8" t="inlineStr">
+      <c r="I129" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="J129" s="8" t="inlineStr">
         <is>
           <t>Великобританія</t>
         </is>
       </c>
-      <c r="J129" s="8" t="inlineStr"/>
-      <c r="K129" s="10" t="inlineStr">
+      <c r="K129" s="8" t="inlineStr"/>
+      <c r="L129" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPT21fRzk1ZmZ1OUtEVmJkWXpGd1RFNUhaVU9KRU9TVWZ1T2sxVVozclBXVjczRTU5NlVFaTRZbjZEWGU3TnhuaW5XYndqUmxCNzFFWlpWYXp1TWhPVzVzaHl2a3NyNFhOT200TXNpSWRwVDZhc2NOWnY4c3JULTk1SUI1bGhscnktSHFpU1BEQW1neFptU0F5ZU9NN1VJNnZC?oc=5</t>
         </is>
       </c>
-      <c r="L129" s="8" t="inlineStr">
+      <c r="M129" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8354,30 +9000,35 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
+          <t>Airbus повідомляє клієнтів серії A320neo про затримки реактивних літаків у 2027 і 2028 роках, повідомляє Bloomberg News Reuters</t>
+        </is>
+      </c>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H130" s="8" t="inlineStr">
+      <c r="I130" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I130" s="8" t="inlineStr">
+      <c r="J130" s="8" t="inlineStr">
         <is>
           <t>Франція</t>
         </is>
       </c>
-      <c r="J130" s="8" t="inlineStr">
+      <c r="K130" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K130" s="10" t="inlineStr">
+      <c r="L130" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNcDlYTU4zU1p5M0YwN2hPd3FNdTdKWDVsaGI5QXZfUWY1MHNGVjg1MHotS2RrYUE3cEU3UjZBbmMyOHFTNDZNNko2VHZvenNHM0J5bmM0YmkwV09SYllzYWozNjY4T3pvNUliR1g0QnlNRmNCMUloWWFhZjR0VkpGc3pRUEtDd0FYR0I1N0M2OE9qU1JjMEpKOGpOcFBHbFh0SE1hQ1ZHVHRJeHJNWHctWTZWY0VyOHBRME5OcE9VaUd2Z25STGxTVTBtQko4bnIwOEVFd0hB?oc=5</t>
         </is>
       </c>
-      <c r="L130" s="8" t="inlineStr">
+      <c r="M130" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8416,26 +9067,31 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
+          <t>Торговці облігаціями роблять ставку на зростання ІСЦ, що підтверджує аргументи ФРС. Bloomberg</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H131" s="8" t="inlineStr">
+      <c r="I131" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I131" s="8" t="inlineStr">
+      <c r="J131" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J131" s="8" t="inlineStr"/>
-      <c r="K131" s="10" t="inlineStr">
+      <c r="K131" s="8" t="inlineStr"/>
+      <c r="L131" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOSXlnaHBqaEI1ZmI2RHpwQlBLdFN0Ym9LdE9WOFk1VnJzcUhEVmRnaFNVcnFtbmNHdHliM3FPdDJHMW1Vcmw1NzBKd2FjUjFyX2xCSl9QQlFTalQ4LVNQUDBXdWYtcUQyTy1MbzFBYjc5Y0VNZ1c5X2ViVUhuc3AwT3k1aG84aWNNZUxRSlBTeWZaLV9SeE5MUVhTMlhZWXRMZGtlR1A5MDNhdXJTSk9pai1KeDl2dw?oc=5</t>
         </is>
       </c>
-      <c r="L131" s="8" t="inlineStr">
+      <c r="M131" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8474,26 +9130,31 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
+          <t>Трамп заявив, що не розморозить активи Ірану до укладення мирної угоди Reuters</t>
+        </is>
+      </c>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H132" s="8" t="inlineStr">
+      <c r="I132" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr">
+      <c r="J132" s="8" t="inlineStr">
         <is>
           <t>США, Іран</t>
         </is>
       </c>
-      <c r="J132" s="8" t="inlineStr"/>
-      <c r="K132" s="10" t="inlineStr">
+      <c r="K132" s="8" t="inlineStr"/>
+      <c r="L132" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQR0t2Sk5ISElDUHNqUWthaDlabUV5czBtSVVtQ05kOTJFVVFYRm01RWRnTkZ6U2JXdEUxVFJjdXpUYUhSbGdJVFRsdEhMYS1lNENNYjVMcWtJdnE4dExueWM5TzBLQlpVYmxQUjVObEN6dDUzcnpUeUpXV2h6cnFSeWllWElnMXlZdjN6MWg4S2NQamVfd2U4dDZaQjJlOFMwX2xwNTFvcWJ5VzNMR3RIY2EtMjBQeEIxYTFhdmlxOVBkbmc?oc=5</t>
         </is>
       </c>
-      <c r="L132" s="8" t="inlineStr">
+      <c r="M132" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8532,26 +9193,31 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
+          <t>Швейцарські фірми інвестують 27 мільярдів доларів США після тарифної угоди, NZZ am Sonntag повідомляє Reuters</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H133" s="8" t="inlineStr">
+      <c r="I133" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I133" s="8" t="inlineStr">
+      <c r="J133" s="8" t="inlineStr">
         <is>
           <t>Швейцарія, США</t>
         </is>
       </c>
-      <c r="J133" s="8" t="inlineStr"/>
-      <c r="K133" s="10" t="inlineStr">
+      <c r="K133" s="8" t="inlineStr"/>
+      <c r="L133" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOVHM5RXlLd3dJWFNHX1JWMWJXVHFaU295N0REclBidnhhemVacVZTelRsTWxQRGdCSmN5Qy1CNmxvQTdlZEw1dnpleGI2Sm5hRUVSQnNZM2pOeVB6RDE0ZXpIaVh5cHFSWjBaVXpyYWpsb3BDMW1JUjlCS2RCdTFjUGRzYVlwSHZxNDJHelVVeWRRUThSOTZ2Y0tIWVk2LXg2OGVpN2wtc01XOGhsdnN0NzFPVmJiaGZDSzUyTUV3R0ppcmFO?oc=5</t>
         </is>
       </c>
-      <c r="L133" s="8" t="inlineStr">
+      <c r="M133" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8590,26 +9256,31 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
+          <t>Глава консерваторів ЄС закликає посилити торговельну позицію Китаю, повідомляє Bild am Sonntag Reuters</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H134" s="8" t="inlineStr">
+      <c r="I134" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I134" s="8" t="inlineStr">
+      <c r="J134" s="8" t="inlineStr">
         <is>
           <t>ЄС, Китай</t>
         </is>
       </c>
-      <c r="J134" s="8" t="inlineStr"/>
-      <c r="K134" s="10" t="inlineStr">
+      <c r="K134" s="8" t="inlineStr"/>
+      <c r="L134" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQMUdpbWFtUm41OGJQNl9zSWh4SE5GXzhINXBOb1djT2Vjb1o3eUxmeHVROGFDLXhsX3lrY1Q1YUQwUGhtSmZOelFSbS1fbkpoNmZjdzlTb1hpSGxPM3BZMW5YSVFpY3ZRMzN3TFJqbURWdDFMU29PN2ljdG1JdUx4WUdHMlB4QmQ3bXZSdlFaTGZha0xWOVo3UHVSamZ1WVg4ZldzV2plTWtDeUZmNV9ONXNVQW15WWE4UkxETmd6NVpDOVQw?oc=5</t>
         </is>
       </c>
-      <c r="L134" s="8" t="inlineStr">
+      <c r="M134" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8648,26 +9319,31 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
+          <t>Діаграма тижня: Середня довжина перевезення у вихідному напрямку – США SONAR : OALOHA.USA Незважаючи на постійне загострення внутрішнього ринку вантажних вантажів, тенденція до скорочення довжини вантажів, яка почалася в 2024 році, практично не змінюється. З червня 2024 року середня довжина перевезення в наборі тендерних даних SONAR зменшилася з приблизно 607 миль до трохи більше 500 миль — падіння на 21%, причому 11% цього показника припало лише на минулий рік, що робить цю тенденцію досить лінійною. Чи є це частиною стійкої структури?</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H135" s="8" t="inlineStr">
+      <c r="I135" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I135" s="8" t="inlineStr">
+      <c r="J135" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J135" s="8" t="inlineStr"/>
-      <c r="K135" s="10" t="inlineStr">
+      <c r="K135" s="8" t="inlineStr"/>
+      <c r="L135" s="10" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/truckloads-shrinking-miles</t>
         </is>
       </c>
-      <c r="L135" s="8" t="inlineStr">
+      <c r="M135" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8706,26 +9382,31 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
+          <t>ЄЦБ стає провідним яструбом у G7 завдяки підвищенню процентної ставки, наголошує Bloomberg</t>
+        </is>
+      </c>
+      <c r="H136" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H136" s="8" t="inlineStr">
+      <c r="I136" s="8" t="inlineStr">
         <is>
           <t>НМА</t>
         </is>
       </c>
-      <c r="I136" s="8" t="inlineStr">
+      <c r="J136" s="8" t="inlineStr">
         <is>
           <t>Європа</t>
         </is>
       </c>
-      <c r="J136" s="8" t="inlineStr"/>
-      <c r="K136" s="10" t="inlineStr">
+      <c r="K136" s="8" t="inlineStr"/>
+      <c r="L136" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQOHQ2cTBlTHBFMnNTVGtKYnJzN01LTDRXSzlOd2NVWVNRd1ZHQnlEcllwMGNZbXNDNVl5ZGk3c0hfRnltbXFFRThFZjczT0NxM3Q0ZVlrVlpvZlJKR3hQN3BSR0pXbjFDV0hPNEloVmlpVzd3VnVEUkU3dXV3NmtGX2QwSHZfYzVUbVlrLS0yX2NaZTFQbkRVVHYwNmtoZThKUnk2LVhTLWgzOVk1OVlrY0pB?oc=5</t>
         </is>
       </c>
-      <c r="L136" s="8" t="inlineStr">
+      <c r="M136" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8764,30 +9445,35 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
+          <t>Велика нафтова компанія змінює свою думку щодо Венесуели: нова економіка Bloomberg</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H137" s="8" t="inlineStr">
+      <c r="I137" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I137" s="8" t="inlineStr">
+      <c r="J137" s="8" t="inlineStr">
         <is>
           <t>Венесуела</t>
         </is>
       </c>
-      <c r="J137" s="8" t="inlineStr">
+      <c r="K137" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K137" s="10" t="inlineStr">
+      <c r="L137" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPYS02alh5LVN1ZUlSbEYza3Y4ZmF3X0prNXVoSkRhLWdrM1FMNXAwcDE5V2xHUFRXVC1MdVBzMXRLa1puQzZYRjVkTmRaanc0SUR2WThvbjViNDF2MFpuNGxpNWJPSFFnRHU1RG1lczdzdnNaSnB1NXIyT0dCLWEtVFpad3VseWJtQnFjZ0g5cUM4SlZnRFBvbHZFREo5MUNCWDhxUFFiSEo2QXc2ZEN3?oc=5</t>
         </is>
       </c>
-      <c r="L137" s="8" t="inlineStr">
+      <c r="M137" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8826,26 +9512,31 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
+          <t>Доларові компанії після сильних даних про робочі місця в США підштовхують ієну до рівня 160 Reuters</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H138" s="8" t="inlineStr">
+      <c r="I138" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I138" s="8" t="inlineStr">
+      <c r="J138" s="8" t="inlineStr">
         <is>
           <t>США, Японія</t>
         </is>
       </c>
-      <c r="J138" s="8" t="inlineStr"/>
-      <c r="K138" s="10" t="inlineStr">
+      <c r="K138" s="8" t="inlineStr"/>
+      <c r="L138" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNY1I1UFVHbFdub2xoRDE3aktGWXBsaC1XNFZReFFnVEFiMl9YR2t1UVlXMjhtYWtWbHJjNkMtWlZKZERtTEZMTEE4TzFtZGhFS3oyc3p1Wm1nVEtxdEN6OENxWWFtdTNYOEpnNFRDaVdKMTNySW1MZTlQWEZyd0tMSEdkaVpvOU1VY19CZ2hrR3JhY0R5LUFiQlFhNy1PYllOcGlnVzhHY3lqNnNQS0RxOW5MSzFIb2Y3Rnc?oc=5</t>
         </is>
       </c>
-      <c r="L138" s="8" t="inlineStr">
+      <c r="M138" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8884,30 +9575,35 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
+          <t>Мідь зберігає приріст завдяки ослабленню напруженості в Ірані, у фокусі дані Китаю Bloomberg</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H139" s="8" t="inlineStr">
+      <c r="I139" s="8" t="inlineStr">
         <is>
           <t>Вит.матеріали/МШП</t>
         </is>
       </c>
-      <c r="I139" s="8" t="inlineStr">
+      <c r="J139" s="8" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J139" s="8" t="inlineStr">
+      <c r="K139" s="8" t="inlineStr">
         <is>
           <t>Метали</t>
         </is>
       </c>
-      <c r="K139" s="10" t="inlineStr">
+      <c r="L139" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRXZJZzlUVXdFNXpvMkJkSVhfbEd1em1sS1RTM0N2S2pCZlZJQVNLWVltTVFIcHVXSXBzbzVVT2F2dW1xSmFsNWpucmQtdUhWcThxUk1zTVBvbjhSTk02YTFxTlpMbUI5a1dqcUNOS3pnLWJpMGFpRVA5VVBlMFlCbEVZbjFVWFlBclRfYXVXVzEtVFlGRmd5QkpIWElHN0RjMWxvMGVLd2poWDBPNHRkMkZqemo?oc=5</t>
         </is>
       </c>
-      <c r="L139" s="8" t="inlineStr">
+      <c r="M139" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -8946,30 +9642,35 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
+          <t>Останню загрозу судноплавства Хусі притупили через слабкий трафік у Червоному морі Bloomberg</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H140" s="8" t="inlineStr">
+      <c r="I140" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="J140" s="8" t="inlineStr">
         <is>
           <t>Йемен</t>
         </is>
       </c>
-      <c r="J140" s="8" t="inlineStr">
+      <c r="K140" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K140" s="10" t="inlineStr">
+      <c r="L140" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQakJaUkM0aTVJMEdla0V3aXhycXZVXzU3Z2lBVHRablM2LUl1ekEyRDZteWdObzlhTHVfM2U0VUtXYlRDUTM4MHpZYzkyWVpWTmVvcUI5cGF2dWJKcW13OGo4OUEtZ0xxOTJOQ0VxMXJmUUZkSFZudU1CLTVhSHExRGEwUWRCNVROQ0plSmNuMVZCcmhJUlJ0ZzRYTF9GRmwwSTVSeV9rNHcyUmVjY0s5NXBDT18tcGVSRnc?oc=5</t>
         </is>
       </c>
-      <c r="L140" s="8" t="inlineStr">
+      <c r="M140" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9008,30 +9709,35 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
+          <t>Зростання штучного інтелекту, можливо, нарешті зустріло свій конкурент - Fed Reuters</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H141" s="8" t="inlineStr">
+      <c r="I141" s="8" t="inlineStr">
         <is>
           <t>НМА</t>
         </is>
       </c>
-      <c r="I141" s="8" t="inlineStr">
+      <c r="J141" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J141" s="8" t="inlineStr">
+      <c r="K141" s="8" t="inlineStr">
         <is>
           <t>Фінанси</t>
         </is>
       </c>
-      <c r="K141" s="10" t="inlineStr">
+      <c r="L141" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNZFh0ZXR3OW5raVRWQ2pXM2NDUWNoVnh6WFlISWJuM2ExbW9YdjZmWDhwVFBGbzFZaUVldUYtRlJPZnVlMkRuWjdhRFdPVi1HV0NGX3dIcjM5NTE5ZC1PZW10WTdYQTRTWU56czVvVWJ3M2dGZ0tXeHkwVzliV0hFZXY1YTlGTnNWbGNsY2pXZ1dtc3dIbkQ0TnhtaE1ZaDk0S0hRYWZvTkJCOUNQUUZnZkxB?oc=5</t>
         </is>
       </c>
-      <c r="L141" s="8" t="inlineStr">
+      <c r="M141" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9070,30 +9776,35 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
+          <t>Канада запускає кредитну програму, щоб допомогти авіакомпаніям впоратися з високими цінами на паливо Reuters</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H142" s="8" t="inlineStr">
+      <c r="I142" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I142" s="8" t="inlineStr">
+      <c r="J142" s="8" t="inlineStr">
         <is>
           <t>Канада</t>
         </is>
       </c>
-      <c r="J142" s="8" t="inlineStr">
+      <c r="K142" s="8" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K142" s="10" t="inlineStr">
+      <c r="L142" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNdmhXaHdWckU2LW85THJEVWp2d0lhV05Gb0pqVld3M3Jkc0ctaExOMjA0X3JQYV94YUNzTHNSMTVaNFdzN1dhM0hBZW9VTmN3X3E5QW5KZV82U3FCY29uNVd6VkFUTnYtT1htTlhIOHd2aTlZRlJ6czIyaFhMa2FyVXhIdzhGeXhCOUhTS2ptcFdVWXlRNVN0MjVkaEV3ZlV0OUVETnVSTVhVZ2hpOWxmeA?oc=5</t>
         </is>
       </c>
-      <c r="L142" s="8" t="inlineStr">
+      <c r="M142" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9132,30 +9843,35 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
+          <t>Транспортний брокер Fura оголосив у понеділок про придбання LG Logistics Solutions. Це стало шостим придбанням для 3PL із штучним інтелектом у Цинциннаті. Фінансові умови угоди не розголошуються. «Фрахтове брокерство є однією з найбільших і найбільш фрагментованих галузей надання послуг у країні — тисячі дрібних брокерів працюють вручну та мають великі накладні витрати», — йдеться в прес-релізі Fura. «Фура вважає, що штучний інтелект докорінно змінює математику консолідації: скоріше</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H143" s="8" t="inlineStr">
+      <c r="I143" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I143" s="8" t="inlineStr">
+      <c r="J143" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J143" s="8" t="inlineStr">
+      <c r="K143" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K143" s="10" t="inlineStr">
+      <c r="L143" s="10" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/ai-powered-broker-fura-announces-latest-acquisition</t>
         </is>
       </c>
-      <c r="L143" s="8" t="inlineStr">
+      <c r="M143" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9194,30 +9910,35 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
+          <t>Ринок танкерів VLCC, схоже, спостерігає зниження волатильності після багатотижневої турбулентності. У своєму останньому щотижневому звіті судновий брокер Gibson зазначив, що "глобальний ринок VLCC, схоже, увійшов у фазу обережної стабілізації, коли фрахтові ставки повертаються від піку, викликаного війною, до довоєнних показників. Серйозне вільне падіння, яке багато хто очікував від структурних ...</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H144" s="8" t="inlineStr">
+      <c r="I144" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="J144" s="8" t="inlineStr">
         <is>
           <t>світ</t>
         </is>
       </c>
-      <c r="J144" s="8" t="inlineStr">
+      <c r="K144" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K144" s="10" t="inlineStr">
+      <c r="L144" s="10" t="inlineStr">
         <is>
           <t>https://www.hellenicshippingnews.com/vlcc-market-seems-to-be-stabilizing/</t>
         </is>
       </c>
-      <c r="L144" s="8" t="inlineStr">
+      <c r="M144" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9256,30 +9977,35 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
+          <t>Газифікація вугілля дедалі більше стає додатковим рушієм торгівлі вугіллям і попиту на перевезення насипних вантажів. Хоча це малоймовірно, щоб кардинально повернути назад довгостроковий перехід від вугілля, це поступово створює новий промисловий попит, окрім традиційного виробництва теплової енергії. Це особливо очевидно в таких країнах, як Індія, які прагнуть більшої ...</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H145" s="8" t="inlineStr">
+      <c r="I145" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I145" s="8" t="inlineStr">
+      <c r="J145" s="8" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J145" s="8" t="inlineStr">
+      <c r="K145" s="8" t="inlineStr">
         <is>
           <t>Паливо</t>
         </is>
       </c>
-      <c r="K145" s="10" t="inlineStr">
+      <c r="L145" s="10" t="inlineStr">
         <is>
           <t>https://www.hellenicshippingnews.com/indias-coal-gasification-drive-adds-fresh-momentum-to-the-coal-trade-and-bulk-shipping/</t>
         </is>
       </c>
-      <c r="L145" s="8" t="inlineStr">
+      <c r="M145" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9318,30 +10044,35 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
+          <t>Американський суддя скасовує політику Трампа щодо обмеження вітру та сонячної енергії Reuters</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H146" s="8" t="inlineStr">
+      <c r="I146" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I146" s="8" t="inlineStr">
+      <c r="J146" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J146" s="8" t="inlineStr">
+      <c r="K146" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K146" s="10" t="inlineStr">
+      <c r="L146" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNUGhONTdCSjNWQUdBWFlpbmI2UnR4elR0SjZmNFphRTlOdDlQTVhjalgyeTZoYy1jbVUwb2pQWW5uUC1NMlJUYktOY3hyM2x2dnlSVk1RY193S19HbEp5WWZiX18yWWo2X3hlUzBYa1Z4TVZNYi1KdWt6V0pHbmJHZG5ETW1mS2QwOTFyLUtCQnQ3QVJPNHoyeGk2YUlrXzM4amtRZGJ1RVBNSGFOQWdaakd6MkVNZw?oc=5</t>
         </is>
       </c>
-      <c r="L146" s="8" t="inlineStr">
+      <c r="M146" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9380,26 +10111,31 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
+          <t>Трамп застеріг Нетаньяху від відновлення війни з Іраном, повідомляє Axios Reuters</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H147" s="8" t="inlineStr">
+      <c r="I147" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I147" s="8" t="inlineStr">
+      <c r="J147" s="8" t="inlineStr">
         <is>
           <t>США, Іран</t>
         </is>
       </c>
-      <c r="J147" s="8" t="inlineStr"/>
-      <c r="K147" s="10" t="inlineStr">
+      <c r="K147" s="8" t="inlineStr"/>
+      <c r="L147" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQdEppbGtCYUg1d2g4cVR1d3pxTDZVNFJKTV9sSm5xbEl0V19VQVVvMlZIYXFQeXRtbkZ5SnRVUjRmb19mdEg3bjMwNXZmMjJnT3pmODRIMGZkNGZyenhoYjQ3STlyeVZpNkNvODNoS25YM2pXd1JXaHpxaFNkeUQzWkU5aTMwR2JkanlfcXl0RkNnVVNpV1NkQS1IN2ZGWHBMX0FaeVY0YmJYUWF3ZEUxRWZqb01uUQ?oc=5</t>
         </is>
       </c>
-      <c r="L147" s="8" t="inlineStr">
+      <c r="M147" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9438,30 +10174,35 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
+          <t>Дженсен Хуанг розмовляє зі своїми постачальниками. Це хвилює Bloomberg</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H148" s="8" t="inlineStr">
+      <c r="I148" s="8" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I148" s="8" t="inlineStr">
+      <c r="J148" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J148" s="8" t="inlineStr">
+      <c r="K148" s="8" t="inlineStr">
         <is>
           <t>Обладнання, Технології</t>
         </is>
       </c>
-      <c r="K148" s="10" t="inlineStr">
+      <c r="L148" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPQnIxNG9WeE4tX3pYVWd6N2lpVE1Kc0lCcFc5ZExjQjZfSGVNcGV3RTdKYnZXbVZBQjlTV3JweTJWcG5BVjQ1WWNVcFRGNDhnOVFpNkFsdUVDRzhIamZkTzdfRExJWVFJdjhYOW5KYk5mTmV3enR1bXIyYThlaTRrMUdqUFktT0plcE1rTlgtbXFSMmNkYTlUalhtbWp4MnZQRmdpcHBFLTRjanNy?oc=5</t>
         </is>
       </c>
-      <c r="L148" s="8" t="inlineStr">
+      <c r="M148" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9500,22 +10241,27 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
+          <t>BofA попереджає, що настав час «фіксувати прибуток», оскільки червоні прапори множаться Bloomberg</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H149" s="8" t="inlineStr">
+      <c r="I149" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I149" s="8" t="inlineStr"/>
       <c r="J149" s="8" t="inlineStr"/>
-      <c r="K149" s="10" t="inlineStr">
+      <c r="K149" s="8" t="inlineStr"/>
+      <c r="L149" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcXFubGxGWVo1eUVsVlJOdXRzdE91ZHZIaTNKNFNLWnZDQV9sa3RaV3VqMnBDTlpfX1VuYVpublBTLVdBRnNMd25UUGhQV3cwUTNmaV9oZVhIR0ZNNGVhajB5Nk4zc2dEbEtqODFsNE9rcHhnUDBWUDExYncxa05NVG9DWUl0cDJqdlZOVS1IcEtZNDh0R0ozcVJCVlBWUlVPYWJiQncxeWRfZlMtRHc?oc=5</t>
         </is>
       </c>
-      <c r="L149" s="8" t="inlineStr">
+      <c r="M149" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9554,30 +10300,35 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
+          <t>США стверджують, що BYD, Baidu, Alibaba та інші технічні гіганти допомагають китайській армії Reuters</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H150" s="8" t="inlineStr">
+      <c r="I150" s="8" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I150" s="8" t="inlineStr">
+      <c r="J150" s="8" t="inlineStr">
         <is>
           <t>Китай, США</t>
         </is>
       </c>
-      <c r="J150" s="8" t="inlineStr">
+      <c r="K150" s="8" t="inlineStr">
         <is>
           <t>Обладнання</t>
         </is>
       </c>
-      <c r="K150" s="10" t="inlineStr">
+      <c r="L150" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPelJqSF9oSWNaaE56YnpwNkVadW83aHZ4OWNCWk40c21jTXF2T0l4dF94UmpiN0wyaHRoWUp2UXZ4NW9VVW1ERXJhRURTYkRQZnRycFZmMkoxMHdtblR2ZVNZcFVHTTV1NHFyQ1h1OUhkY2E2anBETkQySXlxeGd1cndQNlNzYzBXWkxJOUQ1WUlYamxfUFlCNFUyYThuM1I2MW9FTDJ6SHV2QngwYU9MOUFBRm4?oc=5</t>
         </is>
       </c>
-      <c r="L150" s="8" t="inlineStr">
+      <c r="M150" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9616,30 +10367,35 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
+          <t>Європейський індекс STOXX 600 закривається слабко, оскільки нафтове ралі згасає; Італійські банки в центрі уваги Reuters</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H151" s="8" t="inlineStr">
+      <c r="I151" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I151" s="8" t="inlineStr">
+      <c r="J151" s="8" t="inlineStr">
         <is>
           <t>Європа</t>
         </is>
       </c>
-      <c r="J151" s="8" t="inlineStr">
+      <c r="K151" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K151" s="10" t="inlineStr">
+      <c r="L151" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPQjhBTkhOWEdQZFY1SEtKbjloYTNvVVBRUmlzM1FLOHVSd2VZMXh6MEIwVFFHbTJnYmZCVmJhWWFVd2JGbE52VWREQnlnS0hBdzdpNjFqN3R3WTUtcmlUWkZybWZ1b01WMEFxUHpSaWQxVnZya3Juak5QTTM3ODJSQVdqTC1QejRHOGZua3RjRkcwVlp5Sm96MXNvbEdtTnR1bWhKNHVnNmlNQmM5a0d0bndIblF4NXM?oc=5</t>
         </is>
       </c>
-      <c r="L151" s="8" t="inlineStr">
+      <c r="M151" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9678,26 +10434,31 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
+          <t>Samsara каже, що будівництво центрів обробки даних, оновлення енергетичної мережі та інші пов’язані з державою інфраструктурні інвестиції стимулюють новий попит на її платформі. Нещодавні успіхи в бізнесі спонукали компанію, що займається телематикою та технікою безпеки автопарку, підвищити прогноз доходів і прибутків за весь рік. Компанія Samsara, що базується в Сан-Франциско (NYSE: IOT), повідомила про загальний дохід у розмірі 479 мільйонів доларів США, що на 31% більше, ніж у минулому році, за перший квартал 2027 фінансового року, що закінчився 2 травня. Вона додала 101 мільйон доларів США.</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H152" s="8" t="inlineStr">
+      <c r="I152" s="8" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I152" s="8" t="inlineStr"/>
-      <c r="J152" s="8" t="inlineStr">
+      <c r="J152" s="8" t="inlineStr"/>
+      <c r="K152" s="8" t="inlineStr">
         <is>
           <t>Обладнання</t>
         </is>
       </c>
-      <c r="K152" s="10" t="inlineStr">
+      <c r="L152" s="10" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/samsara-raises-guidance-amid-data-center-boom</t>
         </is>
       </c>
-      <c r="L152" s="8" t="inlineStr">
+      <c r="M152" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9736,30 +10497,35 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
+          <t>Підконтрольні державі енергетичні гіганти Китаю купують та імпортують найбільші обсяги зрідженого природного газу з початку війни в Ірані, оскільки найбільший у світі імпортер СПГ готується до пікового літнього попиту та спеки. Приватні покупці також активізують закупівлі, і Китай намагається компенсувати втрату катарського газу. Китайські імпортери СПГ зараз беруть від 7 до 10 вантажів на місяць, щоб замінити поставки з Катару, повідомили трейдери Bloomberg у понеділок. Частина СПГ Катару, яка була завантажена на вантажі be</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H153" s="8" t="inlineStr">
+      <c r="I153" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I153" s="8" t="inlineStr">
+      <c r="J153" s="8" t="inlineStr">
         <is>
           <t>Китай, Катар, Іран</t>
         </is>
       </c>
-      <c r="J153" s="8" t="inlineStr">
+      <c r="K153" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K153" s="10" t="inlineStr">
+      <c r="L153" s="10" t="inlineStr">
         <is>
           <t>https://oilprice.com/Latest-Energy-News/World-News/Chinas-LNG-Imports-Hit-Highest-Point-Since-Iran-War-Began.html</t>
         </is>
       </c>
-      <c r="L153" s="8" t="inlineStr">
+      <c r="M153" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9798,30 +10564,35 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
+          <t>Танкер загорівся біля узбережжя Оману в понеділок, що призвело до евакуації його екіпажу та спонукало до скоординованої реакції влади Оману та Індії, повідомляє...</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H154" s="8" t="inlineStr">
+      <c r="I154" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I154" s="8" t="inlineStr">
+      <c r="J154" s="8" t="inlineStr">
         <is>
           <t>Оман</t>
         </is>
       </c>
-      <c r="J154" s="8" t="inlineStr">
+      <c r="K154" s="8" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K154" s="10" t="inlineStr">
+      <c r="L154" s="10" t="inlineStr">
         <is>
           <t>https://gcaptain.com/crew-evacuated-after-tanker-fire-near-omans-masirah-island/</t>
         </is>
       </c>
-      <c r="L154" s="8" t="inlineStr">
+      <c r="M154" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9860,30 +10631,35 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
+          <t>ABS закликає регулюючі органи прийняти більш гнучкий підхід до системи скорочення викидів парникових газів Міжнародної морської організації, стверджуючи, що наявність палива та обмеження інфраструктури можуть ускладнити дотримання дедалі суворіших правил щодо викидів великим сегментам глобального флоту.</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
           <t>регуляторика</t>
         </is>
       </c>
-      <c r="H155" s="8" t="inlineStr">
+      <c r="I155" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I155" s="8" t="inlineStr">
+      <c r="J155" s="8" t="inlineStr">
         <is>
           <t>Глобально</t>
         </is>
       </c>
-      <c r="J155" s="8" t="inlineStr">
+      <c r="K155" s="8" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K155" s="10" t="inlineStr">
+      <c r="L155" s="10" t="inlineStr">
         <is>
           <t>https://gcaptain.com/abs-calls-for-more-flexible-imo-decarbonization-framework/</t>
         </is>
       </c>
-      <c r="L155" s="8" t="inlineStr">
+      <c r="M155" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9922,26 +10698,31 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
+          <t>У травні японські інвестори здійснили найбільший вихід з іноземних акцій за п'ять років Reuters</t>
+        </is>
+      </c>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H156" s="8" t="inlineStr">
+      <c r="I156" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I156" s="8" t="inlineStr">
+      <c r="J156" s="8" t="inlineStr">
         <is>
           <t>Японія</t>
         </is>
       </c>
-      <c r="J156" s="8" t="inlineStr"/>
-      <c r="K156" s="10" t="inlineStr">
+      <c r="K156" s="8" t="inlineStr"/>
+      <c r="L156" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQX2doWU1sbG43ejIwdHF5amlGUmhYa3VuSVR2cXh0WEY1QldfV2JVQ0FUSGVxbnU4a3RhUTJHNmF1b3NPbEQ0QmxvZ252clNUcmtXY1k5ZTlDWFRLR2F0ei05c0lLUmx6YXhwLXctSndHUUhoVWozSUE5VjF0N0xwQTVNVnFHVUZhbEVqQWs0ZGp0eXpmOEp5VVBoLUpTWWxpNGZDbjFZS0plRFZ2dEdGZkVDaE9ZT0hwOUE?oc=5</t>
         </is>
       </c>
-      <c r="L156" s="8" t="inlineStr">
+      <c r="M156" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -9980,26 +10761,31 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
+          <t>Індія повідомила про несподіване профіцит платіжного балансу в кварталі січня-березня Reuters</t>
+        </is>
+      </c>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H157" s="8" t="inlineStr">
+      <c r="I157" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I157" s="8" t="inlineStr">
+      <c r="J157" s="8" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J157" s="8" t="inlineStr"/>
-      <c r="K157" s="10" t="inlineStr">
+      <c r="K157" s="8" t="inlineStr"/>
+      <c r="L157" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQcl9aaTQ3eUlqNTltTUtnRGZnWlUtUWxmaVR5bExILVVibndIalFyQWgzRVRWM1hUaUpMcC00eHlSUUN6bkc0TmVERUg4bTFocnhjSVZMOVp0S1g0c1lfVXpiT3dCLWx1dEFmcTVjNm51aXA2MFpXUXM0Ni1CLXRUQThnS0h6YjV2Sl9qcGJFYW4tdUdReEgtMzlMVjJlRDRLVEwwVW5kQ01ULUhQX2JGcldR?oc=5</t>
         </is>
       </c>
-      <c r="L157" s="8" t="inlineStr">
+      <c r="M157" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10038,30 +10824,35 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
+          <t>Російська нафта отримує знижку в Індії вперше за два місяці Bloomberg</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H158" s="8" t="inlineStr">
+      <c r="I158" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I158" s="8" t="inlineStr">
+      <c r="J158" s="8" t="inlineStr">
         <is>
           <t>Росія, Індія</t>
         </is>
       </c>
-      <c r="J158" s="8" t="inlineStr">
+      <c r="K158" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K158" s="10" t="inlineStr">
+      <c r="L158" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOWC12azhMTWFSbjhyN0Q2QXA0RXJpeE12QkZacGRMRjRRSmNfTDludEpwVk1mSWQ0Z0kwUEg3TWFzRVpzay1vZkFIbnhEZ183aUtLUWRoMVJkU1NfMXlqc2dValJaU05YTjNmaC1oSFBEVGdXVmRtMjRiNnBheEQtQXh0VVVkMVBCTm9SZ0t1XzBBNmFLQjBQZUN2U3dLSUpwLUFXb0wxM1FzMWUxSE91M1dBTXVjUQ?oc=5</t>
         </is>
       </c>
-      <c r="L158" s="8" t="inlineStr">
+      <c r="M158" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10100,30 +10891,35 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
+          <t>Мідь відновлюється після падіння в п'ятницю через купівлю в Китаї та потоки США Bloomberg</t>
+        </is>
+      </c>
+      <c r="H159" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H159" s="8" t="inlineStr">
+      <c r="I159" s="8" t="inlineStr">
         <is>
           <t>Вит.матеріали/МШП</t>
         </is>
       </c>
-      <c r="I159" s="8" t="inlineStr">
+      <c r="J159" s="8" t="inlineStr">
         <is>
           <t>Китай, США</t>
         </is>
       </c>
-      <c r="J159" s="8" t="inlineStr">
+      <c r="K159" s="8" t="inlineStr">
         <is>
           <t>Метали</t>
         </is>
       </c>
-      <c r="K159" s="10" t="inlineStr">
+      <c r="L159" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPZ0p3NXR1TnJwMng1d1RHbDU2X0dZYU13TXpYMUhwYldjaE4tRVZpdXV4cVhKZXg2UjRycEJTVHZCaXp5QUJ5YWU2bDkzcHdwTktxTXFZTVVscmJKMklxaHVWeWNYa3BuNDQ0blg4QU5tY2VsRUFXN0tSVFMwdnZ5bWI3dHpOWXdrRkIxemZ6S2hpOElkdTZRdUZ2ckNaNmp4bE1CSG5JQU9mM3FQd3BMZFdIdw?oc=5</t>
         </is>
       </c>
-      <c r="L159" s="8" t="inlineStr">
+      <c r="M159" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10162,30 +10958,35 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
+          <t>Італійська велика компанія Eni та малайзійська державна компанія Petronas створили Searah, нове спільне підприємство 50-50, що об’єднує ключові підприємства в Індонезії та Малайзії. СП було офіційно створено через сім місяців після підписання інвестиційної угоди в листопаді 2025 року та через 16 місяців після Меморандуму про взаєморозуміння в лютому 2025 року. Весь персонал Eni Indonesia та Petronas Indonesia …</t>
+        </is>
+      </c>
+      <c r="H160" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H160" s="8" t="inlineStr">
+      <c r="I160" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I160" s="8" t="inlineStr">
+      <c r="J160" s="8" t="inlineStr">
         <is>
           <t>Індонезія, Малайзія</t>
         </is>
       </c>
-      <c r="J160" s="8" t="inlineStr">
+      <c r="K160" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K160" s="10" t="inlineStr">
+      <c r="L160" s="10" t="inlineStr">
         <is>
           <t>https://splash247.com/eni-and-petronas-create-southeast-asia-upstream-powerhouse/</t>
         </is>
       </c>
-      <c r="L160" s="8" t="inlineStr">
+      <c r="M160" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10224,30 +11025,35 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
+          <t>Agentic AI збирається перейти з периферії програмного забезпечення ланцюга постачання до мейнстріму. Перевізники отримають вигоду від тих, хто посилить свої дані про швидкість прямо зараз Gartner очікує, що впровадження агентського штучного інтелекту в програмному забезпеченні ланцюга поставок підприємством зросте з 5% сьогодні до 60% до 2030 року. Це швидка крива, і вона розділить пересилачів на дві групи: тих, чиї дані готові для роботи зі штучним інтелектом, і ... Повідомлення Перемоги пересилачів за допомогою штучного інтелекту почали з міцної основи ставок, вперше з’явилося на The Loadstar</t>
+        </is>
+      </c>
+      <c r="H161" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H161" s="8" t="inlineStr">
+      <c r="I161" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I161" s="8" t="inlineStr">
+      <c r="J161" s="8" t="inlineStr">
         <is>
           <t>глобально</t>
         </is>
       </c>
-      <c r="J161" s="8" t="inlineStr">
+      <c r="K161" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K161" s="10" t="inlineStr">
+      <c r="L161" s="10" t="inlineStr">
         <is>
           <t>https://theloadstar.com/the-forwarders-winning-with-ai-started-with-a-solid-rate-foundation/</t>
         </is>
       </c>
-      <c r="L161" s="8" t="inlineStr">
+      <c r="M161" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10286,30 +11092,35 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
+          <t>Литовський національний оператор залізничних вантажних перевезень LTG Cargo отримав сертифікат для вантажних залізничних перевезень у Німеччині через свою дочірню компанію LTG Cargo Polska. Тепер він може самостійно надавати послуги без посередників. Генеральний директор LTG Cargo Polska Лаймонас Некрошюс каже, що сертифікація призведе до більш ефективних і ефективних транспортних послуг для його компанії. «Перевагою LTG Cargo Polska як перевізника є ефективне транспортування вантажів між Польщею, Україною та країнами Балтії,</t>
+        </is>
+      </c>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H162" s="8" t="inlineStr">
+      <c r="I162" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I162" s="8" t="inlineStr">
+      <c r="J162" s="8" t="inlineStr">
         <is>
           <t>Литва, Польща, Німеччина</t>
         </is>
       </c>
-      <c r="J162" s="8" t="inlineStr">
+      <c r="K162" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K162" s="10" t="inlineStr">
+      <c r="L162" s="10" t="inlineStr">
         <is>
           <t>https://www.railfreight.com/railfreight/2026/06/08/ltg-cargo-cleared-for-rail-operations-in-germany/</t>
         </is>
       </c>
-      <c r="L162" s="8" t="inlineStr">
+      <c r="M162" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10348,30 +11159,35 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
+          <t>У тваринницькому краї Техасу власники скотарів сумніваються, чи може Міністерство сільського господарства США боротися з м’ясоїдними хробаками Reuters</t>
+        </is>
+      </c>
+      <c r="H163" s="8" t="inlineStr">
+        <is>
           <t>здоров'я_біобезпека</t>
         </is>
       </c>
-      <c r="H163" s="8" t="inlineStr">
+      <c r="I163" s="8" t="inlineStr">
         <is>
           <t>Покупні корми тваринництво</t>
         </is>
       </c>
-      <c r="I163" s="8" t="inlineStr">
+      <c r="J163" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J163" s="8" t="inlineStr">
+      <c r="K163" s="8" t="inlineStr">
         <is>
           <t>Сільськогосподарська продукція</t>
         </is>
       </c>
-      <c r="K163" s="10" t="inlineStr">
+      <c r="L163" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNenFocUxvWmFCSTJnZ0QzeUJhaUZMYXJzM3JUNUtjODl1NjR2ZVZGNXhBQ2I2RWh5dUhMencyb2hHaFdjMlBLQlJKczhYd2x5VGdDbno0b08yTC1ELTZuS3k0eUNaQWRCWVdOdFRtcTEtOG9VNkVzTzN4ZWxuYnZBZjJ0MVB0RHIxbWI4WGplUG5XYWd0YklvX3ItVzlVdjFxX3AwVW94eE9ZODVsOUNDLWM1V2xfTWN3Ql9UNkdOR3c5THk2aTM2Tkdad2VpQlN1TEtMN0lOekhiZw?oc=5</t>
         </is>
       </c>
-      <c r="L163" s="8" t="inlineStr">
+      <c r="M163" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10410,30 +11226,35 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
+          <t>ОАЕ продають великі обсяги нафти в Перській затоці для завантаження в найближчі місяці Bloomberg</t>
+        </is>
+      </c>
+      <c r="H164" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H164" s="8" t="inlineStr">
+      <c r="I164" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I164" s="8" t="inlineStr">
+      <c r="J164" s="8" t="inlineStr">
         <is>
           <t>ОАЕ</t>
         </is>
       </c>
-      <c r="J164" s="8" t="inlineStr">
+      <c r="K164" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K164" s="10" t="inlineStr">
+      <c r="L164" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTV9xcUdHRHEtTF9MNGprUnk2X053V2hBVVBUaWhDNktGS21scGhzZHBSOUxROENIRUlEWi15X01xYl9LT3o0VGwyWVYwdFJuZFA5SlV2VnRoR2J4MGlPR0kwOG0wRFhKcVFMUy0tdWoxdGVyZWFFT0ZfdmZhQzI2RzVSdUE2cXVfR0ZQZmQ3Q3dqUDN2YzlZSWhlZTVJOHBNR1dZbFJVRHdXSFNpTVhQdXRleTlpUQ?oc=5</t>
         </is>
       </c>
-      <c r="L164" s="8" t="inlineStr">
+      <c r="M164" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10472,30 +11293,35 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
+          <t>Чому війна Трампа не зламала економіку Ірану Bloomberg</t>
+        </is>
+      </c>
+      <c r="H165" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H165" s="8" t="inlineStr">
+      <c r="I165" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I165" s="8" t="inlineStr">
+      <c r="J165" s="8" t="inlineStr">
         <is>
           <t>Іран</t>
         </is>
       </c>
-      <c r="J165" s="8" t="inlineStr">
+      <c r="K165" s="8" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K165" s="10" t="inlineStr">
+      <c r="L165" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNbHE1eHFhZkJfUVVEdmdaZ3Mzb1Vrekw2b1FLMDJNWnN3SUR1T2JJcWFRSHhMYjhKRWhyMG4xd29BcVV4a3FNTzliRDlSd2ZUV1ptZXFmdmtsQ19ZQ291R19qOER5UlBDTWJLVTZWOC1kM2ZZUlR3eUh5Z0xRUDFnWjVNRkRKRzZNVWVFUHZxOWdVM2RiVU5NVGlIXzdSSjRzQ29GWUU0WjE?oc=5</t>
         </is>
       </c>
-      <c r="L165" s="8" t="inlineStr">
+      <c r="M165" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10534,30 +11360,35 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
+          <t>США висувають доріку Ірану через зникнення урану після початку бомбардувань Bloomberg</t>
+        </is>
+      </c>
+      <c r="H166" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H166" s="8" t="inlineStr">
+      <c r="I166" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I166" s="8" t="inlineStr">
+      <c r="J166" s="8" t="inlineStr">
         <is>
           <t>Іран, США</t>
         </is>
       </c>
-      <c r="J166" s="8" t="inlineStr">
+      <c r="K166" s="8" t="inlineStr">
         <is>
           <t>Логістика, Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K166" s="10" t="inlineStr">
+      <c r="L166" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOcU1BTTV0TDBsMXNtTzVsRXZVUUs5NG9hZkRqNHFNS09iQlk1MjRSVmEzQkJCRVlEMFdmbU5qOTlLS1ZZN0hrZ0tZZDI0NjNzWTRmS3lVSl9EeU5oRnpFaEE1VS1CZkU2MEE3YzdwYl9pcUVRUFpxUW5YYXZxSlNsYlpPdW1QOF9XVkd4RlpOalEzd2hWWnZPOXpHaWpjSGRmZUJXbEh1TXhzVXRQdFFTRWhuc0Y?oc=5</t>
         </is>
       </c>
-      <c r="L166" s="8" t="inlineStr">
+      <c r="M166" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10596,30 +11427,35 @@
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
+          <t>Cosco використовуватиме новий іспанський портовий термінал для імпорту автомобілів з Китаю Bloomberg</t>
+        </is>
+      </c>
+      <c r="H167" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H167" s="8" t="inlineStr">
+      <c r="I167" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I167" s="8" t="inlineStr">
+      <c r="J167" s="8" t="inlineStr">
         <is>
           <t>Іспанія, Китай</t>
         </is>
       </c>
-      <c r="J167" s="8" t="inlineStr">
+      <c r="K167" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K167" s="10" t="inlineStr">
+      <c r="L167" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQZWdTYmc1eWpNWkViSzZiVk00YWtOWnFYWDliSUpxZVZqRVp5WW1hU0ZSUHYyejhMQVBxNU5qdm9uUGtQN3hDRVJFZDRaUmlWandOTmJnak9odXcwSF9KclczZWRhcW9kYXh5cW05VmZ2dk4wamNvaUloWGRFQ2VhQjN0UUNJeUpWYlVsYU1BZjg1ekwwQ05GOHpsNjVYVndSVlhLMFpfXzU4YnA5dHRRaXdac1F0Zw?oc=5</t>
         </is>
       </c>
-      <c r="L167" s="8" t="inlineStr">
+      <c r="M167" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10658,30 +11494,35 @@
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
+          <t>Японія та Філіппіни в нещодавній спільній заяві підкреслили свою прихильність створенню нових і вдосконалених залізничних вантажних перевезень на філіппінському острові Лусон. Модернізація залізниць і портів є ключовими сферами в обіцянці поглибити співпрацю щодо високоефективної інфраструктури та економічних ініціатив у рамках Лусонського економічного коридору (LEC). Країни підкреслили свою «відданість перетворенню LEC в економічний центр світового класу, який зміцнює глобальні ланцюги поставок, прискорює економічний розвиток.</t>
+        </is>
+      </c>
+      <c r="H168" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H168" s="8" t="inlineStr">
+      <c r="I168" s="8" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I168" s="8" t="inlineStr">
+      <c r="J168" s="8" t="inlineStr">
         <is>
           <t>Філіппіни, Японія</t>
         </is>
       </c>
-      <c r="J168" s="8" t="inlineStr">
+      <c r="K168" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K168" s="10" t="inlineStr">
+      <c r="L168" s="10" t="inlineStr">
         <is>
           <t>https://www.railfreight.com/infrastructure/2026/06/08/japan-and-philippines-underlined-commitment-to-lec-development/</t>
         </is>
       </c>
-      <c r="L168" s="8" t="inlineStr">
+      <c r="M168" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10720,26 +11561,31 @@
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
+          <t>У квітні промислові замовлення в Німеччині впали більше, ніж очікувалося Reuters</t>
+        </is>
+      </c>
+      <c r="H169" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H169" s="8" t="inlineStr">
+      <c r="I169" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I169" s="8" t="inlineStr">
+      <c r="J169" s="8" t="inlineStr">
         <is>
           <t>Німеччина</t>
         </is>
       </c>
-      <c r="J169" s="8" t="inlineStr"/>
-      <c r="K169" s="10" t="inlineStr">
+      <c r="K169" s="8" t="inlineStr"/>
+      <c r="L169" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOdnl4RDNFN1h6VTVXSjI2REtKb1R6YzBheDFsTG1TTEpmZEd4eUxBcmlXbVhtbmpZX1JHdTFyUGx0RldQdXlkV2txbkpERG02MFp2LXFoVUttbFBUV0dGaFlrT3FrRGF0UDJnRXBjZk1CT0RLTEtzS0hjd2dqaUREMDFKN2JFcEVkVGNV?oc=5</t>
         </is>
       </c>
-      <c r="L169" s="8" t="inlineStr">
+      <c r="M169" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10778,26 +11624,31 @@
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
+          <t>Віце-керівник центрального банку В’єтнаму каже, що країна буде орієнтуватися на фіскальну політику, щоб досягти мети зростання Reuters</t>
+        </is>
+      </c>
+      <c r="H170" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H170" s="8" t="inlineStr">
+      <c r="I170" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I170" s="8" t="inlineStr">
+      <c r="J170" s="8" t="inlineStr">
         <is>
           <t>В'єтнам</t>
         </is>
       </c>
-      <c r="J170" s="8" t="inlineStr"/>
-      <c r="K170" s="10" t="inlineStr">
+      <c r="K170" s="8" t="inlineStr"/>
+      <c r="L170" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPVGtkUzZLTTYtZTBCYkJxWnBRc19MTXFOUDEwZ0FqclJuM3lyOHBkZjE5SXgtWkYxTjVBRlhoQ2FidTlRNEZDQnRRaTF6NXB2bWZpRVRubkFZX29qWHJ4MUtUbnprVVZRNmtxb0NPYW0yVE01SDdKR21idUFlV2FHdXBJMXlycTNxalVGVU1ucDZsZ3V6bi0zb3psaTRFRlZQeW1SS0RtQVpIQnc2MkFpN1dFVDh1QVRsUXFKb2pPZ3pzcWZwUFA0Q3FFWVk?oc=5</t>
         </is>
       </c>
-      <c r="L170" s="8" t="inlineStr">
+      <c r="M170" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10836,22 +11687,27 @@
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
+          <t>Голова МВФ: Ми не можемо повторити помилки глобалізації з AI Bloomberg</t>
+        </is>
+      </c>
+      <c r="H171" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H171" s="8" t="inlineStr">
+      <c r="I171" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I171" s="8" t="inlineStr"/>
       <c r="J171" s="8" t="inlineStr"/>
-      <c r="K171" s="10" t="inlineStr">
+      <c r="K171" s="8" t="inlineStr"/>
+      <c r="L171" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNMWY2YUV1aHNiZ0Q5UW84TFBsTF8yOVZFa0NTX0hjcmtqQTF3bEZhTGpJS0NCdHBZajdFa3l1ME9xVjNnUkVmUUxkdU5UeEpuRGN0S1dxbG1vY2xOd3liN0dURm1DNjdkNjNzOW0yYUhzYW1VbDBCSUswMWw0WDl4TVV5LUJLdHVBa3g4U0VqR2hValdwX2hrYzJCRFVmR3dvYTV1M3BES0w2SXRYLVd5QUh3?oc=5</t>
         </is>
       </c>
-      <c r="L171" s="8" t="inlineStr">
+      <c r="M171" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10890,26 +11746,31 @@
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
+          <t>ЄЦБ ризикує повторити помилку 2011 року з підвищенням ставок, попереджають економісти Bloomberg</t>
+        </is>
+      </c>
+      <c r="H172" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H172" s="8" t="inlineStr">
+      <c r="I172" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I172" s="8" t="inlineStr">
+      <c r="J172" s="8" t="inlineStr">
         <is>
           <t>ЄС</t>
         </is>
       </c>
-      <c r="J172" s="8" t="inlineStr"/>
-      <c r="K172" s="10" t="inlineStr">
+      <c r="K172" s="8" t="inlineStr"/>
+      <c r="L172" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPaXh0LUNZOW0zdmJ3bEtCM1Axd25TcUZYcDlSN3RhUTdFTUQzcTExVDM2dnNGeThlQ3FfZnJJNXJ0WHhmWlBHVHlONWJaQWE3UjQweGpwZXM3MVJYaE9xWFdidDRlTEZFTGNuWlE3UGZuWEZmTkNvdkxwd0xUbDlDMWF3V0xvYVM2QV9aS3owYm5iZlF0ZG9yTkhCNmxhVkE3R0h4VnJrNmVfM21jV0FvOUVqSkI?oc=5</t>
         </is>
       </c>
-      <c r="L172" s="8" t="inlineStr">
+      <c r="M172" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -10948,30 +11809,35 @@
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
+          <t>Nvidia та SK Hynix підписали багаторічну угоду про розробку чіпів AI Bloomberg</t>
+        </is>
+      </c>
+      <c r="H173" s="8" t="inlineStr">
+        <is>
           <t>не_релевантно</t>
         </is>
       </c>
-      <c r="H173" s="8" t="inlineStr">
+      <c r="I173" s="8" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I173" s="8" t="inlineStr">
+      <c r="J173" s="8" t="inlineStr">
         <is>
           <t>США, Південна Корея</t>
         </is>
       </c>
-      <c r="J173" s="8" t="inlineStr">
+      <c r="K173" s="8" t="inlineStr">
         <is>
           <t>Технології</t>
         </is>
       </c>
-      <c r="K173" s="10" t="inlineStr">
+      <c r="L173" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOOEZ4dzJPVGhvWnBvWlJvaHpaLTk3Y3BVajV2OG03QkFhMERtdVJMMGhuNFZzZjdOaW8zaUV2THJNTDZ5YTFaM1ZHYTh0Yy0tOUFxTHpnM2h3cEdLZU9qcEFxd0dQTkJFYmRDX0FBMzFlcjQtcWtkRDRFLTJNNDU5WVhnbDBtN1d0SEUyR0dPc3JrUFBBUjdyT2ZvWXZVbUh4RVNFTU81dC1pbl9rVnZjOXI0NA?oc=5</t>
         </is>
       </c>
-      <c r="L173" s="8" t="inlineStr">
+      <c r="M173" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11010,26 +11876,31 @@
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
+          <t>Економіка Японії охолоджується через низькі капіталовкладення в I кварталі, показують переглянуті дані Reuters</t>
+        </is>
+      </c>
+      <c r="H174" s="8" t="inlineStr">
+        <is>
           <t>не_релевантно</t>
         </is>
       </c>
-      <c r="H174" s="8" t="inlineStr">
+      <c r="I174" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I174" s="8" t="inlineStr">
+      <c r="J174" s="8" t="inlineStr">
         <is>
           <t>Японія</t>
         </is>
       </c>
-      <c r="J174" s="8" t="inlineStr"/>
-      <c r="K174" s="10" t="inlineStr">
+      <c r="K174" s="8" t="inlineStr"/>
+      <c r="L174" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNZDkwZWctbDBjcVY4UkNNdXFZc1U1MVV0N3JaSHZXc2Y0VloyNWdIYlVBa3ZUeF91TU1fejR2WTFhellMRGJKM1N3SzNNM2s4Mk14dGdOcENGN1MzT2pack92NlFDTVp6QVBDazM3Z0wtY05KOVl1Q3Q4My1pdmFZYm5UT3RlQUtyQTZja1RDb1pkYmhUb3NkZWdDcExVWTczdVktRFlRSQ?oc=5</t>
         </is>
       </c>
-      <c r="L174" s="8" t="inlineStr">
+      <c r="M174" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11068,26 +11939,31 @@
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
+          <t>Заощаджувачі материкового Китаю стікаються до Гонконгу, оскільки регулятори посилюють контроль над капіталом Reuters</t>
+        </is>
+      </c>
+      <c r="H175" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H175" s="8" t="inlineStr">
+      <c r="I175" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I175" s="8" t="inlineStr">
+      <c r="J175" s="8" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J175" s="8" t="inlineStr"/>
-      <c r="K175" s="10" t="inlineStr">
+      <c r="K175" s="8" t="inlineStr"/>
+      <c r="L175" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNUVBrd0Uxb3N0YW1KdzY3Y1FMMkJXS0JRazNZLTkwZThmRUZGZ1d6WmdSV2x3Z0UwTGxlQzVIYjdnNFhROEtMNnBKeTYxU0pLbUxUZFlOa19OaVctMjhlQjZQdWhOdWtBZTJPRDZqS2hKcDNwX3BnOWpUV3k3UVltNk1tcVR3S0pJMENsV3M0dlRuSHVUVUNtbE56UGJpU0pVV0tTeVJxVi1FY0ppVTg5eW93RkdPSS1ZVy1nY1pzajFJbDUxMFZzVWp3?oc=5</t>
         </is>
       </c>
-      <c r="L175" s="8" t="inlineStr">
+      <c r="M175" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11126,26 +12002,31 @@
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
+          <t>Ф'ючерси на акції США впали після розпродажу технологій, зростання нафти: звіт ринків Bloomberg</t>
+        </is>
+      </c>
+      <c r="H176" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H176" s="8" t="inlineStr">
+      <c r="I176" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I176" s="8" t="inlineStr">
+      <c r="J176" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J176" s="8" t="inlineStr"/>
-      <c r="K176" s="10" t="inlineStr">
+      <c r="K176" s="8" t="inlineStr"/>
+      <c r="L176" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPaS1YdVJWMW1Gc2Y0ZzZycEh6SThkdUozVlROTTZSQ2pNWWRBeEs5N01ZcGZIMmZMRnY1Qk9iNmZhUUh0MDNKMDdEUzdBTHBER09yb3daVDRjRGRWUFFaYTJ5bEJac09ja2ptWTBaTUtHa1FwVmo0Vk91cWVuTlM0OXlxNy1Xd2d2RnZCdGRPN2xDUGNtbkY0ZUtLZS1xbnNIeEo3cFBTVzE1Z0xfQXRQZA?oc=5</t>
         </is>
       </c>
-      <c r="L176" s="8" t="inlineStr">
+      <c r="M176" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11184,26 +12065,31 @@
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
+          <t>Іран відкидає ідею використання своїх активів для відшкодування збитків союзникам США Reuters</t>
+        </is>
+      </c>
+      <c r="H177" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H177" s="8" t="inlineStr">
+      <c r="I177" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I177" s="8" t="inlineStr">
+      <c r="J177" s="8" t="inlineStr">
         <is>
           <t>Іран</t>
         </is>
       </c>
-      <c r="J177" s="8" t="inlineStr"/>
-      <c r="K177" s="10" t="inlineStr">
+      <c r="K177" s="8" t="inlineStr"/>
+      <c r="L177" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOWENyVGtVLV9tWVN5M3FuNkRxRFlGcmNoM3Q0Y0huOVZrUjdvYnplcDRqNU1HMS1OdkZSVHR5QlRQXzV1QllZZ3RscUpFQmhUWktKVnFaWndQRzd6R2hBRTZkbzJ2OVQ5UXVfT1V0WkhsQk5DZ3hQbUtib21NSlV6NElQTzZ3RWVpbXlTRE5xN3U5TUMxdkRUbzF4TnhHenhXVWJhbEQwR0FOQ3ZodGc?oc=5</t>
         </is>
       </c>
-      <c r="L177" s="8" t="inlineStr">
+      <c r="M177" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11242,26 +12128,31 @@
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
+          <t>Трамп каже, що підвищення ставки ФРС було б неправильним напередодні дебюту Warsh Bloomberg</t>
+        </is>
+      </c>
+      <c r="H178" s="8" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H178" s="8" t="inlineStr">
+      <c r="I178" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I178" s="8" t="inlineStr">
+      <c r="J178" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J178" s="8" t="inlineStr"/>
-      <c r="K178" s="10" t="inlineStr">
+      <c r="K178" s="8" t="inlineStr"/>
+      <c r="L178" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxORWZocVJMa2IydlNzZklaLVozdVlhNEx4djhkOXdfT0VzM0M0VnU4NmJJekc2dFBWM08xNDhhdEY4eTdpd1BEUFBHR1FseERocDVSWFBHdFdNQ1FLMlF6dHVZa2ZiaVd6YkpJOENDZVJyeDhZV0lxaDAyekcxLVNZa19iRTZmOE93YWN3NnIwNFF4QWd6YjVoNFNPOEctQ1JtdC1wTG5WX2pKWDdmdF9ZMHhCZWg?oc=5</t>
         </is>
       </c>
-      <c r="L178" s="8" t="inlineStr">
+      <c r="M178" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11300,26 +12191,31 @@
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
+          <t>Європейські лідери готові підтримати переговори про припинення вогню між Україною та Росією Reuters</t>
+        </is>
+      </c>
+      <c r="H179" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H179" s="8" t="inlineStr">
+      <c r="I179" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I179" s="8" t="inlineStr">
+      <c r="J179" s="8" t="inlineStr">
         <is>
           <t>Україна, Росія, ЄС</t>
         </is>
       </c>
-      <c r="J179" s="8" t="inlineStr"/>
-      <c r="K179" s="10" t="inlineStr">
+      <c r="K179" s="8" t="inlineStr"/>
+      <c r="L179" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZjRUNmJIWk5NM3pWZURGaWt0Sm1FZWlzT0FFQTBfNkZWaGxsZjhzb2tpM0RvSnhUZEY5YVpSUmxlMUh0VkNKVjFDRnFVbjloajRBVWlpbUs4OGxHVWZMWUdQbzI4S3ZzMjBQTFpfWVRzZWxVQUlZWHBLUjJnSVo2T3o2MGNGb1FPbERwQ05KVmlRNkJud0Rz?oc=5</t>
         </is>
       </c>
-      <c r="L179" s="8" t="inlineStr">
+      <c r="M179" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11358,30 +12254,35 @@
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
+          <t>Контракт про поглиблення аргентинської річки оголює суперництво між США та Китаєм Bloomberg</t>
+        </is>
+      </c>
+      <c r="H180" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H180" s="8" t="inlineStr">
+      <c r="I180" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="I180" s="8" t="inlineStr">
+      <c r="J180" s="8" t="inlineStr">
         <is>
           <t>США, Китай, Аргентина</t>
         </is>
       </c>
-      <c r="J180" s="8" t="inlineStr">
+      <c r="K180" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K180" s="10" t="inlineStr">
+      <c r="L180" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOYWR0a1JtQjl4QmhyNy1NOEE3bTM5TTJSQ0xzZEVPM0lIZVBmampqYlNvQjA5R0I5N3FSLTY4cllzRkRaaE1KcHBWLWRsRlBJcGhrQ3JuaGJVSlJkQXhvV1Rfc3h4Y0s0eEhnRjRlTUVTRF96WlZnR0VHZHg5TndENGtoSHpkdEFyY1c1eXpKbHhDTUhPR09vTHFURUVGNDZSRmUyMXBTam9wVEtYYzlKeEZrZ2hoRDU5VkM2c0JwYThXZw?oc=5</t>
         </is>
       </c>
-      <c r="L180" s="8" t="inlineStr">
+      <c r="M180" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11420,30 +12321,35 @@
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
+          <t>Споживачі в США переосмислюють свої витрати від роздрібних торговців: від незаповнених бензобаків до меншої кількості надмірностей AP News</t>
+        </is>
+      </c>
+      <c r="H181" s="8" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H181" s="8" t="inlineStr">
+      <c r="I181" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I181" s="8" t="inlineStr">
+      <c r="J181" s="8" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J181" s="8" t="inlineStr">
+      <c r="K181" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K181" s="10" t="inlineStr">
+      <c r="L181" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNdWRzM3lwbmNVb2V2b19LTTZNeEIwWjI3Q0ExLVdJb0NNVkhmLWE1dnZ3UmloVlg4R1BHQlBDQUVkODlfM053Y1hGanhTNVRSSDl6SFdLRFJpUnNsbXBBMXZ5bjVHQ19kX3pWeFpEMTVIS2xqbDNwLVJlN045Ul9aVnV0Q0dla0IzU0M2WEJkaWRwYkVFSks5TmJIMA?oc=5</t>
         </is>
       </c>
-      <c r="L181" s="8" t="inlineStr">
+      <c r="M181" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11482,30 +12388,35 @@
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
+          <t>Etihad Airways замовляє широкофюзеляжні літаки, повертається до довоєнних потужностей у червні Reuters</t>
+        </is>
+      </c>
+      <c r="H182" s="8" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H182" s="8" t="inlineStr">
+      <c r="I182" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="I182" s="8" t="inlineStr">
+      <c r="J182" s="8" t="inlineStr">
         <is>
           <t>ОАЕ</t>
         </is>
       </c>
-      <c r="J182" s="8" t="inlineStr">
+      <c r="K182" s="8" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K182" s="10" t="inlineStr">
+      <c r="L182" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQc1J3bHVhc0NLSUNlWTdBZHJHaDRIU1pYTUZLQzd0VlVveW5xM0FTcFBzU3hGTzd1T2dlN1FJSDB5ak1zV2RFTGNYTkxGSlRfcW1MWDU3NHQ5RzhkNmRzc1VGb0JucVdaZmJ5eWVJeWt4aTh2VzZOVnU0eENmZGlMWTU2eEdvM1N3dlNZc3k0NGNtMWlEUHl3WEZvQTl3aTUtQWFNYjVTUEloZHF3ZW4xX3Y5UHhiVV92TGJIOGcwdGJNOTl2aVItRVV3dDBXeFk?oc=5</t>
         </is>
       </c>
-      <c r="L182" s="8" t="inlineStr">
+      <c r="M182" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11544,30 +12455,35 @@
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
+          <t>США дають угорській MOL додатковий час для переговорів щодо купівлі сербської нафтової компанії NIS Reuters</t>
+        </is>
+      </c>
+      <c r="H183" s="8" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H183" s="8" t="inlineStr">
+      <c r="I183" s="8" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I183" s="8" t="inlineStr">
+      <c r="J183" s="8" t="inlineStr">
         <is>
           <t>Угорщина, Сербія</t>
         </is>
       </c>
-      <c r="J183" s="8" t="inlineStr">
+      <c r="K183" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K183" s="10" t="inlineStr">
+      <c r="L183" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNcGstRlVEVW9tUVFiT0pFTGEtSkoxMl85amlKb3IwZm9hdERaaW04V2FZN2ZBbkRnZDZ5bTVxMG1qcEdIblkxSDA4Z3E5WGdreEt4X0s1YkRDSTRYTHJDR2JVVDgzWVRFSm5hY0NfTUNDd2dPTE9tZGE0azVWbXpkTGVvVHp6YWwyX1R5Rk1ISVV3X2ZlU0tZczViVUx0NEpXNlBrYUVyMmlHTnZuNmw5eGFiWEg?oc=5</t>
         </is>
       </c>
-      <c r="L183" s="8" t="inlineStr">
+      <c r="M183" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11606,30 +12522,35 @@
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
+          <t>Другий тур президентських виборів у Колумбії може вплинути на майбутнє тропічних лісів Амазонки та викопного палива AP News</t>
+        </is>
+      </c>
+      <c r="H184" s="8" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H184" s="8" t="inlineStr">
+      <c r="I184" s="8" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I184" s="8" t="inlineStr">
+      <c r="J184" s="8" t="inlineStr">
         <is>
           <t>Колумбія</t>
         </is>
       </c>
-      <c r="J184" s="8" t="inlineStr">
+      <c r="K184" s="8" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K184" s="10" t="inlineStr">
+      <c r="L184" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOTUFxV0NPX0FRNnJrRllzYm5sWDBtdzYtbnFCdlVrVE16eWhxbFFWbXR0bFRidVJZQjNBaFQ4cDBjV3Y5aXl4ZXZVMThETTdLRHNLaVdJVkxKX3RXSm9saHFqR0UteUJsa3YzMFBZOVl1VWt4Z3dSdVpmdmdoRUYyMzBCZ2wybVdNOGh4NTZtYk1YT19ZY1E0SFhTSXU3Tll2WjAtWmdKSTZyQ1NHMzJlZXJELVp4NjNjVTgzdnNNNHM?oc=5</t>
         </is>
       </c>
-      <c r="L184" s="8" t="inlineStr">
+      <c r="M184" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11668,30 +12589,35 @@
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
+          <t>Китайський виробник акумуляторів CATL очікує, що накопичувачі енергії становитимуть половину світових продажів до 2030 року Reuters</t>
+        </is>
+      </c>
+      <c r="H185" s="8" t="inlineStr">
+        <is>
           <t>не_релевантно</t>
         </is>
       </c>
-      <c r="H185" s="8" t="inlineStr">
+      <c r="I185" s="8" t="inlineStr">
         <is>
           <t>НМА</t>
         </is>
       </c>
-      <c r="I185" s="8" t="inlineStr">
+      <c r="J185" s="8" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J185" s="8" t="inlineStr">
+      <c r="K185" s="8" t="inlineStr">
         <is>
           <t>Технології</t>
         </is>
       </c>
-      <c r="K185" s="10" t="inlineStr">
+      <c r="L185" s="10" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQc0h2SWtZckhIbjQ1V2VLZTVVQUhfeVNid3hxZ0xVR1RoWnl5TmhGajJWQ2l5bExiUGhMdVd2ZkJYRGJxLURhc19FcnhfOWpJUEV0VHlBZ0dESWFtTlpfN1VrMVJZNndUTXNjREY4Q0QwR1NteTZPM1BOcTdMVnhGQTZjT1FqbUU0Rk5pV0ZoX09kODczNWRGUDRNU29qVEJINGZ2YWpYcHBCeHFWM0xXS3FxSGtZQVVUaVliYm9BX2R2ZHp1RzVaX0JR?oc=5</t>
         </is>
       </c>
-      <c r="L185" s="8" t="inlineStr">
+      <c r="M185" s="8" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11730,30 +12656,35 @@
       </c>
       <c r="G186" s="11" t="inlineStr">
         <is>
+          <t>Логістична фірма GLP планує цього року продати активи на 2 мільярди доларів Bloomberg</t>
+        </is>
+      </c>
+      <c r="H186" s="11" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H186" s="11" t="inlineStr">
+      <c r="I186" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I186" s="11" t="inlineStr">
+      <c r="J186" s="11" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J186" s="11" t="inlineStr">
+      <c r="K186" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K186" s="13" t="inlineStr">
+      <c r="L186" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOUkR1dE5CY3pHNG1hQ1N3SWhMRlA5SE1MZXNFWnVZU3lJUkRsUVhuTUVOYXQ1azJCbmRFU1g5Ny1pMzNIZGRuTHZwTXRFdUw4MWp4LUxUdGZfa1NpSm1RdnJhWXNuM0s2RmRCeTVGVkljX3V1WnJKamVqd1NSS2NoZ09QbmN0NXlXZjk3NlM5bFN1MGRQWkVfNEoxdldCSlhST3BxY1A1bGVGUVFtT0ZBRnlsYw?oc=5</t>
         </is>
       </c>
-      <c r="L186" s="11" t="inlineStr">
+      <c r="M186" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11792,26 +12723,31 @@
       </c>
       <c r="G187" s="11" t="inlineStr">
         <is>
+          <t>Алмазна економіка Ботсвани переживає дедалі більшу напругу, оскільки світовий попит слабшає, а виробництво падає.</t>
+        </is>
+      </c>
+      <c r="H187" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H187" s="11" t="inlineStr">
+      <c r="I187" s="11" t="inlineStr">
         <is>
           <t>НМА</t>
         </is>
       </c>
-      <c r="I187" s="11" t="inlineStr">
+      <c r="J187" s="11" t="inlineStr">
         <is>
           <t>Ботсвана</t>
         </is>
       </c>
-      <c r="J187" s="11" t="inlineStr"/>
-      <c r="K187" s="13" t="inlineStr">
+      <c r="K187" s="11" t="inlineStr"/>
+      <c r="L187" s="13" t="inlineStr">
         <is>
           <t>https://www.aljazeera.com/news/2026/6/9/botswana-diamond-slump-hits-miners-living-on-the-edge-of-survival?traffic_source=rss</t>
         </is>
       </c>
-      <c r="L187" s="11" t="inlineStr">
+      <c r="M187" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11850,26 +12786,31 @@
       </c>
       <c r="G188" s="11" t="inlineStr">
         <is>
+          <t>Російські атаки на Україну вбили чотирьох, оскільки Зеленський отримав підтримку переговорів про припинення вогню Reuters</t>
+        </is>
+      </c>
+      <c r="H188" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H188" s="11" t="inlineStr">
+      <c r="I188" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I188" s="11" t="inlineStr">
+      <c r="J188" s="11" t="inlineStr">
         <is>
           <t>Україна, Росія</t>
         </is>
       </c>
-      <c r="J188" s="11" t="inlineStr"/>
-      <c r="K188" s="13" t="inlineStr">
+      <c r="K188" s="11" t="inlineStr"/>
+      <c r="L188" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNZ1N4dmFzTURxWVl5d3hKYmNCeHhaQkgzNlQ0M3JGVUFtMlBMSll0Q1dUdjN6LV9qc2V2REVVWjdqcUJweHdxc3UyVDhQR0k5QlZDb2NWM0RoeXZYX1NoSVJyRXdJbERmcHk5MFVQUmtEMjVTQ0JUOTVidEhVMnQ5Q21YczdkN0dNVklsY2lJVU9fMEpvUUtYS0gwN0JRTmpSNTZyZkZ1T1RsVjBDSHZVUDVZYm1xUQ?oc=5</t>
         </is>
       </c>
-      <c r="L188" s="11" t="inlineStr">
+      <c r="M188" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11908,26 +12849,31 @@
       </c>
       <c r="G189" s="11" t="inlineStr">
         <is>
+          <t>Країни Центральної Азії об’єднуються, щоб посилити управління водними ресурсами та землею для 60 мільйонів людей Продовольчої та сільськогосподарської організації</t>
+        </is>
+      </c>
+      <c r="H189" s="11" t="inlineStr">
+        <is>
           <t>погода_клімат</t>
         </is>
       </c>
-      <c r="H189" s="11" t="inlineStr">
+      <c r="I189" s="11" t="inlineStr">
         <is>
           <t>Добрива</t>
         </is>
       </c>
-      <c r="I189" s="11" t="inlineStr">
+      <c r="J189" s="11" t="inlineStr">
         <is>
           <t>Казахстан, Узбекистан, Киргизія, Таджикистан, Туркменістан</t>
         </is>
       </c>
-      <c r="J189" s="11" t="inlineStr"/>
-      <c r="K189" s="13" t="inlineStr">
+      <c r="K189" s="11" t="inlineStr"/>
+      <c r="L189" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNM3BTRm1lQkZ0SDZQMDF2ZklpNDNzb05LSnY1ZklkeWloTlpGWE0wVTZWMTJwTTBlWF84b2gyc2dnR3A2eTdyOUlmV0JzcFhHd2VUWkdETXdTVzN2RDI2OWVfTzRBRV8wMDRuYUJWTE14bGNWNW93MEJSRl9pNDBXSEFzdVZWeWZPS3lNSTB0bjRfQ2N3dDZhU2VtSWQ4b2FzNF93cDliUFVEMXhYblhFV0h4NTZwZ0tPNVNyZDNtQndVbVZHMnEtb1NXYWY?oc=5</t>
         </is>
       </c>
-      <c r="L189" s="11" t="inlineStr">
+      <c r="M189" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -11966,30 +12912,35 @@
       </c>
       <c r="G190" s="11" t="inlineStr">
         <is>
+          <t>Розгром чіпів піддає корейським «мурахам» інвесторам випробування, оскільки боргова маржа стрімко зростає Reuters</t>
+        </is>
+      </c>
+      <c r="H190" s="11" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H190" s="11" t="inlineStr">
+      <c r="I190" s="11" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I190" s="11" t="inlineStr">
+      <c r="J190" s="11" t="inlineStr">
         <is>
           <t>Південна Корея</t>
         </is>
       </c>
-      <c r="J190" s="11" t="inlineStr">
+      <c r="K190" s="11" t="inlineStr">
         <is>
           <t>Технології</t>
         </is>
       </c>
-      <c r="K190" s="13" t="inlineStr">
+      <c r="L190" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNbHhzTG1xelJvQV9zZlFFTDhPT2lqU1VCZV9SYjNnTmJEeHdVb2w3YXIteG9idmlubXZBUXlDMVZMdGxjWElkZHEyTjZKbGhlMmM1cldvTkNucF8ycmNjVUJZQWppV3Z2NlI3NURqajZPRGQxTjJkQ0JBR2FFNE5RQlVXem1kX0tjV2Z5MTNPU3M2Z201dkk2MWRuZERYdWtRRlZsYVIyWDVwM2Q4VjJmNg?oc=5</t>
         </is>
       </c>
-      <c r="L190" s="11" t="inlineStr">
+      <c r="M190" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12028,30 +12979,35 @@
       </c>
       <c r="G191" s="11" t="inlineStr">
         <is>
+          <t>Компанія Seasystems AS підписала контракт на поставку 2 плавучих причалів для газових стояків та електропостачання проекту FLNG у Канаді. Плавучі причали, які базуються на запатентованому рішенні від Seasystems, гарантують, що газові стояки та кабелі живлення не контактують з морським дном біля берега, ...</t>
+        </is>
+      </c>
+      <c r="H191" s="11" t="inlineStr">
+        <is>
           <t>не_релевантно</t>
         </is>
       </c>
-      <c r="H191" s="11" t="inlineStr">
+      <c r="I191" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I191" s="11" t="inlineStr">
+      <c r="J191" s="11" t="inlineStr">
         <is>
           <t>Канада</t>
         </is>
       </c>
-      <c r="J191" s="11" t="inlineStr">
+      <c r="K191" s="11" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K191" s="13" t="inlineStr">
+      <c r="L191" s="13" t="inlineStr">
         <is>
           <t>https://www.hellenicshippingnews.com/seasystems-secures-riser-and-cable-floating-jetty-contract-for-flng-project/</t>
         </is>
       </c>
-      <c r="L191" s="11" t="inlineStr">
+      <c r="M191" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12090,30 +13046,35 @@
       </c>
       <c r="G192" s="11" t="inlineStr">
         <is>
+          <t>За тиждень, що закінчився 5 червня, індекс Ningbo Containerized Freight Index (NCFI), опублікований Ningbo Shipping Exchange (NBSE), становив 2097,8 пунктів Нижче наведено діаграму даних щотижневого індексу NCFI: Джерело: Ningbo Shipping Exchange</t>
+        </is>
+      </c>
+      <c r="H192" s="11" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H192" s="11" t="inlineStr">
+      <c r="I192" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I192" s="11" t="inlineStr">
+      <c r="J192" s="11" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J192" s="11" t="inlineStr">
+      <c r="K192" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K192" s="13" t="inlineStr">
+      <c r="L192" s="13" t="inlineStr">
         <is>
           <t>https://www.hellenicshippingnews.com/ningbo-containerized-freight-index-report-05-june-2026/</t>
         </is>
       </c>
-      <c r="L192" s="11" t="inlineStr">
+      <c r="M192" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12152,26 +13113,31 @@
       </c>
       <c r="G193" s="11" t="inlineStr">
         <is>
+          <t>У відкритому листі до представників галузі ABS виклала виважений і керований даними підхід для підтримки розробки ефективної глобальної основи для декарбонізації морського транспорту. Під назвою The ABS View: A Practical Path Forward on IMO Mid-Term Measures (Погляд ABS: практичний шлях вперед щодо середньострокових заходів IMO) відображає широку згоду в галузі щодо необхідності єдиного міжнародного підходу до ...</t>
+        </is>
+      </c>
+      <c r="H193" s="11" t="inlineStr">
+        <is>
           <t>регуляторика</t>
         </is>
       </c>
-      <c r="H193" s="11" t="inlineStr">
+      <c r="I193" s="11" t="inlineStr">
         <is>
           <t>НМА</t>
         </is>
       </c>
-      <c r="I193" s="11" t="inlineStr"/>
-      <c r="J193" s="11" t="inlineStr">
+      <c r="J193" s="11" t="inlineStr"/>
+      <c r="K193" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K193" s="13" t="inlineStr">
+      <c r="L193" s="13" t="inlineStr">
         <is>
           <t>https://www.hellenicshippingnews.com/abs-sets-out-technical-view-on-imo-mid-term-measures-and-pathway-to-decarbonization/</t>
         </is>
       </c>
-      <c r="L193" s="11" t="inlineStr">
+      <c r="M193" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12210,26 +13176,31 @@
       </c>
       <c r="G194" s="11" t="inlineStr">
         <is>
+          <t>Війна на Близькому Сході знову розгорається. Ось як кожна сторона бачить ставки AP News</t>
+        </is>
+      </c>
+      <c r="H194" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H194" s="11" t="inlineStr">
+      <c r="I194" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I194" s="11" t="inlineStr">
+      <c r="J194" s="11" t="inlineStr">
         <is>
           <t>Близький Схід</t>
         </is>
       </c>
-      <c r="J194" s="11" t="inlineStr"/>
-      <c r="K194" s="13" t="inlineStr">
+      <c r="K194" s="11" t="inlineStr"/>
+      <c r="L194" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNWkRFQ3RvLTRpQUdqNnl6azI3Z1Y5N3ByQVhSeEhwVmNIS1BoTGEtLVN4SkJqc0VYR2JQQ0taWnhubmpja3JTcDJncWdjeGt1X3laMXdGcWlsUzM0cGZIWFl5Qzk1MzZLNHlFbE96QlJYUEpLWFFOQWZBTGFvZGhwRGVRenN2TEhkb2w1dXlwQlhkcFhnMnc?oc=5</t>
         </is>
       </c>
-      <c r="L194" s="11" t="inlineStr">
+      <c r="M194" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12268,30 +13239,35 @@
       </c>
       <c r="G195" s="11" t="inlineStr">
         <is>
+          <t>Розробник рідкоземельних елементів Aclara шукає підтримки США для чилійського проекту Bloomberg</t>
+        </is>
+      </c>
+      <c r="H195" s="11" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H195" s="11" t="inlineStr">
+      <c r="I195" s="11" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I195" s="11" t="inlineStr">
+      <c r="J195" s="11" t="inlineStr">
         <is>
           <t>Чилі, США</t>
         </is>
       </c>
-      <c r="J195" s="11" t="inlineStr">
+      <c r="K195" s="11" t="inlineStr">
         <is>
           <t>Метали і мінерали</t>
         </is>
       </c>
-      <c r="K195" s="13" t="inlineStr">
+      <c r="L195" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOelc1dHdyWmFuVklzNE5sREYyRjVnVnpLa3pNRlZRWGVKVmwxR2ttRU1KM0UyeUpubGw3RTkwMXZVNXA3WEt3RHp1YVB6MHV2YmNOcTRfamhjWmRzWEgyU3htSWplQ194dFcxV3RwZlJkU0pGckZtVUpsSjBQbTl0RGNXQkJvMHNjM0NiVEsxeWgxY2Q0bjhSbWU0cGJhYUJOQUNxLW1WdElVQzZzSWx4QVdBbm9Kdw?oc=5</t>
         </is>
       </c>
-      <c r="L195" s="11" t="inlineStr">
+      <c r="M195" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12330,30 +13306,35 @@
       </c>
       <c r="G196" s="11" t="inlineStr">
         <is>
+          <t>Amazon планує розгорнути три типи нових роботів у рамках плану інвестувати понад 10 мільярдів доларів у розширення та модернізацію центрів виконання замовлення в Європі та збільшити кількість робочої сили на 25 000 до кінця десятиліття. Amazon (NASDAQ: AMZN) покладається на роботів, щоб зробити робоче середовище безпечнішим і простішим для співробітників, одночасно покращуючи швидкість обробки пакетів. Amazon Robotics була заснована в 2012 році, коли Amazon придбала компанію Kiva Systems, розташовану в Массачусетсі. Оригінальні роботи Kiva переміщали стоси полиць</t>
+        </is>
+      </c>
+      <c r="H196" s="11" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H196" s="11" t="inlineStr">
+      <c r="I196" s="11" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I196" s="11" t="inlineStr">
+      <c r="J196" s="11" t="inlineStr">
         <is>
           <t>Європа</t>
         </is>
       </c>
-      <c r="J196" s="11" t="inlineStr">
+      <c r="K196" s="11" t="inlineStr">
         <is>
           <t>Обладнання</t>
         </is>
       </c>
-      <c r="K196" s="13" t="inlineStr">
+      <c r="L196" s="13" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/robots-drive-10b-amazon-investment-for-european-fulfillment-centers</t>
         </is>
       </c>
-      <c r="L196" s="11" t="inlineStr">
+      <c r="M196" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12392,26 +13373,31 @@
       </c>
       <c r="G197" s="11" t="inlineStr">
         <is>
+          <t>«Коротко, різко та більш стратегічно»: новий підхід ЄС до кліматичних переговорів Reuters</t>
+        </is>
+      </c>
+      <c r="H197" s="11" t="inlineStr">
+        <is>
           <t>погода_клімат</t>
         </is>
       </c>
-      <c r="H197" s="11" t="inlineStr">
+      <c r="I197" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I197" s="11" t="inlineStr">
+      <c r="J197" s="11" t="inlineStr">
         <is>
           <t>ЄС</t>
         </is>
       </c>
-      <c r="J197" s="11" t="inlineStr"/>
-      <c r="K197" s="13" t="inlineStr">
+      <c r="K197" s="11" t="inlineStr"/>
+      <c r="L197" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQeTF2OENlY3JnTnRrY3draHY0TUExSkxnYVRlSDZ1SXZqaVg1bFRoV1lkdl9MdnZTeEtHX2NrNnhGV2lNekRKNjBTVkhPeWo3cEZLdllEdXJBRG9ER0tsV1ZaTXdZSUNqY0lraTVrR3ZMMXhMRk5ZWEhZN3dkMFlJOVNWM2NOZ3RKLXZ0cTdSREJPT09LNjZuVXl3Y2ZWNDBJM3l1MTlsdTlYVXFjV0hZZW5B?oc=5</t>
         </is>
       </c>
-      <c r="L197" s="11" t="inlineStr">
+      <c r="M197" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12450,30 +13436,35 @@
       </c>
       <c r="G198" s="11" t="inlineStr">
         <is>
+          <t>IATA розширила свою послугу розрахунків CASS у Латинській Америці, оскільки обсяги повітряних вантажів у регіоні продовжують збільшуватися. Асоціація авіакомпаній оголосила, що тепер CASS буде доступний для внутрішніх рейсів у Мексиці та незабаром у Бразилії, тоді як він буде доступний для експорту з Парагваю пізніше цього року. Пояснюючи рішення про запуск…</t>
+        </is>
+      </c>
+      <c r="H198" s="11" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H198" s="11" t="inlineStr">
+      <c r="I198" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I198" s="11" t="inlineStr">
+      <c r="J198" s="11" t="inlineStr">
         <is>
           <t>Мексика, Бразилія, Парагвай</t>
         </is>
       </c>
-      <c r="J198" s="11" t="inlineStr">
+      <c r="K198" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K198" s="13" t="inlineStr">
+      <c r="L198" s="13" t="inlineStr">
         <is>
           <t>https://www.aircargonews.net/iata/2026/06/iata-expands-cass-payment-service-in-latin-america/</t>
         </is>
       </c>
-      <c r="L198" s="11" t="inlineStr">
+      <c r="M198" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12512,30 +13503,35 @@
       </c>
       <c r="G199" s="11" t="inlineStr">
         <is>
+          <t>Данський фахівець з логістики Deugro призначив Даніеля К'єра віце-президентом Global Wind Renewable Energy з 1 червня 2026 року. К'єр, який базується в Орхусі, Данія, відповідатиме за подальший розвиток і реалізацію глобальної стратегії морської вітрової енергетики Deugro. У нещодавно оголошеній ролі…</t>
+        </is>
+      </c>
+      <c r="H199" s="11" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H199" s="11" t="inlineStr">
+      <c r="I199" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I199" s="11" t="inlineStr">
+      <c r="J199" s="11" t="inlineStr">
         <is>
           <t>Данія</t>
         </is>
       </c>
-      <c r="J199" s="11" t="inlineStr">
+      <c r="K199" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K199" s="13" t="inlineStr">
+      <c r="L199" s="13" t="inlineStr">
         <is>
           <t>https://www.marinelink.com/news/deugro-expands-offshore-wind-leadership-540044</t>
         </is>
       </c>
-      <c r="L199" s="11" t="inlineStr">
+      <c r="M199" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12574,26 +13570,31 @@
       </c>
       <c r="G200" s="11" t="inlineStr">
         <is>
+          <t>ФРС очікує підвищення процентних ставок, повідомляє Bloomberg Мартін з Schwab Center</t>
+        </is>
+      </c>
+      <c r="H200" s="11" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H200" s="11" t="inlineStr">
+      <c r="I200" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I200" s="11" t="inlineStr">
+      <c r="J200" s="11" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J200" s="11" t="inlineStr"/>
-      <c r="K200" s="13" t="inlineStr">
+      <c r="K200" s="11" t="inlineStr"/>
+      <c r="L200" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxOT216M282NmJsYi0yTE44T0NzVzNhRGlBUy1ZS2w2Y3JEcHJZbkNJaW5kd0h2VzhFTXRNZkFqMjlzZGFzOGdZdmhmeVZGV2h3aGtycVBQREtmM3c4SzB6TmhHYkhvUUxZXzh3clU3ajlZWDYwV3lKcExjblVkSk1IYy1CajlOeTNNaS1zWTF6SjByQ1dueG9ncVNNbloxVWRiMWV6T2t2R0ZHb0J4WkNwd2hB?oc=5</t>
         </is>
       </c>
-      <c r="L200" s="11" t="inlineStr">
+      <c r="M200" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12632,26 +13633,31 @@
       </c>
       <c r="G201" s="11" t="inlineStr">
         <is>
+          <t>Tate &amp; Lyle — остання втрата Лондона після продажу американському конкуренту Bloomberg</t>
+        </is>
+      </c>
+      <c r="H201" s="11" t="inlineStr">
+        <is>
           <t>не_релевантно</t>
         </is>
       </c>
-      <c r="H201" s="11" t="inlineStr">
+      <c r="I201" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I201" s="11" t="inlineStr">
+      <c r="J201" s="11" t="inlineStr">
         <is>
           <t>Великобританія, США</t>
         </is>
       </c>
-      <c r="J201" s="11" t="inlineStr"/>
-      <c r="K201" s="13" t="inlineStr">
+      <c r="K201" s="11" t="inlineStr"/>
+      <c r="L201" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQWHNZaWhINXFxMXg4VHZNQU5uaFFQQjExSEVmc3VZVjJyOTJRbnFnY3dXVXUwU0lnRXh5ZUdkT0tQbTJqTTBtM21ETGJTZDlhQ2tlQkpGc25BRE1hbF9Vc2ZrQ2VmQXM3cFdMWURnc1FuZDA5ZXRRWnJaZUNhb2VrOHk2aVQyS1B2Nkl0ZVlMS1JfdnFtX1J1VlJDd2c1a1hhY3hIakVRZTFhTlVnVEE?oc=5</t>
         </is>
       </c>
-      <c r="L201" s="11" t="inlineStr">
+      <c r="M201" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12690,26 +13696,31 @@
       </c>
       <c r="G202" s="11" t="inlineStr">
         <is>
+          <t>Індійські банки можуть залучити 35-40 мільярдів доларів за допомогою схеми депозитів в іноземній валюті RBI, заявив генеральний директор PNB Reuters</t>
+        </is>
+      </c>
+      <c r="H202" s="11" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H202" s="11" t="inlineStr">
+      <c r="I202" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I202" s="11" t="inlineStr">
+      <c r="J202" s="11" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J202" s="11" t="inlineStr"/>
-      <c r="K202" s="13" t="inlineStr">
+      <c r="K202" s="11" t="inlineStr"/>
+      <c r="L202" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOdGtrMEtXYklQcXJPdV9pZzRneG5kaGJxREQ4MWRQRlItQzV3SDVrSGhYZ1ZLb2hjZkpEdG5UaWNiMTJvWXlfbDFhb18tQVc0RFAxWTU2MzdjUDZySkhsZmRRQmljUHZzaTVlZWRKbVlWNUx6bjFESnpMSXJ1c1VnQWEtQ2IybXoydTNndmM5bUkzQVNLSHd4NFpyVXRkc0RDVHkyNzRrWWJWR0VvRU5fYzdwWHNHemJ4dzZNM0p3dTNkTHRq?oc=5</t>
         </is>
       </c>
-      <c r="L202" s="11" t="inlineStr">
+      <c r="M202" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12748,30 +13759,35 @@
       </c>
       <c r="G203" s="11" t="inlineStr">
         <is>
+          <t>Комісія ЄС схвалила державні субсидії Італії на відновлювані джерела енергії Reuters</t>
+        </is>
+      </c>
+      <c r="H203" s="11" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H203" s="11" t="inlineStr">
+      <c r="I203" s="11" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I203" s="11" t="inlineStr">
+      <c r="J203" s="11" t="inlineStr">
         <is>
           <t>Італія</t>
         </is>
       </c>
-      <c r="J203" s="11" t="inlineStr">
+      <c r="K203" s="11" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K203" s="13" t="inlineStr">
+      <c r="L203" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNUFRCV2tUdkVHMEFPQXNXcjc5TW1BWkhaRkVubWRzYTluOWRVVXNTR2pRQUtiU2VRa3VhS3R0VTd0Z0oxUTVHOWVOUzAzVUxwd1NtVGJYQUZnN3FKMi1McWUtLW5PY3AzRHM2YzN3ZnlPcWRpdlJ6VmR6QURMbHl0Um5PdkZ6WW8wQnZwWTRWWE8tYWpSOHlWaGl2ZzB5WGNRN0hGMk9lbDNlUjR0NkE?oc=5</t>
         </is>
       </c>
-      <c r="L203" s="11" t="inlineStr">
+      <c r="M203" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12810,30 +13826,35 @@
       </c>
       <c r="G204" s="11" t="inlineStr">
         <is>
+          <t>Логістичний підрозділ Hyundai Motor, Hyundai Glovis, побудує підприємство з імпорту автомобілів у голландському порту Амстердам для збільшення імпорту європейських автомобілів. Об’єкт матиме причали для трьох чистих перевізників легкових і вантажних автомобілів (PCTC) і більше ніж 20 000 транспортних засобів, а також засоби перевірки перед доставкою з під’їздами для забезпечення залізничного транспорту. Термінал планується відкрити в січні 2027 року, а Hyundai Glovis Europe (GEU) візьме ... The post Hyundai Glovis розробить готовий автомобіль</t>
+        </is>
+      </c>
+      <c r="H204" s="11" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H204" s="11" t="inlineStr">
+      <c r="I204" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I204" s="11" t="inlineStr">
+      <c r="J204" s="11" t="inlineStr">
         <is>
           <t>Нідерланди</t>
         </is>
       </c>
-      <c r="J204" s="11" t="inlineStr">
+      <c r="K204" s="11" t="inlineStr">
         <is>
           <t>Запчастини, Логістика</t>
         </is>
       </c>
-      <c r="K204" s="13" t="inlineStr">
+      <c r="L204" s="13" t="inlineStr">
         <is>
           <t>https://theloadstar.com/hyundai-glovis-to-develop-finished-vehicle-hub-in-amsterdam/</t>
         </is>
       </c>
-      <c r="L204" s="11" t="inlineStr">
+      <c r="M204" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12872,30 +13893,35 @@
       </c>
       <c r="G205" s="11" t="inlineStr">
         <is>
+          <t>Коаліція, яка виступає проти злиття Union Pacific і Southern Pacific, отримала поштовх від потужного комітету Палати представників, який закликав до ретельного перегляду угоди, яка передбачає створення першої трансконтинентальної залізниці, призначеної для виключно вантажних перевезень. Раду наземного транспорту закликали провести ретельний аналіз злиття у формулюванні, доданому до законопроекту про асигнування на транспорт, житлове будівництво та розвиток міст (THUD) на 2027 фінансовий рік. Включення двопартійним комітетом з асигнувань Палати представників відбулося в червні</t>
+        </is>
+      </c>
+      <c r="H205" s="11" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H205" s="11" t="inlineStr">
+      <c r="I205" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I205" s="11" t="inlineStr">
+      <c r="J205" s="11" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J205" s="11" t="inlineStr">
+      <c r="K205" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K205" s="13" t="inlineStr">
+      <c r="L205" s="13" t="inlineStr">
         <is>
           <t>https://www.freightwaves.com/news/house-endorses-25-year-old-rules-for-rail-merger-review</t>
         </is>
       </c>
-      <c r="L205" s="11" t="inlineStr">
+      <c r="M205" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12934,30 +13960,35 @@
       </c>
       <c r="G206" s="11" t="inlineStr">
         <is>
+          <t>ADNOC оголошує другий тендер на вантажоперевезення нафти в ОАЕ за тиждень Reuters</t>
+        </is>
+      </c>
+      <c r="H206" s="11" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H206" s="11" t="inlineStr">
+      <c r="I206" s="11" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I206" s="11" t="inlineStr">
+      <c r="J206" s="11" t="inlineStr">
         <is>
           <t>ОАЕ</t>
         </is>
       </c>
-      <c r="J206" s="11" t="inlineStr">
+      <c r="K206" s="11" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K206" s="13" t="inlineStr">
+      <c r="L206" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOd2ZXSV9ROEU0SGtYbTFDcDRycHRzdThjYWJYQ0FqbnAtMXFRajNPVGNlNmtsMExVQWZoa1UzM2lBUmVONlVlNGc4OVFFZ1l6S3h1V1RKbFhGY3N3ME9kcFplRzFZZEp2ZkhJellnYkVZamF3MlFNQlV1eHF0eXdiZWVhSEpfRzNhVEliRklPTkhyR2R6STNlODVuakJvX2pTNzdza083Mlk?oc=5</t>
         </is>
       </c>
-      <c r="L206" s="11" t="inlineStr">
+      <c r="M206" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -12996,30 +14027,35 @@
       </c>
       <c r="G207" s="11" t="inlineStr">
         <is>
+          <t>Падіння продажів автомобілів у Китаї спонукає PCA поглибити річний прогноз Bloomberg</t>
+        </is>
+      </c>
+      <c r="H207" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H207" s="11" t="inlineStr">
+      <c r="I207" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I207" s="11" t="inlineStr">
+      <c r="J207" s="11" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J207" s="11" t="inlineStr">
+      <c r="K207" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K207" s="13" t="inlineStr">
+      <c r="L207" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWDJvVm51RmtHWDlYck1SM1VId3FqdGdseWhvS2xtUkF4X2l6Rk9xaXRXNHIxUUhvUzh0S3Y2aE1xRkxlZ3pFczdWUm5pRHRVNEY4LU4wRk51Mk9vdVpLTG5tVXZYcDVvNUo2OGMyYkZVblQxMUJKay13QkpxSVJ2eEhQV0tIV3EzRW50N0JRMEZmcDZIT1lVV1lQZ3dNZ1Z6aXRvc2lRZTFQcjhjNGtkbHVZUQ?oc=5</t>
         </is>
       </c>
-      <c r="L207" s="11" t="inlineStr">
+      <c r="M207" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13058,30 +14094,35 @@
       </c>
       <c r="G208" s="11" t="inlineStr">
         <is>
+          <t>ЄС планує змінити податки, щоб зменшити рахунки за електроенергію, повідомляє Reuters</t>
+        </is>
+      </c>
+      <c r="H208" s="11" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H208" s="11" t="inlineStr">
+      <c r="I208" s="11" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I208" s="11" t="inlineStr">
+      <c r="J208" s="11" t="inlineStr">
         <is>
           <t>ЄС</t>
         </is>
       </c>
-      <c r="J208" s="11" t="inlineStr">
+      <c r="K208" s="11" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K208" s="13" t="inlineStr">
+      <c r="L208" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxOZlI3UGJUdjJYTlVhMzhfcjl0TWNlU1hhektzWkNqR1ZxcnN2NGhUaEZvaE5JRHpJbk1EeEVQeG5OV2FobGtLQTRjWnB1RkJHa1dTTWU3VG03U2l4TmJyUzFuSlg0a29KdjE4NWNLZDdTellBUGVVYW5FSGhISG9PZ1doMlYyaWlWY0ozdUxLRTBCaVNfQmc5VlRuZWlRMHFjdTVGU0NvSU9PRFM2YlE?oc=5</t>
         </is>
       </c>
-      <c r="L208" s="11" t="inlineStr">
+      <c r="M208" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13120,30 +14161,35 @@
       </c>
       <c r="G209" s="11" t="inlineStr">
         <is>
+          <t>Компанія Kuehne+Nagel розширила свою авіамережу за допомогою нового сполучення між Німеччиною та США, щоб націлити на обсяги фармацевтичної продукції. Новий рейс виконуватиметься між Франкфуртом і Чикаго, продовжуючи до Атланти на одному з експедиторських вантажних літаків Boeing 747-8. «З’єднання напряму з’єднує Франкфурт і Чикаго, два головні центри виробництва та розподілу фармацевтичних препаратів, підтримуючи…</t>
+        </is>
+      </c>
+      <c r="H209" s="11" t="inlineStr">
+        <is>
           <t>логістика</t>
         </is>
       </c>
-      <c r="H209" s="11" t="inlineStr">
+      <c r="I209" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I209" s="11" t="inlineStr">
+      <c r="J209" s="11" t="inlineStr">
         <is>
           <t>Німеччина, США</t>
         </is>
       </c>
-      <c r="J209" s="11" t="inlineStr">
+      <c r="K209" s="11" t="inlineStr">
         <is>
           <t>Логістика, Незернові компоненти</t>
         </is>
       </c>
-      <c r="K209" s="13" t="inlineStr">
+      <c r="L209" s="13" t="inlineStr">
         <is>
           <t>https://www.aircargonews.net/freight-forwarder/2026/06/kn-expands-air-network-with-frankfurt-addition/</t>
         </is>
       </c>
-      <c r="L209" s="11" t="inlineStr">
+      <c r="M209" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13182,26 +14228,31 @@
       </c>
       <c r="G210" s="11" t="inlineStr">
         <is>
+          <t>The post MICT полегшує індійську торгівлю, звіти Oxford Economics спершу з’явилися на Logistics Manager .</t>
+        </is>
+      </c>
+      <c r="H210" s="11" t="inlineStr">
+        <is>
           <t>санкції_торгівля</t>
         </is>
       </c>
-      <c r="H210" s="11" t="inlineStr">
+      <c r="I210" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I210" s="11" t="inlineStr">
+      <c r="J210" s="11" t="inlineStr">
         <is>
           <t>Індія</t>
         </is>
       </c>
-      <c r="J210" s="11" t="inlineStr"/>
-      <c r="K210" s="13" t="inlineStr">
+      <c r="K210" s="11" t="inlineStr"/>
+      <c r="L210" s="13" t="inlineStr">
         <is>
           <t>https://www.logisticsmanager.com/mict-facilitating-indian-trade-oxford-economics-reports/</t>
         </is>
       </c>
-      <c r="L210" s="11" t="inlineStr">
+      <c r="M210" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13240,26 +14291,31 @@
       </c>
       <c r="G211" s="11" t="inlineStr">
         <is>
+          <t>Спокій на ринку нафти маскує безліч невідомих Reuters</t>
+        </is>
+      </c>
+      <c r="H211" s="11" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H211" s="11" t="inlineStr">
+      <c r="I211" s="11" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I211" s="11" t="inlineStr"/>
-      <c r="J211" s="11" t="inlineStr">
+      <c r="J211" s="11" t="inlineStr"/>
+      <c r="K211" s="11" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K211" s="13" t="inlineStr">
+      <c r="L211" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxOY3Q3T2xKWFI3bFdfMUZtUTBjVmlKT3B3elNTaWlpNGtfUFFQWW92RDBsRjh2NndOMjhBVWc2TGZHeTlQNkR4Z0FHMDlIWVVVd2w4eEJ2RUFMVjAzV0RGV3FBdVpXUjdacFc5UHdWaVdPTExIN3hfeHZVdl92ektkbGY2YmtINFltQ0s1NE9ZWjNDVmxJbjc1YVJIWmZRQ0pVdng4dV9uMA?oc=5</t>
         </is>
       </c>
-      <c r="L211" s="11" t="inlineStr">
+      <c r="M211" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13298,26 +14354,31 @@
       </c>
       <c r="G212" s="11" t="inlineStr">
         <is>
+          <t>Золото стирає втрати, незважаючи на сильні дані про робочі місця в США, оскільки надії на припинення вогню з’являються Reuters</t>
+        </is>
+      </c>
+      <c r="H212" s="11" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H212" s="11" t="inlineStr">
+      <c r="I212" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I212" s="11" t="inlineStr"/>
-      <c r="J212" s="11" t="inlineStr">
+      <c r="J212" s="11" t="inlineStr"/>
+      <c r="K212" s="11" t="inlineStr">
         <is>
           <t>Метали</t>
         </is>
       </c>
-      <c r="K212" s="13" t="inlineStr">
+      <c r="L212" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPVjd4bHo0Sk1fN3U4OWtieHFoRkgxT0Y4OGxpa3lyc1RGb0MtaVNXVFlmRW1OQlNPaEZpVGFvUEtxUlFhUDJnMVNhNkpOOE52YmJQTUZNYjktTGk2R0FMc0VNTHpmNTFDbUk0RC1iUzVLMzR4eElLQk9icU1nWGRRRU8wYlgwMEpoQ1VKSTdyd185cWJ2cUlXdFpvOA?oc=5</t>
         </is>
       </c>
-      <c r="L212" s="11" t="inlineStr">
+      <c r="M212" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13356,30 +14417,35 @@
       </c>
       <c r="G213" s="11" t="inlineStr">
         <is>
+          <t>Генеральний директор Watch Vale не бачить падіння попиту на ринках металів Bloomberg</t>
+        </is>
+      </c>
+      <c r="H213" s="11" t="inlineStr">
+        <is>
           <t>ціни_сировини</t>
         </is>
       </c>
-      <c r="H213" s="11" t="inlineStr">
+      <c r="I213" s="11" t="inlineStr">
         <is>
           <t>Вит.матеріали/МШП</t>
         </is>
       </c>
-      <c r="I213" s="11" t="inlineStr">
+      <c r="J213" s="11" t="inlineStr">
         <is>
           <t>Бразилія</t>
         </is>
       </c>
-      <c r="J213" s="11" t="inlineStr">
+      <c r="K213" s="11" t="inlineStr">
         <is>
           <t>Метали</t>
         </is>
       </c>
-      <c r="K213" s="13" t="inlineStr">
+      <c r="L213" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPMjBma1Jab3FkM0RaUDkyN1NoZFJwOGwzelI2NVBLQWpiTHQ0ek5fOTR2SjVnYWtXVzBXLUJnTEgzX3U1MEEyY0dWWENySlV1eXROSWxrV0Vqdm42YzhacVk1bEpheXctOGlBVUlGbHVnQm52azBTN0lBSzBXNlFueE5NQWROZ3dSdm03Z3E2eFlKM2xhOWFOcVdONzFHQTVnRmNhdGI1TGtNLThl?oc=5</t>
         </is>
       </c>
-      <c r="L213" s="11" t="inlineStr">
+      <c r="M213" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13418,26 +14484,31 @@
       </c>
       <c r="G214" s="11" t="inlineStr">
         <is>
+          <t>Китай Сі обіцяє непохитну підтримку північнокорейського Кіма в рідкісних візитах до Пхеньяна Reuters</t>
+        </is>
+      </c>
+      <c r="H214" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H214" s="11" t="inlineStr">
+      <c r="I214" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I214" s="11" t="inlineStr">
+      <c r="J214" s="11" t="inlineStr">
         <is>
           <t>Китай, КНДР</t>
         </is>
       </c>
-      <c r="J214" s="11" t="inlineStr"/>
-      <c r="K214" s="13" t="inlineStr">
+      <c r="K214" s="11" t="inlineStr"/>
+      <c r="L214" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQRWY1bGhhZXQ0TlBOOTFKWFpCN3dBdkUzNWctcFE5cXh6UXljOWhwQ3g4cFhpYVNVRmZXSXJ6ZVVNeFgyaDZPX3Ata3BJQ3lTYng0RkZqQUFmemF4eGxzSzNWemhIYmVTRHdpODJhXzRSbVJtd05RbTRqQlVrdVd6OG8yUWhJdVZjYVpONkYwNnZpYjV0VEhtbG5lZy1HbUpNaC1UYkVzUnluM25icm11SmJoc3NrRDNjeG5LN1lQZnMzaXMy?oc=5</t>
         </is>
       </c>
-      <c r="L214" s="11" t="inlineStr">
+      <c r="M214" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13476,26 +14547,31 @@
       </c>
       <c r="G215" s="11" t="inlineStr">
         <is>
+          <t>Ірак ризикує припинити виплату уряду, якщо війна триватиме, каже міністр Bloomberg</t>
+        </is>
+      </c>
+      <c r="H215" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H215" s="11" t="inlineStr">
+      <c r="I215" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I215" s="11" t="inlineStr">
+      <c r="J215" s="11" t="inlineStr">
         <is>
           <t>Ірак</t>
         </is>
       </c>
-      <c r="J215" s="11" t="inlineStr"/>
-      <c r="K215" s="13" t="inlineStr">
+      <c r="K215" s="11" t="inlineStr"/>
+      <c r="L215" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQTG1DZ21CbmJuRmRmVmJaaV9INVlFWWNDMVJYay1QblJkWHU3eEpQUzdNSWlYMzdPV2t5SFNBc0VLSk5rV28xN1ZuTEVjTUVGcy1lNndFLVhQQUtjd2Z6ck50UHFMck92NkhsazhKWjZLbk9ZUmRnMDAzRVg1Z3YxTDk2M1ZyZDJ2SnpwUWx2a1dYdmhvT1VFNXVrRWZDNHlablYtNFJLTHNfdUY1STVOT3BVZlk?oc=5</t>
         </is>
       </c>
-      <c r="L215" s="11" t="inlineStr">
+      <c r="M215" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13534,26 +14610,31 @@
       </c>
       <c r="G216" s="11" t="inlineStr">
         <is>
+          <t>Великі угоди з акціями штучного інтелекту підвищують кількість акцій більше, ніж кількість покупців Bloomberg</t>
+        </is>
+      </c>
+      <c r="H216" s="11" t="inlineStr">
+        <is>
           <t>валюта_фінанси</t>
         </is>
       </c>
-      <c r="H216" s="11" t="inlineStr">
+      <c r="I216" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I216" s="11" t="inlineStr">
+      <c r="J216" s="11" t="inlineStr">
         <is>
           <t>США</t>
         </is>
       </c>
-      <c r="J216" s="11" t="inlineStr"/>
-      <c r="K216" s="13" t="inlineStr">
+      <c r="K216" s="11" t="inlineStr"/>
+      <c r="L216" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPeGR2NzFtYXRmRnVkZHR4SW5yc0FObm5yNkl4eHJTZWgxa0kxR3RJRERMSHo5Y2ZaU1ZUS1hreGpMRTNwQk4wMERrMTd1SS1PMlEyWmIzSHd2dTNYTXNSNEZla3ZGaE80OWJ0WWR6cGlMbS12M1BINzZfak83TWJ1UXd6NVhJQXNNbHAtZHdfZldKbFpWTXFPQ19JUlBzaHFnYWNpME83TzJrS1JTc2YzTHo4RQ?oc=5</t>
         </is>
       </c>
-      <c r="L216" s="11" t="inlineStr">
+      <c r="M216" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13592,30 +14673,35 @@
       </c>
       <c r="G217" s="11" t="inlineStr">
         <is>
+          <t>Бразильська компанія Embraer бачить можливий прорив у Китаї для літаків E2 Reuters</t>
+        </is>
+      </c>
+      <c r="H217" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H217" s="11" t="inlineStr">
+      <c r="I217" s="11" t="inlineStr">
         <is>
           <t>Послуги</t>
         </is>
       </c>
-      <c r="I217" s="11" t="inlineStr">
+      <c r="J217" s="11" t="inlineStr">
         <is>
           <t>Китай, Бразилія</t>
         </is>
       </c>
-      <c r="J217" s="11" t="inlineStr">
+      <c r="K217" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K217" s="13" t="inlineStr">
+      <c r="L217" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQLUxaRGJZclBXamdpMi11a3ZHemRhc0FhVm9SR0t1ZDVZZWUyZm9uVFZ5Rkc3d0F6QkJBOF9pM3pwQUVuMTFDQTlXakZBMU91NUpnekRVa01xU08xOVJHckpKYVVRS0F2enQtcDdpU09vVjJISlVqa19waXZBU1ZfQjg4UXFHeVpVUUU2VUE1WnljZXREWDNfa05saDFIczRhQVFKZlJfREJjOXlaaXRnYjc1YmFMYmkzY1NZ?oc=5</t>
         </is>
       </c>
-      <c r="L217" s="11" t="inlineStr">
+      <c r="M217" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13654,26 +14740,31 @@
       </c>
       <c r="G218" s="11" t="inlineStr">
         <is>
+          <t>США та Іран, здається, далекі від мирної угоди через 100 днів після початку війни Bloomberg</t>
+        </is>
+      </c>
+      <c r="H218" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H218" s="11" t="inlineStr">
+      <c r="I218" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I218" s="11" t="inlineStr">
+      <c r="J218" s="11" t="inlineStr">
         <is>
           <t>США, Іран</t>
         </is>
       </c>
-      <c r="J218" s="11" t="inlineStr"/>
-      <c r="K218" s="13" t="inlineStr">
+      <c r="K218" s="11" t="inlineStr"/>
+      <c r="L218" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPU3FxRnVNWEJhdzZseUVHSlJKcTFIUWhnQk0xdXkweDZPTjVFYW5Cdjl4aHc2dU1PYmxXclItWWx1aGpqSFFVdERVSW85WVF6RW9DS05laFZjSTNzcTV5TE94Uzc5XzAzcFdKeEFTcFpQODZxTjdXUFBVU1puZG1VcXEyLWljSFBkQ2ZsRmExWVAwYmNUSnkyd1RVZXRuQmtzWUVxS05qY2NNVWlhMkZOa2trZU0?oc=5</t>
         </is>
       </c>
-      <c r="L218" s="11" t="inlineStr">
+      <c r="M218" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13712,30 +14803,35 @@
       </c>
       <c r="G219" s="11" t="inlineStr">
         <is>
+          <t>Італійська авіакомпанія ITA Airways найближчим часом прийме рішення щодо позову через несправності двигуна RTX Reuters</t>
+        </is>
+      </c>
+      <c r="H219" s="11" t="inlineStr">
+        <is>
           <t>не_релевантно</t>
         </is>
       </c>
-      <c r="H219" s="11" t="inlineStr">
+      <c r="I219" s="11" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I219" s="11" t="inlineStr">
+      <c r="J219" s="11" t="inlineStr">
         <is>
           <t>Італія, США</t>
         </is>
       </c>
-      <c r="J219" s="11" t="inlineStr">
+      <c r="K219" s="11" t="inlineStr">
         <is>
           <t>Логістика</t>
         </is>
       </c>
-      <c r="K219" s="13" t="inlineStr">
+      <c r="L219" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNZEQ4Y1pvU1pnNDBKcW0xeElWX3NCS1FoREJzNld3WVRseFItZ3NlUUVjM3ZUS29odUhMNGpfMXJuZHRrRGxrT2ttZE9jc1g2bnhhYkM4OWNOcGhZLUUwMTh3bzJkV09ad0pCRGMyUlhqYUxESjhuWGVyUW9FelpVeVlGRVFUVDRrV19XVEYyTzRzM2tIcU82dTkwSGRKOVhScW5Vc0M3S3haUUxCSjI5Z1NpVmhsWTZoLXB5eEg4NDE2MFdyU0Z0WA?oc=5</t>
         </is>
       </c>
-      <c r="L219" s="11" t="inlineStr">
+      <c r="M219" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13774,26 +14870,31 @@
       </c>
       <c r="G220" s="11" t="inlineStr">
         <is>
+          <t>Японія стає супердержавою середніх держав Bloomberg</t>
+        </is>
+      </c>
+      <c r="H220" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H220" s="11" t="inlineStr">
+      <c r="I220" s="11" t="inlineStr">
         <is>
           <t>Всі категорії</t>
         </is>
       </c>
-      <c r="I220" s="11" t="inlineStr">
+      <c r="J220" s="11" t="inlineStr">
         <is>
           <t>Японія</t>
         </is>
       </c>
-      <c r="J220" s="11" t="inlineStr"/>
-      <c r="K220" s="13" t="inlineStr">
+      <c r="K220" s="11" t="inlineStr"/>
+      <c r="L220" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQMm9uX2oydWM4ek1aRXhHbzUtbmRlTlJWZE5ING9IMXN3TmphdFlINHMwZG5kZTRwcjA5dloyRlNrRXI0TERDdjRHdTNxRnVmRkxob1VtQnpZY2MwUnhlM19aN2lzd3hNWVZqMy1VbnFUUTlhNnF2NDVDM2t6bFlIN2xBWTRhTHczaU5CM25BNXRMcTRfRjNuREJHU05wSjQ?oc=5</t>
         </is>
       </c>
-      <c r="L220" s="11" t="inlineStr">
+      <c r="M220" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13832,26 +14933,31 @@
       </c>
       <c r="G221" s="11" t="inlineStr">
         <is>
+          <t>Safran інвестує 120 мільйонів євро в прецизійні навігаційні датчики у Франції Reuters</t>
+        </is>
+      </c>
+      <c r="H221" s="11" t="inlineStr">
+        <is>
           <t>не_релевантно</t>
         </is>
       </c>
-      <c r="H221" s="11" t="inlineStr">
+      <c r="I221" s="11" t="inlineStr">
         <is>
           <t>Запчастини</t>
         </is>
       </c>
-      <c r="I221" s="11" t="inlineStr">
+      <c r="J221" s="11" t="inlineStr">
         <is>
           <t>Франція</t>
         </is>
       </c>
-      <c r="J221" s="11" t="inlineStr"/>
-      <c r="K221" s="13" t="inlineStr">
+      <c r="K221" s="11" t="inlineStr"/>
+      <c r="L221" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPOHRhT2U5MWJCSDBPemhEMHZaeDZ0Tm03RXp3X05pVlppa3M4V0c4cy1neng3LWNCaDhFV09xOVBrUHZDSnFzM1NtSTJ4bTN6UXFjYkN1bk5ZSjNIbXMzaG1BeDZDUTUzc2NzWnZ0UGNZcUdQdnZCLTFiSEFwa0RmRGd1S2dVUHNybEZYaFVBcHFtWnZpNkkxNVNIZG5Pb2tkaEg1WUtwaVdTS0RQS2ZEUTZObDdfWGxPQ3B5b0RGRGZiUQ?oc=5</t>
         </is>
       </c>
-      <c r="L221" s="11" t="inlineStr">
+      <c r="M221" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13890,30 +14996,35 @@
       </c>
       <c r="G222" s="11" t="inlineStr">
         <is>
+          <t>Bloomberg повідомляє CCTV, що в Китаї запускають збірні електроцентрали для центрів обробки даних</t>
+        </is>
+      </c>
+      <c r="H222" s="11" t="inlineStr">
+        <is>
           <t>енергетика</t>
         </is>
       </c>
-      <c r="H222" s="11" t="inlineStr">
+      <c r="I222" s="11" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I222" s="11" t="inlineStr">
+      <c r="J222" s="11" t="inlineStr">
         <is>
           <t>Китай</t>
         </is>
       </c>
-      <c r="J222" s="11" t="inlineStr">
+      <c r="K222" s="11" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K222" s="13" t="inlineStr">
+      <c r="L222" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxObW5iR3ZkQkpYc2U1WXV1OUd3VElpejdTTHVaVTZGWUJoQUtNX0tBZjR2VERMZFFVU2tHU0pSQ0NmOXF1aDZ2TkFGSmNwRDctREZMTFUwUjV2R21janltRFVMdVIta0FtUU5tQmNIVTZGVks1X05PMXpDVGdMWkZvMU5NSkJiMWx4dmNTeHNRY3ZmYXM0b0tHX2l4LTRBQTFZbW9vWFRISnZVMUNsN0Q4bHBTS2M?oc=5</t>
         </is>
       </c>
-      <c r="L222" s="11" t="inlineStr">
+      <c r="M222" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
@@ -13952,260 +15063,265 @@
       </c>
       <c r="G223" s="11" t="inlineStr">
         <is>
+          <t>ЄС планує знизити податки на чисту енергію, щоб скоротити рахунки за електроенергію Bloomberg</t>
+        </is>
+      </c>
+      <c r="H223" s="11" t="inlineStr">
+        <is>
           <t>геополітика</t>
         </is>
       </c>
-      <c r="H223" s="11" t="inlineStr">
+      <c r="I223" s="11" t="inlineStr">
         <is>
           <t>Енергоносії</t>
         </is>
       </c>
-      <c r="I223" s="11" t="inlineStr">
+      <c r="J223" s="11" t="inlineStr">
         <is>
           <t>ЄС</t>
         </is>
       </c>
-      <c r="J223" s="11" t="inlineStr">
+      <c r="K223" s="11" t="inlineStr">
         <is>
           <t>Паливо і енергоносії</t>
         </is>
       </c>
-      <c r="K223" s="13" t="inlineStr">
+      <c r="L223" s="13" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQTjNqNVM4c2huU0R2MkFWbEd3bWxUWlNBUUpjcUFTUVA3N1J6SWxvLWhBNlFycndraUZJSHlRWFZhVXA1T1Z5YTV5R3g3UHQ2RFVqOUJ0aHdoOUpkdk5yckpzejlGdGxxOTBOdFpCMHdlMFg5ZXY0MzRJbVJHRVBWSnUta2xvdndjc1NCQU1ucVdvQ1ZjWjM4QkctNHZjd0t3ZmVMV2FjSHl0aHBxNGtIaDJxV0JaUQ?oc=5</t>
         </is>
       </c>
-      <c r="L223" s="11" t="inlineStr">
+      <c r="M223" s="11" t="inlineStr">
         <is>
           <t>news_2026-06-09_AI.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K189" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K190" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K195" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K196" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K197" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K198" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K208" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K209" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K212" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K215" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K216" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K217" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K218" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K219" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K221" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K222" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId222"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
